--- a/research/traditional_assets/database/data/greece/greece_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_telecom_services.xlsx
@@ -650,10 +650,10 @@
         <v>0.3099711348559275</v>
       </c>
       <c r="X2">
-        <v>0.09313609751358749</v>
+        <v>0.09312892466090551</v>
       </c>
       <c r="Y2">
-        <v>0.21683503734234</v>
+        <v>0.216842210195022</v>
       </c>
       <c r="Z2">
         <v>1.765785095017077</v>
@@ -662,10 +662,10 @@
         <v>0.2748034865275618</v>
       </c>
       <c r="AB2">
-        <v>0.08811908972481827</v>
+        <v>0.08811312427442389</v>
       </c>
       <c r="AC2">
-        <v>0.1866843968027435</v>
+        <v>0.1866903622531379</v>
       </c>
       <c r="AD2">
         <v>1268.8</v>
@@ -787,10 +787,10 @@
         <v>0.3099711348559275</v>
       </c>
       <c r="X3">
-        <v>0.09313609751358749</v>
+        <v>0.09312892466090551</v>
       </c>
       <c r="Y3">
-        <v>0.21683503734234</v>
+        <v>0.216842210195022</v>
       </c>
       <c r="Z3">
         <v>1.765785095017077</v>
@@ -799,10 +799,10 @@
         <v>0.2748034865275618</v>
       </c>
       <c r="AB3">
-        <v>0.08811908972481827</v>
+        <v>0.08811312427442389</v>
       </c>
       <c r="AC3">
-        <v>0.1866843968027435</v>
+        <v>0.1866903622531379</v>
       </c>
       <c r="AD3">
         <v>1268.8</v>
@@ -1157,13 +1157,13 @@
         <v>6268.8</v>
       </c>
       <c r="L2">
-        <v>7697.69383575485</v>
+        <v>7697.7208730791</v>
       </c>
       <c r="M2">
         <v>7022.2</v>
       </c>
       <c r="N2">
-        <v>7182.29383575485</v>
+        <v>7182.3208730791</v>
       </c>
       <c r="O2">
         <v>1268.8</v>
@@ -1172,16 +1172,16 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.0881190897248183</v>
+        <v>0.0881131242744239</v>
       </c>
       <c r="R2">
-        <v>0.0866820003919806</v>
+        <v>0.08667580553052059</v>
       </c>
       <c r="S2">
         <v>0.063331401810067</v>
       </c>
       <c r="T2">
-        <v>0.059665401810067</v>
+        <v>0.058573401810067</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.09313609751358751</v>
+        <v>0.0931289246609055</v>
       </c>
       <c r="X2">
-        <v>0.0866820003919806</v>
+        <v>0.08667580553052059</v>
       </c>
       <c r="Y2">
         <v>0.616854549154934</v>
@@ -1236,7 +1236,7 @@
         <v>6268.8</v>
       </c>
       <c r="AK2">
-        <v>0.07673785915729414</v>
+        <v>0.07672623104708273</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08668200039198062</v>
+        <v>0.08667580553052057</v>
       </c>
       <c r="C2">
-        <v>7697.693835754849</v>
+        <v>7697.7208730791</v>
       </c>
       <c r="D2">
-        <v>7182.293835754849</v>
+        <v>7182.3208730791</v>
       </c>
       <c r="E2">
         <v>-1268.8</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08668200039198062</v>
+        <v>0.08667580553052057</v>
       </c>
       <c r="T2">
         <v>0.532748774085323</v>
       </c>
       <c r="U2">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V2">
         <v>0.22</v>
       </c>
       <c r="W2">
-        <v>0.05966540181006696</v>
+        <v>0.05857340181006696</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08673071400921895</v>
+        <v>0.08671361277645408</v>
       </c>
       <c r="C3">
-        <v>7616.771633486631</v>
+        <v>7618.039596012441</v>
       </c>
       <c r="D3">
-        <v>7176.747633486631</v>
+        <v>7178.015596012441</v>
       </c>
       <c r="E3">
         <v>-1193.424</v>
@@ -1539,37 +1539,37 @@
         <v>560.1</v>
       </c>
       <c r="M3">
-        <v>5.76581964978924</v>
+        <v>5.66029324978924</v>
       </c>
       <c r="N3">
-        <v>554.3341803502108</v>
+        <v>554.4397067502108</v>
       </c>
       <c r="O3">
-        <v>121.9535196770464</v>
+        <v>121.9767354850464</v>
       </c>
       <c r="P3">
-        <v>432.3806606731644</v>
+        <v>432.4629712651644</v>
       </c>
       <c r="Q3">
-        <v>1134.280660673164</v>
+        <v>1134.362971265164</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08700410100112957</v>
+        <v>0.08699785733167012</v>
       </c>
       <c r="T3">
         <v>0.5369461886690254</v>
       </c>
       <c r="U3">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V3">
         <v>0.22</v>
       </c>
       <c r="W3">
-        <v>0.05966540181006696</v>
+        <v>0.05857340181006696</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>97.14143591370805</v>
+        <v>98.95247035493351</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08677942762645725</v>
+        <v>0.08675142002238763</v>
       </c>
       <c r="C4">
-        <v>7535.857990217903</v>
+        <v>7538.363477252397</v>
       </c>
       <c r="D4">
-        <v>7171.209990217903</v>
+        <v>7173.715477252398</v>
       </c>
       <c r="E4">
         <v>-1118.048</v>
@@ -1621,37 +1621,37 @@
         <v>560.1</v>
       </c>
       <c r="M4">
-        <v>11.53163929957848</v>
+        <v>11.32058649957848</v>
       </c>
       <c r="N4">
-        <v>548.5683607004215</v>
+        <v>548.7794135004216</v>
       </c>
       <c r="O4">
-        <v>120.6850393540927</v>
+        <v>120.7314709700927</v>
       </c>
       <c r="P4">
-        <v>427.8833213463288</v>
+        <v>428.0479425303288</v>
       </c>
       <c r="Q4">
-        <v>1129.783321346329</v>
+        <v>1129.947942530329</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08733277509209787</v>
+        <v>0.08732648161855744</v>
       </c>
       <c r="T4">
         <v>0.5412292647748445</v>
       </c>
       <c r="U4">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V4">
         <v>0.22</v>
       </c>
       <c r="W4">
-        <v>0.05966540181006696</v>
+        <v>0.05857340181006696</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>48.57071795685403</v>
+        <v>49.47623517746676</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08682814124369558</v>
+        <v>0.08678922726832115</v>
       </c>
       <c r="C5">
-        <v>7454.952886151332</v>
+        <v>7458.692507534</v>
       </c>
       <c r="D5">
-        <v>7165.680886151332</v>
+        <v>7169.420507534001</v>
       </c>
       <c r="E5">
         <v>-1042.672</v>
@@ -1703,37 +1703,37 @@
         <v>560.1</v>
       </c>
       <c r="M5">
-        <v>17.29745894936772</v>
+        <v>16.98087974936772</v>
       </c>
       <c r="N5">
-        <v>542.8025410506323</v>
+        <v>543.1191202506322</v>
       </c>
       <c r="O5">
-        <v>119.4165590311391</v>
+        <v>119.4862064551391</v>
       </c>
       <c r="P5">
-        <v>423.3859820194932</v>
+        <v>423.6329137954932</v>
       </c>
       <c r="Q5">
-        <v>1125.285982019493</v>
+        <v>1125.532913795493</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08766822596844698</v>
+        <v>0.08766188166393726</v>
       </c>
       <c r="T5">
         <v>0.545600651728206</v>
       </c>
       <c r="U5">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V5">
         <v>0.22</v>
       </c>
       <c r="W5">
-        <v>0.05966540181006696</v>
+        <v>0.05857340181006696</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>32.38047863790268</v>
+        <v>32.98415678497783</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08687685486093387</v>
+        <v>0.08682703451425468</v>
       </c>
       <c r="C6">
-        <v>7374.056301550605</v>
+        <v>7379.026677614442</v>
       </c>
       <c r="D6">
-        <v>7160.160301550605</v>
+        <v>7165.130677614442</v>
       </c>
       <c r="E6">
         <v>-967.2959999999999</v>
@@ -1785,37 +1785,37 @@
         <v>560.1</v>
       </c>
       <c r="M6">
-        <v>23.06327859915696</v>
+        <v>22.64117299915696</v>
       </c>
       <c r="N6">
-        <v>537.036721400843</v>
+        <v>537.458827000843</v>
       </c>
       <c r="O6">
-        <v>118.1480787081855</v>
+        <v>118.2409419401855</v>
       </c>
       <c r="P6">
-        <v>418.8886426926575</v>
+        <v>419.2178850606576</v>
       </c>
       <c r="Q6">
-        <v>1120.788642692658</v>
+        <v>1121.117885060657</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08801066540472</v>
+        <v>0.0880042692102625</v>
       </c>
       <c r="T6">
         <v>0.550063109243096</v>
       </c>
       <c r="U6">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.05966540181006696</v>
+        <v>0.05857340181006696</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>24.28535897842701</v>
+        <v>24.73811758873337</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08692556847817219</v>
+        <v>0.0868648417601882</v>
       </c>
       <c r="C7">
-        <v>7293.168216740169</v>
+        <v>7299.365978273029</v>
       </c>
       <c r="D7">
-        <v>7154.648216740169</v>
+        <v>7160.84597827303</v>
       </c>
       <c r="E7">
         <v>-891.9199999999998</v>
@@ -1867,37 +1867,37 @@
         <v>560.1</v>
       </c>
       <c r="M7">
-        <v>28.8290982489462</v>
+        <v>28.3014662489462</v>
       </c>
       <c r="N7">
-        <v>531.2709017510538</v>
+        <v>531.7985337510538</v>
       </c>
       <c r="O7">
-        <v>116.8795983852318</v>
+        <v>116.9956774252318</v>
       </c>
       <c r="P7">
-        <v>414.391303365822</v>
+        <v>414.8028563258219</v>
       </c>
       <c r="Q7">
-        <v>1116.291303365822</v>
+        <v>1116.702856325822</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.088360314092283</v>
+        <v>0.08835386491545774</v>
       </c>
       <c r="T7">
         <v>0.5546195132319837</v>
       </c>
       <c r="U7">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.05966540181006696</v>
+        <v>0.05857340181006696</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.42828718274161</v>
+        <v>19.7904940709867</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08697428209541049</v>
+        <v>0.08690264900612171</v>
       </c>
       <c r="C8">
-        <v>7212.288612105028</v>
+        <v>7219.710400311111</v>
       </c>
       <c r="D8">
-        <v>7149.144612105029</v>
+        <v>7156.566400311111</v>
       </c>
       <c r="E8">
         <v>-816.5439999999999</v>
@@ -1949,37 +1949,37 @@
         <v>560.1</v>
       </c>
       <c r="M8">
-        <v>34.59491789873544</v>
+        <v>33.96175949873544</v>
       </c>
       <c r="N8">
-        <v>525.5050821012646</v>
+        <v>526.1382405012646</v>
       </c>
       <c r="O8">
-        <v>115.6111180622782</v>
+        <v>115.7504129102782</v>
       </c>
       <c r="P8">
-        <v>409.8939640389864</v>
+        <v>410.3878275909864</v>
       </c>
       <c r="Q8">
-        <v>1111.793964038986</v>
+        <v>1112.287827590986</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08871740211362392</v>
+        <v>0.08871089882714649</v>
       </c>
       <c r="T8">
         <v>0.5592728619865922</v>
       </c>
       <c r="U8">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.05966540181006696</v>
+        <v>0.05857340181006696</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.19023931895134</v>
+        <v>16.49207839248892</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08702299571264881</v>
+        <v>0.08694045625205525</v>
       </c>
       <c r="C9">
-        <v>7131.41746809048</v>
+        <v>7140.059934552008</v>
       </c>
       <c r="D9">
-        <v>7143.64946809048</v>
+        <v>7152.291934552009</v>
       </c>
       <c r="E9">
         <v>-741.1679999999999</v>
@@ -2031,37 +2031,37 @@
         <v>560.1</v>
       </c>
       <c r="M9">
-        <v>40.36073754852468</v>
+        <v>39.62205274852468</v>
       </c>
       <c r="N9">
-        <v>519.7392624514754</v>
+        <v>520.4779472514754</v>
       </c>
       <c r="O9">
-        <v>114.3426377393246</v>
+        <v>114.5051483953246</v>
       </c>
       <c r="P9">
-        <v>405.3966247121508</v>
+        <v>405.9727988561508</v>
       </c>
       <c r="Q9">
-        <v>1107.296624712151</v>
+        <v>1107.872798856151</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08908216944725175</v>
+        <v>0.08907561088747372</v>
       </c>
       <c r="T9">
         <v>0.5640262827574291</v>
       </c>
       <c r="U9">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.05966540181006696</v>
+        <v>0.05857340181006696</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>13.87734798767258</v>
+        <v>14.13606719356193</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08707170932988711</v>
+        <v>0.08697826349798876</v>
       </c>
       <c r="C10">
-        <v>7050.554765201906</v>
+        <v>7060.414571840963</v>
       </c>
       <c r="D10">
-        <v>7138.162765201906</v>
+        <v>7148.022571840963</v>
       </c>
       <c r="E10">
         <v>-665.7919999999999</v>
@@ -2113,37 +2113,37 @@
         <v>560.1</v>
       </c>
       <c r="M10">
-        <v>46.12655719831392</v>
+        <v>45.28234599831392</v>
       </c>
       <c r="N10">
-        <v>513.9734428016861</v>
+        <v>514.8176540016862</v>
       </c>
       <c r="O10">
-        <v>113.074157416371</v>
+        <v>113.2598838803709</v>
       </c>
       <c r="P10">
-        <v>400.8992853853152</v>
+        <v>401.5577701213152</v>
       </c>
       <c r="Q10">
-        <v>1102.799285385315</v>
+        <v>1103.457770121315</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08945486650552366</v>
+        <v>0.08944825147085153</v>
       </c>
       <c r="T10">
         <v>0.5688830387624144</v>
       </c>
       <c r="U10">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.05966540181006696</v>
+        <v>0.05857340181006696</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.14267948921351</v>
+        <v>12.36905879436669</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08712042294712545</v>
+        <v>0.08701607074392229</v>
       </c>
       <c r="C11">
-        <v>6969.700484004529</v>
+        <v>6980.774303045053</v>
       </c>
       <c r="D11">
-        <v>7132.68448400453</v>
+        <v>7143.758303045053</v>
       </c>
       <c r="E11">
         <v>-590.4159999999999</v>
@@ -2195,37 +2195,37 @@
         <v>560.1</v>
       </c>
       <c r="M11">
-        <v>51.89237684810315</v>
+        <v>50.94263924810316</v>
       </c>
       <c r="N11">
-        <v>508.2076231518969</v>
+        <v>509.1573607518969</v>
       </c>
       <c r="O11">
-        <v>111.8056770934173</v>
+        <v>112.0146193654173</v>
       </c>
       <c r="P11">
-        <v>396.4019460584796</v>
+        <v>397.1427413864795</v>
       </c>
       <c r="Q11">
-        <v>1098.30194605848</v>
+        <v>1099.04274138648</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08983575470793342</v>
+        <v>0.08982908195716073</v>
       </c>
       <c r="T11">
         <v>0.5738465366576193</v>
       </c>
       <c r="U11">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.05966540181006696</v>
+        <v>0.05857340181006696</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>10.7934928793009</v>
+        <v>10.99471892832595</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08716913656436376</v>
+        <v>0.08705387798985581</v>
       </c>
       <c r="C12">
-        <v>6888.854605123195</v>
+        <v>6901.139119053142</v>
       </c>
       <c r="D12">
-        <v>7127.214605123196</v>
+        <v>7139.499119053143</v>
       </c>
       <c r="E12">
         <v>-515.0399999999998</v>
@@ -2277,37 +2277,37 @@
         <v>560.1</v>
       </c>
       <c r="M12">
-        <v>57.6581964978924</v>
+        <v>56.6029324978924</v>
       </c>
       <c r="N12">
-        <v>502.4418035021076</v>
+        <v>503.4970675021076</v>
       </c>
       <c r="O12">
-        <v>110.5371967704637</v>
+        <v>110.7693548504637</v>
       </c>
       <c r="P12">
-        <v>391.904606731644</v>
+        <v>392.7277126516439</v>
       </c>
       <c r="Q12">
-        <v>1093.804606731644</v>
+        <v>1094.627712651644</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09022510709261895</v>
+        <v>0.09021837534316568</v>
       </c>
       <c r="T12">
         <v>0.578920334506051</v>
       </c>
       <c r="U12">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.05966540181006696</v>
+        <v>0.05857340181006696</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.714143591370805</v>
+        <v>9.89524703549335</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08721785018160207</v>
+        <v>0.08709168523578935</v>
       </c>
       <c r="C13">
-        <v>6808.017109242132</v>
+        <v>6821.509010775806</v>
       </c>
       <c r="D13">
-        <v>7121.753109242133</v>
+        <v>7135.245010775807</v>
       </c>
       <c r="E13">
         <v>-439.6639999999999</v>
@@ -2359,37 +2359,37 @@
         <v>560.1</v>
       </c>
       <c r="M13">
-        <v>63.42401614768164</v>
+        <v>62.26322574768164</v>
       </c>
       <c r="N13">
-        <v>496.6759838523184</v>
+        <v>497.8367742523184</v>
       </c>
       <c r="O13">
-        <v>109.26871644751</v>
+        <v>109.52409033551</v>
       </c>
       <c r="P13">
-        <v>387.4072674048084</v>
+        <v>388.3126839168083</v>
       </c>
       <c r="Q13">
-        <v>1089.307267404808</v>
+        <v>1090.212683916808</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09062320896909518</v>
+        <v>0.09061641689514829</v>
       </c>
       <c r="T13">
         <v>0.5841081502836609</v>
       </c>
       <c r="U13">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.05966540181006696</v>
+        <v>0.05857340181006696</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.831039628518912</v>
+        <v>8.995679123175773</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08736952379884039</v>
+        <v>0.08726989248172287</v>
       </c>
       <c r="C14">
-        <v>6715.689793777405</v>
+        <v>6726.149032507692</v>
       </c>
       <c r="D14">
-        <v>7104.801793777405</v>
+        <v>7115.261032507692</v>
       </c>
       <c r="E14">
         <v>-364.2879999999999</v>
@@ -2441,37 +2441,37 @@
         <v>560.1</v>
       </c>
       <c r="M14">
-        <v>70.18479899747088</v>
+        <v>69.28028699747088</v>
       </c>
       <c r="N14">
-        <v>489.9152010025292</v>
+        <v>490.8197130025292</v>
       </c>
       <c r="O14">
-        <v>107.7813442205564</v>
+        <v>107.9803368605564</v>
       </c>
       <c r="P14">
-        <v>382.1338567819727</v>
+        <v>382.8393761419728</v>
       </c>
       <c r="Q14">
-        <v>1084.033856781973</v>
+        <v>1084.739376141973</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.0910303586154913</v>
+        <v>0.09102350484603958</v>
       </c>
       <c r="T14">
         <v>0.5894138709653074</v>
       </c>
       <c r="U14">
-        <v>0.07759410488470123</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V14">
         <v>0.22</v>
       </c>
       <c r="W14">
-        <v>0.06052340181006696</v>
+        <v>0.05974340181006696</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.980360533912526</v>
+        <v>8.084550804768561</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08742681741607869</v>
+        <v>0.0873193997276564</v>
       </c>
       <c r="C15">
-        <v>6633.93153581055</v>
+        <v>6645.241193581566</v>
       </c>
       <c r="D15">
-        <v>7098.41953581055</v>
+        <v>7109.729193581567</v>
       </c>
       <c r="E15">
         <v>-288.9119999999999</v>
@@ -2523,37 +2523,37 @@
         <v>560.1</v>
       </c>
       <c r="M15">
-        <v>76.03353224726011</v>
+        <v>75.05364424726012</v>
       </c>
       <c r="N15">
-        <v>484.0664677527399</v>
+        <v>485.0463557527399</v>
       </c>
       <c r="O15">
-        <v>106.4946229056028</v>
+        <v>106.7101982656028</v>
       </c>
       <c r="P15">
-        <v>377.5718448471371</v>
+        <v>378.3361574871371</v>
       </c>
       <c r="Q15">
-        <v>1079.471844847137</v>
+        <v>1080.236157487137</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09144686802387354</v>
+        <v>0.09143995114062953</v>
       </c>
       <c r="T15">
         <v>0.5948415622373364</v>
       </c>
       <c r="U15">
-        <v>0.07759410488470123</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.06052340181006696</v>
+        <v>0.05974340181006696</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.366486646688486</v>
+        <v>7.462662281324825</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08748411103331701</v>
+        <v>0.08736890697358991</v>
       </c>
       <c r="C16">
-        <v>6552.184733943399</v>
+        <v>6564.341949552797</v>
       </c>
       <c r="D16">
-        <v>7092.048733943399</v>
+        <v>7104.205949552797</v>
       </c>
       <c r="E16">
         <v>-213.5359999999998</v>
@@ -2605,37 +2605,37 @@
         <v>560.1</v>
       </c>
       <c r="M16">
-        <v>81.88226549704936</v>
+        <v>80.82700149704937</v>
       </c>
       <c r="N16">
-        <v>478.2177345029506</v>
+        <v>479.2729985029507</v>
       </c>
       <c r="O16">
-        <v>105.2079015906491</v>
+        <v>105.4400596706491</v>
       </c>
       <c r="P16">
-        <v>373.0098329123015</v>
+        <v>373.8329388323015</v>
       </c>
       <c r="Q16">
-        <v>1074.909832912301</v>
+        <v>1075.732938832301</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09187306369756701</v>
+        <v>0.09186608223276807</v>
       </c>
       <c r="T16">
         <v>0.6003954788877849</v>
       </c>
       <c r="U16">
-        <v>0.07759410488470123</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.06052340181006696</v>
+        <v>0.05974340181006696</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.840309029067879</v>
+        <v>6.929614975515908</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08779880465055531</v>
+        <v>0.08761731421952344</v>
       </c>
       <c r="C17">
-        <v>6442.019073670839</v>
+        <v>6461.381606876657</v>
       </c>
       <c r="D17">
-        <v>7057.25907367084</v>
+        <v>7076.621606876658</v>
       </c>
       <c r="E17">
         <v>-138.1599999999999</v>
@@ -2687,37 +2687,37 @@
         <v>560.1</v>
       </c>
       <c r="M17">
-        <v>90.2184067468386</v>
+        <v>88.5224467468386</v>
       </c>
       <c r="N17">
-        <v>469.8815932531614</v>
+        <v>471.5775532531615</v>
       </c>
       <c r="O17">
-        <v>103.3739505156955</v>
+        <v>103.7470617156955</v>
       </c>
       <c r="P17">
-        <v>366.5076427374659</v>
+        <v>367.8304915374659</v>
       </c>
       <c r="Q17">
-        <v>1068.407642737466</v>
+        <v>1069.730491537466</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09230928750475914</v>
+        <v>0.09230223993883929</v>
       </c>
       <c r="T17">
         <v>0.6060800759300086</v>
       </c>
       <c r="U17">
-        <v>0.07979410488470122</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.06223940181006695</v>
+        <v>0.06106940181006695</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.208267472198814</v>
+        <v>6.327208754202254</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08787325826779363</v>
+        <v>0.08768008146545696</v>
       </c>
       <c r="C18">
-        <v>6358.462030913355</v>
+        <v>6379.069496368156</v>
       </c>
       <c r="D18">
-        <v>7049.078030913355</v>
+        <v>7069.685496368156</v>
       </c>
       <c r="E18">
         <v>-62.78399999999988</v>
@@ -2769,37 +2769,37 @@
         <v>560.1</v>
       </c>
       <c r="M18">
-        <v>96.23296719662783</v>
+        <v>94.42394319662783</v>
       </c>
       <c r="N18">
-        <v>463.8670328033722</v>
+        <v>465.6760568033722</v>
       </c>
       <c r="O18">
-        <v>102.0507472167419</v>
+        <v>102.4487324967419</v>
       </c>
       <c r="P18">
-        <v>361.8162855866303</v>
+        <v>363.2273243066303</v>
       </c>
       <c r="Q18">
-        <v>1063.71628558663</v>
+        <v>1065.12732430663</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.0927558975930749</v>
+        <v>0.09274878235219791</v>
       </c>
       <c r="T18">
         <v>0.6119000205208567</v>
       </c>
       <c r="U18">
-        <v>0.07979410488470122</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.06223940181006695</v>
+        <v>0.06106940181006695</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.820250755186388</v>
+        <v>5.931758207064614</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08814661188503194</v>
+        <v>0.08774284871139049</v>
       </c>
       <c r="C19">
-        <v>6253.211612097248</v>
+        <v>6296.770969324601</v>
       </c>
       <c r="D19">
-        <v>7019.203612097248</v>
+        <v>7062.762969324601</v>
       </c>
       <c r="E19">
         <v>12.5920000000001</v>
@@ -2851,45 +2851,45 @@
         <v>560.1</v>
       </c>
       <c r="M19">
-        <v>104.1696156464171</v>
+        <v>100.3254396464171</v>
       </c>
       <c r="N19">
-        <v>455.930384353583</v>
+        <v>459.774560353583</v>
       </c>
       <c r="O19">
-        <v>100.3046845577882</v>
+        <v>101.1504032777883</v>
       </c>
       <c r="P19">
-        <v>355.6256997957947</v>
+        <v>358.6241570757947</v>
       </c>
       <c r="Q19">
-        <v>1057.525699795795</v>
+        <v>1060.524157075795</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09321326937026572</v>
+        <v>0.09320608482370976</v>
       </c>
       <c r="T19">
         <v>0.6178602047403999</v>
       </c>
       <c r="U19">
-        <v>0.08129410488470122</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.06340940181006695</v>
+        <v>0.06106940181006695</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>5.376807781466215</v>
+        <v>5.582831253707872</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08823276550227024</v>
+        <v>0.087917935957324</v>
       </c>
       <c r="C20">
-        <v>6168.472419223881</v>
+        <v>6202.156256162879</v>
       </c>
       <c r="D20">
-        <v>7009.840419223881</v>
+        <v>7043.524256162879</v>
       </c>
       <c r="E20">
         <v>87.96800000000007</v>
@@ -2933,37 +2933,37 @@
         <v>560.1</v>
       </c>
       <c r="M20">
-        <v>110.2972400962063</v>
+        <v>107.3123504962063</v>
       </c>
       <c r="N20">
-        <v>449.8027599037937</v>
+        <v>452.7876495037937</v>
       </c>
       <c r="O20">
-        <v>98.95660717883462</v>
+        <v>99.61328289083461</v>
       </c>
       <c r="P20">
-        <v>350.8461527249591</v>
+        <v>353.1743666129591</v>
       </c>
       <c r="Q20">
-        <v>1052.746152724959</v>
+        <v>1055.074366612959</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09368179655665633</v>
+        <v>0.09367454101403896</v>
       </c>
       <c r="T20">
         <v>0.6239657593067611</v>
       </c>
       <c r="U20">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.06340940181006695</v>
+        <v>0.06169340181006696</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.078096238051424</v>
+        <v>5.219343322647663</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08831891911950857</v>
+        <v>0.08798694320325753</v>
       </c>
       <c r="C21">
-        <v>6083.75817293869</v>
+        <v>6119.226454473512</v>
       </c>
       <c r="D21">
-        <v>7000.502172938691</v>
+        <v>7035.970454473512</v>
       </c>
       <c r="E21">
         <v>163.3440000000001</v>
@@ -3015,37 +3015,37 @@
         <v>560.1</v>
       </c>
       <c r="M21">
-        <v>116.4248645459955</v>
+        <v>113.2741477459955</v>
       </c>
       <c r="N21">
-        <v>443.6751354540045</v>
+        <v>446.8258522540045</v>
       </c>
       <c r="O21">
-        <v>97.60852979988098</v>
+        <v>98.30168749588098</v>
       </c>
       <c r="P21">
-        <v>346.0666056541235</v>
+        <v>348.5241647581235</v>
       </c>
       <c r="Q21">
-        <v>1047.966605654123</v>
+        <v>1050.424164758123</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09416189231555042</v>
+        <v>0.09415456402388248</v>
       </c>
       <c r="T21">
         <v>0.6302220683068598</v>
       </c>
       <c r="U21">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.06340940181006695</v>
+        <v>0.06169340181006696</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.810828014996087</v>
+        <v>4.944641042508312</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08840507273674689</v>
+        <v>0.08805595044919105</v>
       </c>
       <c r="C22">
-        <v>5999.068773675592</v>
+        <v>6036.312837520578</v>
       </c>
       <c r="D22">
-        <v>6991.188773675593</v>
+        <v>7028.432837520579</v>
       </c>
       <c r="E22">
         <v>238.7200000000003</v>
@@ -3097,37 +3097,37 @@
         <v>560.1</v>
       </c>
       <c r="M22">
-        <v>122.5524889957848</v>
+        <v>119.2359449957848</v>
       </c>
       <c r="N22">
-        <v>437.5475110042152</v>
+        <v>440.8640550042152</v>
       </c>
       <c r="O22">
-        <v>96.26045242092735</v>
+        <v>96.99009210092736</v>
       </c>
       <c r="P22">
-        <v>341.2870585832878</v>
+        <v>343.8739629032879</v>
       </c>
       <c r="Q22">
-        <v>1043.187058583288</v>
+        <v>1045.773962903288</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09465399046841685</v>
+        <v>0.09464658760897207</v>
       </c>
       <c r="T22">
         <v>0.6366347850319609</v>
       </c>
       <c r="U22">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.06340940181006695</v>
+        <v>0.06169340181006696</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.570286614246282</v>
+        <v>4.697408990382896</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08849122635398518</v>
+        <v>0.08812495769512457</v>
       </c>
       <c r="C23">
-        <v>5914.404122397645</v>
+        <v>5953.415353343742</v>
       </c>
       <c r="D23">
-        <v>6981.900122397645</v>
+        <v>7020.911353343742</v>
       </c>
       <c r="E23">
         <v>314.096</v>
@@ -3179,37 +3179,37 @@
         <v>560.1</v>
       </c>
       <c r="M23">
-        <v>128.680113445574</v>
+        <v>125.197742245574</v>
       </c>
       <c r="N23">
-        <v>431.419886554426</v>
+        <v>434.902257754426</v>
       </c>
       <c r="O23">
-        <v>94.91237504197372</v>
+        <v>95.67849670597371</v>
       </c>
       <c r="P23">
-        <v>336.5075115124523</v>
+        <v>339.2237610484523</v>
       </c>
       <c r="Q23">
-        <v>1038.407511512452</v>
+        <v>1041.123761048452</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.0951585468023685</v>
+        <v>0.09515106748735508</v>
       </c>
       <c r="T23">
         <v>0.6432098490159253</v>
       </c>
       <c r="U23">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.06340940181006695</v>
+        <v>0.06169340181006696</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.352653918329793</v>
+        <v>4.47372284798371</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.0888176199712235</v>
+        <v>0.08819396494105811</v>
       </c>
       <c r="C24">
-        <v>5804.060760695699</v>
+        <v>5870.533950204852</v>
       </c>
       <c r="D24">
-        <v>6946.932760695699</v>
+        <v>7013.405950204852</v>
       </c>
       <c r="E24">
         <v>389.4720000000002</v>
@@ -3261,45 +3261,45 @@
         <v>560.1</v>
       </c>
       <c r="M24">
-        <v>137.1293186953633</v>
+        <v>131.1595394953633</v>
       </c>
       <c r="N24">
-        <v>422.9706813046367</v>
+        <v>428.9404605046367</v>
       </c>
       <c r="O24">
-        <v>93.05354988702008</v>
+        <v>94.36690131102009</v>
       </c>
       <c r="P24">
-        <v>329.9171314176166</v>
+        <v>334.5735591936167</v>
       </c>
       <c r="Q24">
-        <v>1031.817131417617</v>
+        <v>1036.473559193617</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09567604047821636</v>
+        <v>0.09566848274723509</v>
       </c>
       <c r="T24">
         <v>0.6499535043840939</v>
       </c>
       <c r="U24">
-        <v>0.08269410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.06450140181006696</v>
+        <v>0.06169340181006696</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.084465709658183</v>
+        <v>4.270371809438997</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08891469358846181</v>
+        <v>0.08844237218699162</v>
       </c>
       <c r="C25">
-        <v>5718.352497217969</v>
+        <v>5768.272887024945</v>
       </c>
       <c r="D25">
-        <v>6936.60049721797</v>
+        <v>6986.520887024945</v>
       </c>
       <c r="E25">
         <v>464.8480000000002</v>
@@ -3343,37 +3343,37 @@
         <v>560.1</v>
       </c>
       <c r="M25">
-        <v>143.3624695451525</v>
+        <v>138.8549847451525</v>
       </c>
       <c r="N25">
-        <v>416.7375304548475</v>
+        <v>421.2450152548475</v>
       </c>
       <c r="O25">
-        <v>91.68225670006645</v>
+        <v>92.67390335606645</v>
       </c>
       <c r="P25">
-        <v>325.0552737547811</v>
+        <v>328.5711118987811</v>
       </c>
       <c r="Q25">
-        <v>1026.955273754781</v>
+        <v>1030.471111898781</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09620697554824209</v>
+        <v>0.09619933736451458</v>
       </c>
       <c r="T25">
         <v>0.6568723196319554</v>
       </c>
       <c r="U25">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.06450140181006696</v>
+        <v>0.06247340181006696</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.90688024402087</v>
+        <v>4.033704666980299</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08901176720570012</v>
+        <v>0.08851917943292516</v>
       </c>
       <c r="C26">
-        <v>5632.674922715922</v>
+        <v>5684.625725080169</v>
       </c>
       <c r="D26">
-        <v>6926.298922715922</v>
+        <v>6978.24972508017</v>
       </c>
       <c r="E26">
         <v>540.2240000000002</v>
@@ -3425,37 +3425,37 @@
         <v>560.1</v>
       </c>
       <c r="M26">
-        <v>149.5956203949418</v>
+        <v>144.8921579949418</v>
       </c>
       <c r="N26">
-        <v>410.5043796050583</v>
+        <v>415.2078420050583</v>
       </c>
       <c r="O26">
-        <v>90.31096351311282</v>
+        <v>91.34572524111283</v>
       </c>
       <c r="P26">
-        <v>320.1934160919454</v>
+        <v>323.8621167639454</v>
       </c>
       <c r="Q26">
-        <v>1022.093416091945</v>
+        <v>1025.762116763945</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.0967518825937948</v>
+        <v>0.09674416184014353</v>
       </c>
       <c r="T26">
         <v>0.6639732089652868</v>
       </c>
       <c r="U26">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.06450140181006696</v>
+        <v>0.06247340181006696</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.744093567186667</v>
+        <v>3.865633639189454</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08910884082293845</v>
+        <v>0.08859598667885868</v>
       </c>
       <c r="C27">
-        <v>5547.02790066333</v>
+        <v>5600.998124008524</v>
       </c>
       <c r="D27">
-        <v>6916.027900663331</v>
+        <v>6969.998124008524</v>
       </c>
       <c r="E27">
         <v>615.6000000000001</v>
@@ -3507,37 +3507,37 @@
         <v>560.1</v>
       </c>
       <c r="M27">
-        <v>155.828771244731</v>
+        <v>150.929331244731</v>
       </c>
       <c r="N27">
-        <v>404.271228755269</v>
+        <v>409.170668755269</v>
       </c>
       <c r="O27">
-        <v>88.93967032615919</v>
+        <v>90.01754712615919</v>
       </c>
       <c r="P27">
-        <v>315.3315584291098</v>
+        <v>319.1531216291099</v>
       </c>
       <c r="Q27">
-        <v>1017.23155842911</v>
+        <v>1021.05312162911</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.0973113204938956</v>
+        <v>0.09730351496845592</v>
       </c>
       <c r="T27">
         <v>0.671263455347507</v>
       </c>
       <c r="U27">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.06450140181006696</v>
+        <v>0.06247340181006696</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.594329824499201</v>
+        <v>3.711008293621876</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08920591444017675</v>
+        <v>0.08867279392479221</v>
       </c>
       <c r="C28">
-        <v>5461.411295342599</v>
+        <v>5517.390014501272</v>
       </c>
       <c r="D28">
-        <v>6905.787295342599</v>
+        <v>6961.766014501272</v>
       </c>
       <c r="E28">
         <v>690.9760000000001</v>
@@ -3589,37 +3589,37 @@
         <v>560.1</v>
       </c>
       <c r="M28">
-        <v>162.0619220945202</v>
+        <v>156.9665044945203</v>
       </c>
       <c r="N28">
-        <v>398.0380779054798</v>
+        <v>403.1334955054798</v>
       </c>
       <c r="O28">
-        <v>87.56837713920555</v>
+        <v>88.68936901120556</v>
       </c>
       <c r="P28">
-        <v>310.4697007662742</v>
+        <v>314.4441264942743</v>
       </c>
       <c r="Q28">
-        <v>1012.369700766274</v>
+        <v>1016.344126494274</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09788587833724235</v>
+        <v>0.09787798574888487</v>
       </c>
       <c r="T28">
         <v>0.6787507354157332</v>
       </c>
       <c r="U28">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V28">
         <v>0.22</v>
       </c>
       <c r="W28">
-        <v>0.06450140181006696</v>
+        <v>0.06247340181006696</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.45608636971077</v>
+        <v>3.56827720540565</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08930298805741506</v>
+        <v>0.08874960117072572</v>
       </c>
       <c r="C29">
-        <v>5375.824971838762</v>
+        <v>5433.801327576733</v>
       </c>
       <c r="D29">
-        <v>6895.576971838763</v>
+        <v>6953.553327576733</v>
       </c>
       <c r="E29">
         <v>766.3520000000003</v>
@@ -3671,37 +3671,37 @@
         <v>560.1</v>
       </c>
       <c r="M29">
-        <v>168.2950729443095</v>
+        <v>163.0036777443095</v>
       </c>
       <c r="N29">
-        <v>391.8049270556905</v>
+        <v>397.0963222556906</v>
       </c>
       <c r="O29">
-        <v>86.19708395225192</v>
+        <v>87.36119089625193</v>
       </c>
       <c r="P29">
-        <v>305.6078431034387</v>
+        <v>309.7351313594386</v>
       </c>
       <c r="Q29">
-        <v>1007.507843103439</v>
+        <v>1011.635131359439</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09847617749136572</v>
+        <v>0.09846819545480501</v>
       </c>
       <c r="T29">
         <v>0.6864431464447326</v>
       </c>
       <c r="U29">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.06450140181006696</v>
+        <v>0.06247340181006696</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.328083170832593</v>
+        <v>3.436118790390625</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08940006167465336</v>
+        <v>0.08882640841665926</v>
       </c>
       <c r="C30">
-        <v>5290.26879603358</v>
+        <v>5350.231994578338</v>
       </c>
       <c r="D30">
-        <v>6885.39679603358</v>
+        <v>6945.359994578339</v>
       </c>
       <c r="E30">
         <v>841.7280000000003</v>
@@ -3753,37 +3753,37 @@
         <v>560.1</v>
       </c>
       <c r="M30">
-        <v>174.5282237940987</v>
+        <v>169.0408509940987</v>
       </c>
       <c r="N30">
-        <v>385.5717762059013</v>
+        <v>391.0591490059013</v>
       </c>
       <c r="O30">
-        <v>84.82579076529829</v>
+        <v>86.03301278129828</v>
       </c>
       <c r="P30">
-        <v>300.745985440603</v>
+        <v>305.026136224603</v>
       </c>
       <c r="Q30">
-        <v>1002.645985440603</v>
+        <v>1006.926136224603</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09908287384421476</v>
+        <v>0.09907479987477849</v>
       </c>
       <c r="T30">
         <v>0.694349235557871</v>
       </c>
       <c r="U30">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V30">
         <v>0.22</v>
       </c>
       <c r="W30">
-        <v>0.06450140181006696</v>
+        <v>0.06247340181006696</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.209223057588572</v>
+        <v>3.313400262162388</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.0894971352918917</v>
+        <v>0.08890321566259277</v>
       </c>
       <c r="C31">
-        <v>5204.742634599654</v>
+        <v>5266.681947172743</v>
       </c>
       <c r="D31">
-        <v>6875.246634599654</v>
+        <v>6937.185947172744</v>
       </c>
       <c r="E31">
         <v>917.104</v>
@@ -3835,37 +3835,37 @@
         <v>560.1</v>
       </c>
       <c r="M31">
-        <v>180.7613746438879</v>
+        <v>175.078024243888</v>
       </c>
       <c r="N31">
-        <v>379.3386253561121</v>
+        <v>385.0219757561121</v>
       </c>
       <c r="O31">
-        <v>83.45449757834466</v>
+        <v>84.70483466634465</v>
       </c>
       <c r="P31">
-        <v>295.8841277777674</v>
+        <v>300.3171410897674</v>
       </c>
       <c r="Q31">
-        <v>997.7841277777674</v>
+        <v>1002.217141089767</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09970666023517222</v>
+        <v>0.09969849174320192</v>
       </c>
       <c r="T31">
         <v>0.7024780314065907</v>
       </c>
       <c r="U31">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V31">
         <v>0.22</v>
       </c>
       <c r="W31">
-        <v>0.06450140181006696</v>
+        <v>0.06247340181006696</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.098560193533794</v>
+        <v>3.199145080708513</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09020260890912998</v>
+        <v>0.08898002290852629</v>
       </c>
       <c r="C32">
-        <v>5056.490750061404</v>
+        <v>5183.151117347901</v>
       </c>
       <c r="D32">
-        <v>6802.370750061405</v>
+        <v>6929.031117347901</v>
       </c>
       <c r="E32">
         <v>992.4800000000002</v>
@@ -3917,45 +3917,45 @@
         <v>560.1</v>
       </c>
       <c r="M32">
-        <v>192.8738534936772</v>
+        <v>181.1151974936772</v>
       </c>
       <c r="N32">
-        <v>367.2261465063228</v>
+        <v>378.9848025063228</v>
       </c>
       <c r="O32">
-        <v>80.78975223139102</v>
+        <v>83.37665655139102</v>
       </c>
       <c r="P32">
-        <v>286.4363942749318</v>
+        <v>295.6081459549318</v>
       </c>
       <c r="Q32">
-        <v>988.3363942749318</v>
+        <v>997.5081459549317</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1003482690944427</v>
+        <v>0.1003400033792946</v>
       </c>
       <c r="T32">
         <v>0.7108390785652737</v>
       </c>
       <c r="U32">
-        <v>0.08529410488470121</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V32">
         <v>0.22</v>
       </c>
       <c r="W32">
-        <v>0.06652940181006695</v>
+        <v>0.06247340181006696</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.903970599718232</v>
+        <v>3.092506911351563</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.09031996252636831</v>
+        <v>0.08966133015445983</v>
       </c>
       <c r="C33">
-        <v>4969.141653959733</v>
+        <v>5036.269556618648</v>
       </c>
       <c r="D33">
-        <v>6790.397653959733</v>
+        <v>6857.525556618649</v>
       </c>
       <c r="E33">
         <v>1067.856</v>
@@ -3999,37 +3999,37 @@
         <v>560.1</v>
       </c>
       <c r="M33">
-        <v>199.3029819434664</v>
+        <v>192.9940107434664</v>
       </c>
       <c r="N33">
-        <v>360.7970180565336</v>
+        <v>367.1059892565336</v>
       </c>
       <c r="O33">
-        <v>79.37534397243739</v>
+        <v>80.76331763643739</v>
       </c>
       <c r="P33">
-        <v>281.4216740840962</v>
+        <v>286.3426716200962</v>
       </c>
       <c r="Q33">
-        <v>983.3216740840962</v>
+        <v>988.2426716200962</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.101008475311953</v>
+        <v>0.1010001095555639</v>
       </c>
       <c r="T33">
         <v>0.7194424749169622</v>
       </c>
       <c r="U33">
-        <v>0.08529410488470121</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.06652940181006695</v>
+        <v>0.06442340181006696</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.810294128759579</v>
+        <v>2.902162599980898</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.09043731614360662</v>
+        <v>0.08975763740039336</v>
       </c>
       <c r="C34">
-        <v>4881.834632350779</v>
+        <v>4950.904657509687</v>
       </c>
       <c r="D34">
-        <v>6778.466632350779</v>
+        <v>6847.536657509688</v>
       </c>
       <c r="E34">
         <v>1143.232</v>
@@ -4081,37 +4081,37 @@
         <v>560.1</v>
       </c>
       <c r="M34">
-        <v>205.7321103932557</v>
+        <v>199.2196239932557</v>
       </c>
       <c r="N34">
-        <v>354.3678896067444</v>
+        <v>360.8803760067443</v>
       </c>
       <c r="O34">
-        <v>77.96093571348376</v>
+        <v>79.39368272148376</v>
       </c>
       <c r="P34">
-        <v>276.4069538932606</v>
+        <v>281.4866932852606</v>
       </c>
       <c r="Q34">
-        <v>978.3069538932606</v>
+        <v>983.3866932852605</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.10168809935939</v>
+        <v>0.1016796306193705</v>
       </c>
       <c r="T34">
         <v>0.7282989123378181</v>
       </c>
       <c r="U34">
-        <v>0.08529410488470121</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V34">
         <v>0.22</v>
       </c>
       <c r="W34">
-        <v>0.06652940181006695</v>
+        <v>0.06442340181006696</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.722472437235842</v>
+        <v>2.811470018731495</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.09055466976084492</v>
+        <v>0.08985394464632687</v>
       </c>
       <c r="C35">
-        <v>4794.569463843438</v>
+        <v>4865.568816397199</v>
       </c>
       <c r="D35">
-        <v>6766.577463843439</v>
+        <v>6837.5768163972</v>
       </c>
       <c r="E35">
         <v>1218.608</v>
@@ -4163,37 +4163,37 @@
         <v>560.1</v>
       </c>
       <c r="M35">
-        <v>212.1612388430449</v>
+        <v>205.4452372430449</v>
       </c>
       <c r="N35">
-        <v>347.9387611569551</v>
+        <v>354.6547627569551</v>
       </c>
       <c r="O35">
-        <v>76.54652745453014</v>
+        <v>78.02404780653011</v>
       </c>
       <c r="P35">
-        <v>271.392233702425</v>
+        <v>276.6307149504249</v>
       </c>
       <c r="Q35">
-        <v>973.2922337024249</v>
+        <v>978.5307149504249</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1023880106918251</v>
+        <v>0.102379435894037</v>
       </c>
       <c r="T35">
         <v>0.7374197210249679</v>
       </c>
       <c r="U35">
-        <v>0.08529410488470121</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V35">
         <v>0.22</v>
       </c>
       <c r="W35">
-        <v>0.06652940181006695</v>
+        <v>0.06442340181006696</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.639973272471119</v>
+        <v>2.726273957557813</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.09067202337808322</v>
+        <v>0.08995025189226039</v>
       </c>
       <c r="C36">
-        <v>4707.345928597135</v>
+        <v>4780.261906669512</v>
       </c>
       <c r="D36">
-        <v>6754.729928597136</v>
+        <v>6827.645906669512</v>
       </c>
       <c r="E36">
         <v>1293.984</v>
@@ -4245,37 +4245,37 @@
         <v>560.1</v>
       </c>
       <c r="M36">
-        <v>218.5903672928341</v>
+        <v>211.6708504928342</v>
       </c>
       <c r="N36">
-        <v>341.5096327071659</v>
+        <v>348.4291495071658</v>
       </c>
       <c r="O36">
-        <v>75.13211919557649</v>
+        <v>76.65441289157648</v>
       </c>
       <c r="P36">
-        <v>266.3775135115894</v>
+        <v>271.7747366155893</v>
       </c>
       <c r="Q36">
-        <v>968.2775135115894</v>
+        <v>973.6747366155894</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1031091314585765</v>
+        <v>0.1031004473891479</v>
       </c>
       <c r="T36">
         <v>0.7468169178541527</v>
       </c>
       <c r="U36">
-        <v>0.08529410488470121</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V36">
         <v>0.22</v>
       </c>
       <c r="W36">
-        <v>0.06652940181006695</v>
+        <v>0.06442340181006696</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.562326999751381</v>
+        <v>2.646089429394348</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.09152647699532154</v>
+        <v>0.09004655913819393</v>
       </c>
       <c r="C37">
-        <v>4546.942812993248</v>
+        <v>4694.983802449449</v>
       </c>
       <c r="D37">
-        <v>6669.702812993249</v>
+        <v>6817.74380244945</v>
       </c>
       <c r="E37">
         <v>1369.36</v>
@@ -4327,45 +4327,45 @@
         <v>560.1</v>
       </c>
       <c r="M37">
-        <v>232.1425277426234</v>
+        <v>217.8964637426234</v>
       </c>
       <c r="N37">
-        <v>327.9574722573766</v>
+        <v>342.2035362573766</v>
       </c>
       <c r="O37">
-        <v>72.15064389662285</v>
+        <v>75.28477797662286</v>
       </c>
       <c r="P37">
-        <v>255.8068283607537</v>
+        <v>266.9187582807538</v>
       </c>
       <c r="Q37">
-        <v>957.7068283607537</v>
+        <v>968.8187582807537</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1038524405566125</v>
+        <v>0.1038436438533392</v>
       </c>
       <c r="T37">
         <v>0.7565032592011587</v>
       </c>
       <c r="U37">
-        <v>0.08799410488470122</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V37">
         <v>0.22</v>
       </c>
       <c r="W37">
-        <v>0.06863540181006696</v>
+        <v>0.06442340181006696</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.412741885110268</v>
+        <v>2.570486874268796</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.09166489061255988</v>
+        <v>0.09112566638412745</v>
       </c>
       <c r="C38">
-        <v>4457.994258459075</v>
+        <v>4510.588819409522</v>
       </c>
       <c r="D38">
-        <v>6656.130258459076</v>
+        <v>6708.724819409523</v>
       </c>
       <c r="E38">
         <v>1444.736</v>
@@ -4409,37 +4409,37 @@
         <v>560.1</v>
       </c>
       <c r="M38">
-        <v>238.7751713924126</v>
+        <v>233.6194529924126</v>
       </c>
       <c r="N38">
-        <v>321.3248286075874</v>
+        <v>326.4805470075874</v>
       </c>
       <c r="O38">
-        <v>70.69146229366923</v>
+        <v>71.82572034166922</v>
       </c>
       <c r="P38">
-        <v>250.6333663139181</v>
+        <v>254.6548266659182</v>
       </c>
       <c r="Q38">
-        <v>952.5333663139181</v>
+        <v>956.5548266659182</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1046189780639621</v>
+        <v>0.1046100652070365</v>
       </c>
       <c r="T38">
         <v>0.7664922987152584</v>
       </c>
       <c r="U38">
-        <v>0.08799410488470122</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V38">
         <v>0.22</v>
       </c>
       <c r="W38">
-        <v>0.06863540181006696</v>
+        <v>0.06715340181006696</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.345721277190539</v>
+        <v>2.39748870578081</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.09180330422979818</v>
+        <v>0.09124927363006097</v>
       </c>
       <c r="C39">
-        <v>4369.100830857868</v>
+        <v>4422.947298303839</v>
       </c>
       <c r="D39">
-        <v>6642.612830857868</v>
+        <v>6696.459298303839</v>
       </c>
       <c r="E39">
         <v>1520.112</v>
@@ -4491,37 +4491,37 @@
         <v>560.1</v>
       </c>
       <c r="M39">
-        <v>245.4078150422019</v>
+        <v>240.1088822422019</v>
       </c>
       <c r="N39">
-        <v>314.6921849577982</v>
+        <v>319.9911177577982</v>
       </c>
       <c r="O39">
-        <v>69.2322806907156</v>
+        <v>70.39804590671559</v>
       </c>
       <c r="P39">
-        <v>245.4599042670826</v>
+        <v>249.5930718510826</v>
       </c>
       <c r="Q39">
-        <v>947.3599042670826</v>
+        <v>951.4930718510825</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1054098500953546</v>
+        <v>0.105400817397359</v>
       </c>
       <c r="T39">
         <v>0.7767984505948852</v>
       </c>
       <c r="U39">
-        <v>0.08799410488470122</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V39">
         <v>0.22</v>
       </c>
       <c r="W39">
-        <v>0.06863540181006696</v>
+        <v>0.06715340181006696</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.282323404834038</v>
+        <v>2.33269171373268</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.09333479784703649</v>
+        <v>0.09137288087599449</v>
       </c>
       <c r="C40">
-        <v>4147.743655359116</v>
+        <v>4335.350545305346</v>
       </c>
       <c r="D40">
-        <v>6496.631655359117</v>
+        <v>6684.238545305346</v>
       </c>
       <c r="E40">
         <v>1595.488</v>
@@ -4573,45 +4573,45 @@
         <v>560.1</v>
       </c>
       <c r="M40">
-        <v>265.5026122919911</v>
+        <v>246.5983114919911</v>
       </c>
       <c r="N40">
-        <v>294.5973877080089</v>
+        <v>313.5016885080089</v>
       </c>
       <c r="O40">
-        <v>64.81142529576196</v>
+        <v>68.97037147176196</v>
       </c>
       <c r="P40">
-        <v>229.7859624122469</v>
+        <v>244.5313170362469</v>
       </c>
       <c r="Q40">
-        <v>931.6859624122469</v>
+        <v>946.4313170362469</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1062262341277597</v>
+        <v>0.1062170777228533</v>
       </c>
       <c r="T40">
         <v>0.787437058986758</v>
       </c>
       <c r="U40">
-        <v>0.09269410488470123</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V40">
         <v>0.22</v>
       </c>
       <c r="W40">
-        <v>0.07230140181006696</v>
+        <v>0.06715340181006696</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.109583763281472</v>
+        <v>2.271305089687083</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.09350987146427481</v>
+        <v>0.09234824812192802</v>
       </c>
       <c r="C41">
-        <v>4056.08737106253</v>
+        <v>4165.084759886851</v>
       </c>
       <c r="D41">
-        <v>6480.35137106253</v>
+        <v>6589.348759886852</v>
       </c>
       <c r="E41">
         <v>1670.864</v>
@@ -4655,37 +4655,37 @@
         <v>560.1</v>
       </c>
       <c r="M41">
-        <v>272.4895231417804</v>
+        <v>261.3187999417804</v>
       </c>
       <c r="N41">
-        <v>287.6104768582197</v>
+        <v>298.7812000582197</v>
       </c>
       <c r="O41">
-        <v>63.27430490880833</v>
+        <v>65.73186401280833</v>
       </c>
       <c r="P41">
-        <v>224.3361719494114</v>
+        <v>233.0493360454113</v>
       </c>
       <c r="Q41">
-        <v>926.2361719494113</v>
+        <v>934.9493360454113</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.107069384849752</v>
+        <v>0.1070601006819703</v>
       </c>
       <c r="T41">
         <v>0.7984244742111513</v>
       </c>
       <c r="U41">
-        <v>0.09269410488470123</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V41">
         <v>0.22</v>
       </c>
       <c r="W41">
-        <v>0.07230140181006696</v>
+        <v>0.06933740181006696</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.055491871915279</v>
+        <v>2.143358993401109</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.09368494508151311</v>
+        <v>0.09249369536786155</v>
       </c>
       <c r="C42">
-        <v>3964.512478210886</v>
+        <v>4075.789089304499</v>
       </c>
       <c r="D42">
-        <v>6464.152478210886</v>
+        <v>6575.4290893045</v>
       </c>
       <c r="E42">
         <v>1746.24</v>
@@ -4737,37 +4737,37 @@
         <v>560.1</v>
       </c>
       <c r="M42">
-        <v>279.4764339915696</v>
+        <v>268.0192819915696</v>
       </c>
       <c r="N42">
-        <v>280.6235660084304</v>
+        <v>292.0807180084304</v>
       </c>
       <c r="O42">
-        <v>61.73718452185468</v>
+        <v>64.25775796185468</v>
       </c>
       <c r="P42">
-        <v>218.8863814865757</v>
+        <v>227.8229600465757</v>
       </c>
       <c r="Q42">
-        <v>920.7863814865757</v>
+        <v>929.7229600465757</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1079406405958106</v>
+        <v>0.1079312244063913</v>
       </c>
       <c r="T42">
         <v>0.8097781366096909</v>
       </c>
       <c r="U42">
-        <v>0.09269410488470123</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V42">
         <v>0.22</v>
       </c>
       <c r="W42">
-        <v>0.07230140181006696</v>
+        <v>0.06933740181006696</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.004104575117397</v>
+        <v>2.089775018566081</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.09683415869875142</v>
+        <v>0.09263914261379508</v>
       </c>
       <c r="C43">
-        <v>3610.986956570838</v>
+        <v>3986.552103972082</v>
       </c>
       <c r="D43">
-        <v>6186.002956570838</v>
+        <v>6561.568103972083</v>
       </c>
       <c r="E43">
         <v>1821.616</v>
@@ -4819,45 +4819,45 @@
         <v>560.1</v>
       </c>
       <c r="M43">
-        <v>315.2042136413588</v>
+        <v>274.7197640413589</v>
       </c>
       <c r="N43">
-        <v>244.8957863586412</v>
+        <v>285.3802359586412</v>
       </c>
       <c r="O43">
-        <v>53.87707299890106</v>
+        <v>62.78365191090106</v>
       </c>
       <c r="P43">
-        <v>191.0187133597401</v>
+        <v>222.5965840477401</v>
       </c>
       <c r="Q43">
-        <v>892.9187133597401</v>
+        <v>924.49658404774</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1088414304349559</v>
+        <v>0.1088318777485892</v>
       </c>
       <c r="T43">
         <v>0.8215166689200455</v>
       </c>
       <c r="U43">
-        <v>0.1019941048847012</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V43">
         <v>0.22</v>
       </c>
       <c r="W43">
-        <v>0.07955540181006696</v>
+        <v>0.06933740181006696</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>1.776943250629527</v>
+        <v>2.03880489616203</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09862149231598974</v>
+        <v>0.0953398698597286</v>
       </c>
       <c r="C44">
-        <v>3388.141623108369</v>
+        <v>3664.016274008398</v>
       </c>
       <c r="D44">
-        <v>6038.533623108369</v>
+        <v>6314.408274008399</v>
       </c>
       <c r="E44">
         <v>1896.992</v>
@@ -4901,45 +4901,45 @@
         <v>560.1</v>
       </c>
       <c r="M44">
-        <v>337.771343691148</v>
+        <v>306.1134236911481</v>
       </c>
       <c r="N44">
-        <v>222.328656308852</v>
+        <v>253.986576308852</v>
       </c>
       <c r="O44">
-        <v>48.91230438794745</v>
+        <v>55.87704678794744</v>
       </c>
       <c r="P44">
-        <v>173.4163519209046</v>
+        <v>198.1095295209045</v>
       </c>
       <c r="Q44">
-        <v>875.3163519209046</v>
+        <v>900.0095295209045</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1097732819926925</v>
+        <v>0.109763588102587</v>
       </c>
       <c r="T44">
         <v>0.8336599782066192</v>
       </c>
       <c r="U44">
-        <v>0.1066941048847012</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V44">
         <v>0.22</v>
       </c>
       <c r="W44">
-        <v>0.08322140181006694</v>
+        <v>0.07542140181006696</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>1.658222375762419</v>
+        <v>1.829713944740662</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.09890576593322806</v>
+        <v>0.09554615710566211</v>
       </c>
       <c r="C45">
-        <v>3289.956401873434</v>
+        <v>3570.524920087389</v>
       </c>
       <c r="D45">
-        <v>6015.724401873435</v>
+        <v>6296.29292008739</v>
       </c>
       <c r="E45">
         <v>1972.368</v>
@@ -4983,45 +4983,45 @@
         <v>560.1</v>
       </c>
       <c r="M45">
-        <v>345.8135185409373</v>
+        <v>313.4018385409373</v>
       </c>
       <c r="N45">
-        <v>214.2864814590628</v>
+        <v>246.6981614590627</v>
       </c>
       <c r="O45">
-        <v>47.14302592099381</v>
+        <v>54.27359552099379</v>
       </c>
       <c r="P45">
-        <v>167.143455538069</v>
+        <v>192.4245659380689</v>
       </c>
       <c r="Q45">
-        <v>869.0434555380689</v>
+        <v>894.3245659380689</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1107378300963145</v>
+        <v>0.1107279900479532</v>
       </c>
       <c r="T45">
         <v>0.8462293685207919</v>
       </c>
       <c r="U45">
-        <v>0.1066941048847012</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V45">
         <v>0.22</v>
       </c>
       <c r="W45">
-        <v>0.08322140181006694</v>
+        <v>0.07542140181006696</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>1.619659064698177</v>
+        <v>1.78716245765367</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.09919003955046637</v>
+        <v>0.09709092435159565</v>
       </c>
       <c r="C46">
-        <v>3191.942845758492</v>
+        <v>3362.727447945727</v>
       </c>
       <c r="D46">
-        <v>5993.086845758493</v>
+        <v>6163.871447945728</v>
       </c>
       <c r="E46">
         <v>2047.744</v>
@@ -5065,37 +5065,37 @@
         <v>560.1</v>
       </c>
       <c r="M46">
-        <v>353.8556933907265</v>
+        <v>333.6247749907266</v>
       </c>
       <c r="N46">
-        <v>206.2443066092735</v>
+        <v>226.4752250092735</v>
       </c>
       <c r="O46">
-        <v>45.37374745404017</v>
+        <v>49.82454950204016</v>
       </c>
       <c r="P46">
-        <v>160.8705591552333</v>
+        <v>176.6506755072333</v>
       </c>
       <c r="Q46">
-        <v>862.7705591552333</v>
+        <v>878.5506755072333</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1117368263464945</v>
+        <v>0.1117268349199396</v>
       </c>
       <c r="T46">
         <v>0.8592476656318995</v>
       </c>
       <c r="U46">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V46">
         <v>0.22</v>
       </c>
       <c r="W46">
-        <v>0.08322140181006694</v>
+        <v>0.07846340181006696</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.582848631409582</v>
+        <v>1.678832155122678</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.09947431316770469</v>
+        <v>0.09732763159752916</v>
       </c>
       <c r="C47">
-        <v>3094.099024068358</v>
+        <v>3267.550854679342</v>
       </c>
       <c r="D47">
-        <v>5970.619024068358</v>
+        <v>6144.070854679342</v>
       </c>
       <c r="E47">
         <v>2123.12</v>
@@ -5147,37 +5147,37 @@
         <v>560.1</v>
       </c>
       <c r="M47">
-        <v>361.8978682405157</v>
+        <v>341.2071562405158</v>
       </c>
       <c r="N47">
-        <v>198.2021317594843</v>
+        <v>218.8928437594843</v>
       </c>
       <c r="O47">
-        <v>43.60446898708655</v>
+        <v>48.15642562708654</v>
       </c>
       <c r="P47">
-        <v>154.5976627723978</v>
+        <v>170.7364181323977</v>
       </c>
       <c r="Q47">
-        <v>856.4976627723977</v>
+        <v>872.6364181323977</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1127721497330446</v>
+        <v>0.1127620014236346</v>
       </c>
       <c r="T47">
         <v>0.8727393553652291</v>
       </c>
       <c r="U47">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V47">
         <v>0.22</v>
       </c>
       <c r="W47">
-        <v>0.08322140181006694</v>
+        <v>0.07846340181006696</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.547674217378258</v>
+        <v>1.64152477389773</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09975858678494298</v>
+        <v>0.09756433884346269</v>
       </c>
       <c r="C48">
-        <v>2996.423034952079</v>
+        <v>3172.501067456706</v>
       </c>
       <c r="D48">
-        <v>5948.319034952079</v>
+        <v>6124.397067456706</v>
       </c>
       <c r="E48">
         <v>2198.496</v>
@@ -5229,37 +5229,37 @@
         <v>560.1</v>
       </c>
       <c r="M48">
-        <v>369.940043090305</v>
+        <v>348.789537490305</v>
       </c>
       <c r="N48">
-        <v>190.159956909695</v>
+        <v>211.310462509695</v>
       </c>
       <c r="O48">
-        <v>41.83519052013291</v>
+        <v>46.48830175213291</v>
       </c>
       <c r="P48">
-        <v>148.3247663895621</v>
+        <v>164.8221607575621</v>
       </c>
       <c r="Q48">
-        <v>850.2247663895621</v>
+        <v>866.7221607575621</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1138458184302077</v>
+        <v>0.1138355074274665</v>
       </c>
       <c r="T48">
         <v>0.8867307373109041</v>
       </c>
       <c r="U48">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V48">
         <v>0.22</v>
       </c>
       <c r="W48">
-        <v>0.08322140181006694</v>
+        <v>0.07846340181006696</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.514029125696122</v>
+        <v>1.60583945272604</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1060184404021813</v>
+        <v>0.09780104608939622</v>
       </c>
       <c r="C49">
-        <v>2469.002400016753</v>
+        <v>3077.576872037809</v>
       </c>
       <c r="D49">
-        <v>5496.274400016754</v>
+        <v>6104.84887203781</v>
       </c>
       <c r="E49">
         <v>2273.872</v>
@@ -5311,45 +5311,45 @@
         <v>560.1</v>
       </c>
       <c r="M49">
-        <v>435.7277715400943</v>
+        <v>356.3719187400943</v>
       </c>
       <c r="N49">
-        <v>124.3722284599057</v>
+        <v>203.7280812599058</v>
       </c>
       <c r="O49">
-        <v>27.36189026117926</v>
+        <v>44.82017787717927</v>
       </c>
       <c r="P49">
-        <v>97.01033819872647</v>
+        <v>158.9079033827265</v>
       </c>
       <c r="Q49">
-        <v>798.9103381987264</v>
+        <v>860.8079033827264</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1149600029272638</v>
+        <v>0.1149495230918203</v>
       </c>
       <c r="T49">
         <v>0.9012500959337747</v>
       </c>
       <c r="U49">
-        <v>0.1229941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V49">
         <v>0.22</v>
       </c>
       <c r="W49">
-        <v>0.09593540181006696</v>
+        <v>0.07846340181006696</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.285435624220848</v>
+        <v>1.571672655859528</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1064298540194196</v>
+        <v>0.09803775333532974</v>
       </c>
       <c r="C50">
-        <v>2366.311084312493</v>
+        <v>2982.777069636033</v>
       </c>
       <c r="D50">
-        <v>5468.959084312493</v>
+        <v>6085.425069636033</v>
       </c>
       <c r="E50">
         <v>2349.248000000001</v>
@@ -5393,45 +5393,45 @@
         <v>560.1</v>
       </c>
       <c r="M50">
-        <v>444.9985751898835</v>
+        <v>363.9542999898835</v>
       </c>
       <c r="N50">
-        <v>115.1014248101165</v>
+        <v>196.1457000101165</v>
       </c>
       <c r="O50">
-        <v>25.32231345822563</v>
+        <v>43.15205400222563</v>
       </c>
       <c r="P50">
-        <v>89.77911135189086</v>
+        <v>152.9936460078909</v>
       </c>
       <c r="Q50">
-        <v>791.6791113518908</v>
+        <v>854.8936460078909</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1161170406742067</v>
+        <v>0.1161063855124954</v>
       </c>
       <c r="T50">
         <v>0.9163278914267554</v>
       </c>
       <c r="U50">
-        <v>0.1229941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V50">
         <v>0.22</v>
       </c>
       <c r="W50">
-        <v>0.09593540181006696</v>
+        <v>0.07846340181006696</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.258655715382913</v>
+        <v>1.538929475529122</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1198899202158497</v>
+        <v>0.09827446058126325</v>
       </c>
       <c r="C51">
-        <v>1526.073776924933</v>
+        <v>2888.100476673092</v>
       </c>
       <c r="D51">
-        <v>4704.097776924933</v>
+        <v>6066.124476673092</v>
       </c>
       <c r="E51">
         <v>2424.624</v>
@@ -5475,45 +5475,45 @@
         <v>560.1</v>
       </c>
       <c r="M51">
-        <v>575.0443436396728</v>
+        <v>371.5366812396727</v>
       </c>
       <c r="N51">
-        <v>-14.94434363967275</v>
+        <v>188.5633187603273</v>
       </c>
       <c r="O51">
-        <v>-3.287755600728005</v>
+        <v>41.48393012727201</v>
       </c>
       <c r="P51">
-        <v>-11.65658803894475</v>
+        <v>147.0793886330553</v>
       </c>
       <c r="Q51">
-        <v>690.2434119610552</v>
+        <v>848.9793886330554</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1175440247739218</v>
+        <v>0.1173086150869224</v>
       </c>
       <c r="T51">
-        <v>0.9349234597079891</v>
+        <v>0.9319969730175003</v>
       </c>
       <c r="U51">
-        <v>0.1556941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V51">
-        <v>0.2142826050945592</v>
+        <v>0.22</v>
       </c>
       <c r="W51">
-        <v>0.1223315664921419</v>
+        <v>0.07846340181006696</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.9740118413389055</v>
+        <v>1.507522751538731</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1209888612646967</v>
+        <v>0.1040491678271968</v>
       </c>
       <c r="C52">
-        <v>1397.59090667813</v>
+        <v>2377.069422753841</v>
       </c>
       <c r="D52">
-        <v>4650.99090667813</v>
+        <v>5630.469422753841</v>
       </c>
       <c r="E52">
         <v>2500</v>
@@ -5557,45 +5557,45 @@
         <v>560.1</v>
       </c>
       <c r="M52">
-        <v>586.779942489462</v>
+        <v>432.6360224894621</v>
       </c>
       <c r="N52">
-        <v>-26.67994248946195</v>
+        <v>127.463977510538</v>
       </c>
       <c r="O52">
-        <v>-5.869587347681629</v>
+        <v>28.04207505231835</v>
       </c>
       <c r="P52">
-        <v>-20.81035514178032</v>
+        <v>99.42190245821962</v>
       </c>
       <c r="Q52">
-        <v>681.0896448582197</v>
+        <v>801.3219024582196</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1189789052694002</v>
+        <v>0.1185589338443266</v>
       </c>
       <c r="T52">
-        <v>0.9536219289021487</v>
+        <v>0.9482928178718749</v>
       </c>
       <c r="U52">
-        <v>0.1556941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V52">
-        <v>0.209996952992668</v>
+        <v>0.22</v>
       </c>
       <c r="W52">
-        <v>0.1229988172599931</v>
+        <v>0.08953940181006696</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.9545316045121275</v>
+        <v>1.294621739486898</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1220878023135437</v>
+        <v>0.1043966350731303</v>
       </c>
       <c r="C53">
-        <v>1270.293749418925</v>
+        <v>2277.467113014833</v>
       </c>
       <c r="D53">
-        <v>4599.069749418926</v>
+        <v>5606.243113014833</v>
       </c>
       <c r="E53">
         <v>2575.376</v>
@@ -5639,45 +5639,45 @@
         <v>560.1</v>
       </c>
       <c r="M53">
-        <v>598.5155413392513</v>
+        <v>441.2887429392513</v>
       </c>
       <c r="N53">
-        <v>-38.41554133925126</v>
+        <v>118.8112570607487</v>
       </c>
       <c r="O53">
-        <v>-8.451419094635279</v>
+        <v>26.13847655336473</v>
       </c>
       <c r="P53">
-        <v>-29.96412224461599</v>
+        <v>92.67278050738402</v>
       </c>
       <c r="Q53">
-        <v>671.935877755384</v>
+        <v>794.572780507384</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1204723523157145</v>
+        <v>0.1198602860204003</v>
       </c>
       <c r="T53">
-        <v>0.97308360092056</v>
+        <v>0.9652537992509179</v>
       </c>
       <c r="U53">
-        <v>0.1556941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V53">
-        <v>0.2058793656790863</v>
+        <v>0.22</v>
       </c>
       <c r="W53">
-        <v>0.1236399013310658</v>
+        <v>0.08953940181006696</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.9358152985413013</v>
+        <v>1.269236999496959</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1231867433623907</v>
+        <v>0.1164170503665526</v>
       </c>
       <c r="C54">
-        <v>1144.143033570694</v>
+        <v>1475.722725858248</v>
       </c>
       <c r="D54">
-        <v>4548.295033570695</v>
+        <v>4879.874725858249</v>
       </c>
       <c r="E54">
         <v>2650.752</v>
@@ -5721,37 +5721,37 @@
         <v>560.1</v>
       </c>
       <c r="M54">
-        <v>610.2511401890405</v>
+        <v>562.0406505890405</v>
       </c>
       <c r="N54">
-        <v>-50.15114018904046</v>
+        <v>-1.940650589040501</v>
       </c>
       <c r="O54">
-        <v>-11.0332508415889</v>
+        <v>-0.4269431295889103</v>
       </c>
       <c r="P54">
-        <v>-39.11788934745156</v>
+        <v>-1.513707459451591</v>
       </c>
       <c r="Q54">
-        <v>662.7821106525485</v>
+        <v>700.3862925405484</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.122028026322292</v>
+        <v>0.1212494992476293</v>
       </c>
       <c r="T54">
-        <v>0.9933561759397385</v>
+        <v>0.9833599046632436</v>
       </c>
       <c r="U54">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V54">
-        <v>0.2019201471083346</v>
+        <v>0.2192403696616224</v>
       </c>
       <c r="W54">
-        <v>0.1242563283224819</v>
+        <v>0.1119563283224819</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9178188504924302</v>
+        <v>0.9965471348255565</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1242856844112377</v>
+        <v>0.1173929914153996</v>
       </c>
       <c r="C55">
-        <v>1019.10120288571</v>
+        <v>1349.547960463706</v>
       </c>
       <c r="D55">
-        <v>4498.629202885711</v>
+        <v>4829.075960463707</v>
       </c>
       <c r="E55">
         <v>2726.128000000001</v>
@@ -5803,37 +5803,37 @@
         <v>560.1</v>
       </c>
       <c r="M55">
-        <v>621.9867390388298</v>
+        <v>572.8491246388297</v>
       </c>
       <c r="N55">
-        <v>-61.88673903882977</v>
+        <v>-12.7491246388297</v>
       </c>
       <c r="O55">
-        <v>-13.61508258854255</v>
+        <v>-2.804807420542534</v>
       </c>
       <c r="P55">
-        <v>-48.27165645028722</v>
+        <v>-9.944317218287164</v>
       </c>
       <c r="Q55">
-        <v>653.6283435497128</v>
+        <v>691.9556827817128</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1236498992227663</v>
+        <v>0.1228548077422597</v>
       </c>
       <c r="T55">
-        <v>1.01449141372569</v>
+        <v>1.004282455826291</v>
       </c>
       <c r="U55">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V55">
-        <v>0.1981103330119509</v>
+        <v>0.2151037589132899</v>
       </c>
       <c r="W55">
-        <v>0.1248494939179954</v>
+        <v>0.1125494939179954</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.9005015136906862</v>
+        <v>0.9777443586967725</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1253846254600847</v>
+        <v>0.1183689324642467</v>
       </c>
       <c r="C56">
-        <v>895.1323238027321</v>
+        <v>1224.419913968799</v>
       </c>
       <c r="D56">
-        <v>4450.036323802733</v>
+        <v>4779.3239139688</v>
       </c>
       <c r="E56">
         <v>2801.504000000001</v>
@@ -5885,37 +5885,37 @@
         <v>560.1</v>
       </c>
       <c r="M56">
-        <v>633.722337888619</v>
+        <v>583.657598688619</v>
       </c>
       <c r="N56">
-        <v>-73.62233788861897</v>
+        <v>-23.55759868861901</v>
       </c>
       <c r="O56">
-        <v>-16.19691433549617</v>
+        <v>-5.182671711496182</v>
       </c>
       <c r="P56">
-        <v>-57.4254235531228</v>
+        <v>-18.37492697712283</v>
       </c>
       <c r="Q56">
-        <v>644.4745764468772</v>
+        <v>683.5250730228771</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1253422883363046</v>
+        <v>0.1245299122583958</v>
       </c>
       <c r="T56">
-        <v>1.03654557489364</v>
+        <v>1.026114683126863</v>
       </c>
       <c r="U56">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V56">
-        <v>0.1944416231413593</v>
+        <v>0.2111203559704512</v>
       </c>
       <c r="W56">
-        <v>0.1254206904173789</v>
+        <v>0.1131206904173789</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8838255597334512</v>
+        <v>0.9596379816838692</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1264835665089317</v>
+        <v>0.1193448735130937</v>
       </c>
       <c r="C57">
-        <v>772.2019987446092</v>
+        <v>1100.306564498219</v>
       </c>
       <c r="D57">
-        <v>4402.48199874461</v>
+        <v>4730.58656449822</v>
       </c>
       <c r="E57">
         <v>2876.88</v>
@@ -5967,37 +5967,37 @@
         <v>560.1</v>
       </c>
       <c r="M57">
-        <v>645.4579367384082</v>
+        <v>594.4660727384082</v>
       </c>
       <c r="N57">
-        <v>-85.35793673840817</v>
+        <v>-34.36607273840821</v>
       </c>
       <c r="O57">
-        <v>-18.7787460824498</v>
+        <v>-7.560536002449806</v>
       </c>
       <c r="P57">
-        <v>-66.57919065595837</v>
+        <v>-26.8055367359584</v>
       </c>
       <c r="Q57">
-        <v>635.3208093440417</v>
+        <v>675.0944632640416</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1271098947437781</v>
+        <v>0.1262794658641379</v>
       </c>
       <c r="T57">
-        <v>1.059579921002388</v>
+        <v>1.048917231640793</v>
       </c>
       <c r="U57">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V57">
-        <v>0.1909063209024255</v>
+        <v>0.2072818040437157</v>
       </c>
       <c r="W57">
-        <v>0.1259711161349666</v>
+        <v>0.1136711161349666</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8677560041019341</v>
+        <v>0.9421900183805261</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1275825075577788</v>
+        <v>0.1203208145619407</v>
       </c>
       <c r="C58">
-        <v>650.2772849162711</v>
+        <v>977.1771831688056</v>
       </c>
       <c r="D58">
-        <v>4355.933284916272</v>
+        <v>4682.833183168806</v>
       </c>
       <c r="E58">
         <v>2952.256</v>
@@ -6049,37 +6049,37 @@
         <v>560.1</v>
       </c>
       <c r="M58">
-        <v>657.1935355881975</v>
+        <v>605.2745467881974</v>
       </c>
       <c r="N58">
-        <v>-97.09353558819748</v>
+        <v>-45.1745467881974</v>
       </c>
       <c r="O58">
-        <v>-21.36057782940345</v>
+        <v>-9.938400293403429</v>
       </c>
       <c r="P58">
-        <v>-75.73295775879404</v>
+        <v>-35.23614649479397</v>
       </c>
       <c r="Q58">
-        <v>626.167042241206</v>
+        <v>666.663853505206</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1289578468970458</v>
+        <v>0.1281085446337774</v>
       </c>
       <c r="T58">
-        <v>1.083661282843351</v>
+        <v>1.072756259632629</v>
       </c>
       <c r="U58">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V58">
-        <v>0.1874972794577393</v>
+        <v>0.2035803432572208</v>
       </c>
       <c r="W58">
-        <v>0.1265018837912118</v>
+        <v>0.1142018837912118</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8522603611715422</v>
+        <v>0.9253651966237311</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1286814486066258</v>
+        <v>0.1212967556107877</v>
       </c>
       <c r="C59">
-        <v>529.326618200239</v>
+        <v>855.0022694805593</v>
       </c>
       <c r="D59">
-        <v>4310.35861820024</v>
+        <v>4636.03426948056</v>
       </c>
       <c r="E59">
         <v>3027.632000000001</v>
@@ -6131,37 +6131,37 @@
         <v>560.1</v>
       </c>
       <c r="M59">
-        <v>668.9291344379868</v>
+        <v>616.0830208379867</v>
       </c>
       <c r="N59">
-        <v>-108.8291344379868</v>
+        <v>-55.98302083798671</v>
       </c>
       <c r="O59">
-        <v>-23.9424095763571</v>
+        <v>-12.31626458435708</v>
       </c>
       <c r="P59">
-        <v>-84.8867248616297</v>
+        <v>-43.66675625362964</v>
       </c>
       <c r="Q59">
-        <v>617.0132751383703</v>
+        <v>658.2332437463704</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1308917503132561</v>
+        <v>0.1300226968345629</v>
       </c>
       <c r="T59">
-        <v>1.108862708025755</v>
+        <v>1.097704079624086</v>
       </c>
       <c r="U59">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V59">
-        <v>0.1842078535023403</v>
+        <v>0.2000087582877959</v>
       </c>
       <c r="W59">
-        <v>0.1270140280209222</v>
+        <v>0.1147140280209222</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.837308425010638</v>
+        <v>0.9091307194899813</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1297803896554728</v>
+        <v>0.1222726966596347</v>
       </c>
       <c r="C60">
-        <v>409.3197417802176</v>
+        <v>733.7534905434104</v>
       </c>
       <c r="D60">
-        <v>4265.727741780218</v>
+        <v>4590.161490543411</v>
       </c>
       <c r="E60">
         <v>3103.008</v>
@@ -6213,37 +6213,37 @@
         <v>560.1</v>
       </c>
       <c r="M60">
-        <v>680.6647332877759</v>
+        <v>626.8914948877759</v>
       </c>
       <c r="N60">
-        <v>-120.5647332877759</v>
+        <v>-66.79149488777591</v>
       </c>
       <c r="O60">
-        <v>-26.52424132331069</v>
+        <v>-14.6941288753107</v>
       </c>
       <c r="P60">
-        <v>-94.04049196446519</v>
+        <v>-52.09736601246521</v>
       </c>
       <c r="Q60">
-        <v>607.8595080355348</v>
+        <v>649.8026339875348</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1329177443683336</v>
+        <v>0.1320279991401477</v>
       </c>
       <c r="T60">
-        <v>1.135264201073987</v>
+        <v>1.123839891043707</v>
       </c>
       <c r="U60">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V60">
-        <v>0.1810318560281621</v>
+        <v>0.196560331420765</v>
       </c>
       <c r="W60">
-        <v>0.1275085121047804</v>
+        <v>0.1152085121047804</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8228720728552823</v>
+        <v>0.8934560519125678</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1308793307043198</v>
+        <v>0.1232486377084817</v>
       </c>
       <c r="C61">
-        <v>290.2276391535552</v>
+        <v>613.4036238766903</v>
       </c>
       <c r="D61">
-        <v>4222.011639153556</v>
+        <v>4545.187623876691</v>
       </c>
       <c r="E61">
         <v>3178.384</v>
@@ -6295,37 +6295,37 @@
         <v>560.1</v>
       </c>
       <c r="M61">
-        <v>692.4003321375652</v>
+        <v>637.6999689375651</v>
       </c>
       <c r="N61">
-        <v>-132.3003321375652</v>
+        <v>-77.59996893756511</v>
       </c>
       <c r="O61">
-        <v>-29.10607307026434</v>
+        <v>-17.07199316626432</v>
       </c>
       <c r="P61">
-        <v>-103.1942590673008</v>
+        <v>-60.52797577130079</v>
       </c>
       <c r="Q61">
-        <v>598.7057409326991</v>
+        <v>641.3720242286992</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1350425674017076</v>
+        <v>0.1341311210703952</v>
       </c>
       <c r="T61">
-        <v>1.162953571831889</v>
+        <v>1.151250620093553</v>
       </c>
       <c r="U61">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V61">
-        <v>0.1779635194853119</v>
+        <v>0.1932288003797351</v>
       </c>
       <c r="W61">
-        <v>0.1279862340163045</v>
+        <v>0.1156862340163045</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8089250885695994</v>
+        <v>0.8783127289987956</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1523433391837479</v>
+        <v>0.1242245787573287</v>
       </c>
       <c r="C62">
-        <v>-489.2960769442516</v>
+        <v>493.9265035386443</v>
       </c>
       <c r="D62">
-        <v>3517.863923055749</v>
+        <v>4501.086503538645</v>
       </c>
       <c r="E62">
         <v>3253.76</v>
@@ -6377,45 +6377,45 @@
         <v>560.1</v>
       </c>
       <c r="M62">
-        <v>852.0236429873545</v>
+        <v>648.5084429873544</v>
       </c>
       <c r="N62">
-        <v>-291.9236429873545</v>
+        <v>-88.40844298735442</v>
       </c>
       <c r="O62">
-        <v>-64.22320145721798</v>
+        <v>-19.44985745721797</v>
       </c>
       <c r="P62">
-        <v>-227.7004415301365</v>
+        <v>-68.95858553013645</v>
       </c>
       <c r="Q62">
-        <v>474.1995584698635</v>
+        <v>632.9414144698635</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1391363001632031</v>
+        <v>0.1363393990971551</v>
       </c>
       <c r="T62">
-        <v>1.216300548232472</v>
+        <v>1.180031885595892</v>
       </c>
       <c r="U62">
-        <v>0.1883941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V62">
-        <v>0.1446227472842896</v>
+        <v>0.1900083203734061</v>
       </c>
       <c r="W62">
-        <v>0.1611480318641111</v>
+        <v>0.1161480318641111</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.6573761240194984</v>
+        <v>0.8636741835154822</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1863809519298397</v>
+        <v>0.1252005198061757</v>
       </c>
       <c r="C63">
-        <v>-1300.471985067255</v>
+        <v>375.2969693619716</v>
       </c>
       <c r="D63">
-        <v>2782.064014932745</v>
+        <v>4457.832969361972</v>
       </c>
       <c r="E63">
         <v>3329.136</v>
@@ -6459,45 +6459,45 @@
         <v>560.1</v>
       </c>
       <c r="M63">
-        <v>1106.236296237144</v>
+        <v>659.3169170371435</v>
       </c>
       <c r="N63">
-        <v>-546.1362962371435</v>
+        <v>-99.2169170371435</v>
       </c>
       <c r="O63">
-        <v>-120.1499851721716</v>
+        <v>-21.82772174817157</v>
       </c>
       <c r="P63">
-        <v>-425.9863110649719</v>
+        <v>-77.38919528897193</v>
       </c>
       <c r="Q63">
-        <v>275.9136889350281</v>
+        <v>624.5108047110281</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1435030558013489</v>
+        <v>0.1386609221509283</v>
       </c>
       <c r="T63">
-        <v>1.273205388764901</v>
+        <v>1.210289113431684</v>
       </c>
       <c r="U63">
-        <v>0.2405941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V63">
-        <v>0.1113884984782536</v>
+        <v>0.1868934298754815</v>
       </c>
       <c r="W63">
-        <v>0.2137946887988749</v>
+        <v>0.1165946887988749</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.5063113567193347</v>
+        <v>0.8495155903430975</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1883288929786868</v>
+        <v>0.1261764608550227</v>
       </c>
       <c r="C64">
-        <v>-1408.755633736741</v>
+        <v>257.4908190884598</v>
       </c>
       <c r="D64">
-        <v>2749.156366263258</v>
+        <v>4415.40281908846</v>
       </c>
       <c r="E64">
         <v>3404.512</v>
@@ -6541,45 +6541,45 @@
         <v>560.1</v>
       </c>
       <c r="M64">
-        <v>1124.371317486933</v>
+        <v>670.1253910869328</v>
       </c>
       <c r="N64">
-        <v>-564.2713174869328</v>
+        <v>-110.0253910869328</v>
       </c>
       <c r="O64">
-        <v>-124.1396898471252</v>
+        <v>-24.20558603912522</v>
       </c>
       <c r="P64">
-        <v>-440.1316276398076</v>
+        <v>-85.81980504780759</v>
       </c>
       <c r="Q64">
-        <v>261.7683723601924</v>
+        <v>616.0801949521924</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1460741888487528</v>
+        <v>0.1411046306285843</v>
       </c>
       <c r="T64">
-        <v>1.306710793732398</v>
+        <v>1.242138826943044</v>
       </c>
       <c r="U64">
-        <v>0.2405941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V64">
-        <v>0.1095919097931205</v>
+        <v>0.1838790197161995</v>
       </c>
       <c r="W64">
-        <v>0.2142269374454205</v>
+        <v>0.1170269374454205</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.4981450445141842</v>
+        <v>0.8358137259827249</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1902768340275338</v>
+        <v>0.1271524019038698</v>
       </c>
       <c r="C65">
-        <v>-1516.269886852476</v>
+        <v>140.4847632113733</v>
       </c>
       <c r="D65">
-        <v>2717.018113147524</v>
+        <v>4373.772763211374</v>
       </c>
       <c r="E65">
         <v>3479.888</v>
@@ -6623,45 +6623,45 @@
         <v>560.1</v>
       </c>
       <c r="M65">
-        <v>1142.506338736722</v>
+        <v>680.9338651367221</v>
       </c>
       <c r="N65">
-        <v>-582.4063387367222</v>
+        <v>-120.8338651367221</v>
       </c>
       <c r="O65">
-        <v>-128.1293945220789</v>
+        <v>-26.58345033007887</v>
       </c>
       <c r="P65">
-        <v>-454.2769442146433</v>
+        <v>-94.25041480664325</v>
       </c>
       <c r="Q65">
-        <v>247.6230557853567</v>
+        <v>607.6495851933568</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1487843020608813</v>
+        <v>0.1436804314563839</v>
       </c>
       <c r="T65">
-        <v>1.342027301671112</v>
+        <v>1.275710146590154</v>
       </c>
       <c r="U65">
-        <v>0.2405941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V65">
-        <v>0.1078523556694202</v>
+        <v>0.1809603051175296</v>
       </c>
       <c r="W65">
-        <v>0.2146454639127106</v>
+        <v>0.1174454639127107</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.4902379803155462</v>
+        <v>0.8225468414433165</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1922247750763808</v>
+        <v>0.1281283429527168</v>
       </c>
       <c r="C66">
-        <v>-1623.041415838136</v>
+        <v>24.2563823485616</v>
       </c>
       <c r="D66">
-        <v>2685.622584161864</v>
+        <v>4332.920382348562</v>
       </c>
       <c r="E66">
         <v>3555.264</v>
@@ -6705,45 +6705,45 @@
         <v>560.1</v>
       </c>
       <c r="M66">
-        <v>1160.641359986511</v>
+        <v>691.7423391865113</v>
       </c>
       <c r="N66">
-        <v>-600.5413599865113</v>
+        <v>-131.6423391865113</v>
       </c>
       <c r="O66">
-        <v>-132.1190991970325</v>
+        <v>-28.96131462103249</v>
       </c>
       <c r="P66">
-        <v>-468.4222607894789</v>
+        <v>-102.6810245654788</v>
       </c>
       <c r="Q66">
-        <v>233.4777392105211</v>
+        <v>599.2189754345211</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.151644977118128</v>
+        <v>0.1463993323301724</v>
       </c>
       <c r="T66">
-        <v>1.379305837828642</v>
+        <v>1.311146539550991</v>
       </c>
       <c r="U66">
-        <v>0.2405941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V66">
-        <v>0.1061671626120855</v>
+        <v>0.1781328003500682</v>
       </c>
       <c r="W66">
-        <v>0.215050911427898</v>
+        <v>0.117850911427898</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.4825780118731159</v>
+        <v>0.8096945470457647</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1941727161252278</v>
+        <v>0.1482001220484656</v>
       </c>
       <c r="C67">
-        <v>-1729.09567343118</v>
+        <v>-749.3393098757106</v>
       </c>
       <c r="D67">
-        <v>2654.94432656882</v>
+        <v>3634.70069012429</v>
       </c>
       <c r="E67">
         <v>3630.64</v>
@@ -6787,45 +6787,45 @@
         <v>560.1</v>
       </c>
       <c r="M67">
-        <v>1178.776381236301</v>
+        <v>840.7150212363007</v>
       </c>
       <c r="N67">
-        <v>-618.6763812363007</v>
+        <v>-280.6150212363007</v>
       </c>
       <c r="O67">
-        <v>-136.1088038719862</v>
+        <v>-61.73530467198615</v>
       </c>
       <c r="P67">
-        <v>-482.5675773643145</v>
+        <v>-218.8797165643145</v>
       </c>
       <c r="Q67">
-        <v>219.3324226356855</v>
+        <v>483.0202834356854</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1546691193215031</v>
+        <v>0.1514617076736111</v>
       </c>
       <c r="T67">
-        <v>1.418714576052318</v>
+        <v>1.377126260884264</v>
       </c>
       <c r="U67">
-        <v>0.2405941048847012</v>
+        <v>0.1715941048847012</v>
       </c>
       <c r="V67">
-        <v>0.1045338216488226</v>
+        <v>0.1465680960699355</v>
       </c>
       <c r="W67">
-        <v>0.2154438836349258</v>
+        <v>0.1464438836349257</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.4751537347673755</v>
+        <v>0.666218618499707</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1961206571740748</v>
+        <v>0.1494580630973126</v>
       </c>
       <c r="C68">
-        <v>-1834.456962502859</v>
+        <v>-861.0557717601796</v>
       </c>
       <c r="D68">
-        <v>2624.959037497141</v>
+        <v>3598.360228239821</v>
       </c>
       <c r="E68">
         <v>3706.016000000001</v>
@@ -6869,45 +6869,45 @@
         <v>560.1</v>
       </c>
       <c r="M68">
-        <v>1196.91140248609</v>
+        <v>853.6490984860899</v>
       </c>
       <c r="N68">
-        <v>-636.8114024860901</v>
+        <v>-293.5490984860899</v>
       </c>
       <c r="O68">
-        <v>-140.0985085469398</v>
+        <v>-64.58080166693976</v>
       </c>
       <c r="P68">
-        <v>-496.7128939391503</v>
+        <v>-228.9682968191501</v>
       </c>
       <c r="Q68">
-        <v>205.1871060608497</v>
+        <v>472.9317031808499</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1578711522427237</v>
+        <v>0.1545694049581291</v>
       </c>
       <c r="T68">
-        <v>1.460441475347975</v>
+        <v>1.417629974439683</v>
       </c>
       <c r="U68">
-        <v>0.2405941048847012</v>
+        <v>0.1715941048847012</v>
       </c>
       <c r="V68">
-        <v>0.1029499758662647</v>
+        <v>0.1443473673416032</v>
       </c>
       <c r="W68">
-        <v>0.2158249475932557</v>
+        <v>0.1468249475932557</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.4679544357557486</v>
+        <v>0.6561243970072872</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1980685982229218</v>
+        <v>0.1878281527221357</v>
       </c>
       <c r="C69">
-        <v>-1939.14850026674</v>
+        <v>-1777.360287939618</v>
       </c>
       <c r="D69">
-        <v>2595.643499733261</v>
+        <v>2757.431712060383</v>
       </c>
       <c r="E69">
         <v>3781.392000000001</v>
@@ -6951,37 +6951,37 @@
         <v>560.1</v>
       </c>
       <c r="M69">
-        <v>1215.046423735879</v>
+        <v>1139.293543735879</v>
       </c>
       <c r="N69">
-        <v>-654.9464237358792</v>
+        <v>-579.1935437358792</v>
       </c>
       <c r="O69">
-        <v>-144.0882132218934</v>
+        <v>-127.4225796218934</v>
       </c>
       <c r="P69">
-        <v>-510.8582105139858</v>
+        <v>-451.7709641139858</v>
       </c>
       <c r="Q69">
-        <v>191.0417894860142</v>
+        <v>250.1290358860142</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1612672477652305</v>
+        <v>0.1606901401870907</v>
       </c>
       <c r="T69">
-        <v>1.504697277631247</v>
+        <v>1.497403673022709</v>
       </c>
       <c r="U69">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V69">
-        <v>0.1014134090622906</v>
+        <v>0.108156498101394</v>
       </c>
       <c r="W69">
-        <v>0.2161946365080534</v>
+        <v>0.2011946365080534</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4609700411922301</v>
+        <v>0.4916204459154271</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2000165392717689</v>
+        <v>0.1896260937709827</v>
       </c>
       <c r="C70">
-        <v>-2043.19247823225</v>
+        <v>-1882.604685050287</v>
       </c>
       <c r="D70">
-        <v>2566.97552176775</v>
+        <v>2727.563314949713</v>
       </c>
       <c r="E70">
         <v>3856.768</v>
@@ -7033,37 +7033,37 @@
         <v>560.1</v>
       </c>
       <c r="M70">
-        <v>1233.181444985668</v>
+        <v>1156.297924985668</v>
       </c>
       <c r="N70">
-        <v>-673.0814449856683</v>
+        <v>-596.1979249856682</v>
       </c>
       <c r="O70">
-        <v>-148.077917896847</v>
+        <v>-131.163543496847</v>
       </c>
       <c r="P70">
-        <v>-525.0035270888213</v>
+        <v>-465.0343814888212</v>
       </c>
       <c r="Q70">
-        <v>176.8964729111786</v>
+        <v>236.8656185111788</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.164875599257894</v>
+        <v>0.1642804570679373</v>
       </c>
       <c r="T70">
-        <v>1.551719067557223</v>
+        <v>1.544197537804669</v>
       </c>
       <c r="U70">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V70">
-        <v>0.09992203539960987</v>
+        <v>0.1065659613646088</v>
       </c>
       <c r="W70">
-        <v>0.2165534522194747</v>
+        <v>0.2015534522194747</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4541910699982267</v>
+        <v>0.4843907334754943</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2019644803206159</v>
+        <v>0.1914240348198297</v>
       </c>
       <c r="C71">
-        <v>-2146.610118228649</v>
+        <v>-1987.208949336346</v>
       </c>
       <c r="D71">
-        <v>2538.933881771351</v>
+        <v>2698.335050663654</v>
       </c>
       <c r="E71">
         <v>3932.144</v>
@@ -7115,37 +7115,37 @@
         <v>560.1</v>
       </c>
       <c r="M71">
-        <v>1251.316466235458</v>
+        <v>1173.302306235458</v>
       </c>
       <c r="N71">
-        <v>-691.2164662354577</v>
+        <v>-613.2023062354575</v>
       </c>
       <c r="O71">
-        <v>-152.0676225718007</v>
+        <v>-134.9045073718007</v>
       </c>
       <c r="P71">
-        <v>-539.148843663657</v>
+        <v>-478.2977988636569</v>
       </c>
       <c r="Q71">
-        <v>162.751156336343</v>
+        <v>223.6022011363431</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1687167476210518</v>
+        <v>0.1681024072959353</v>
       </c>
       <c r="T71">
-        <v>1.601774521349392</v>
+        <v>1.594010361604819</v>
       </c>
       <c r="U71">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V71">
-        <v>0.0984738899590358</v>
+        <v>0.1050215271419333</v>
       </c>
       <c r="W71">
-        <v>0.2169018674754924</v>
+        <v>0.2019018674754924</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4476085907228901</v>
+        <v>0.4773705779178785</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2039124213694629</v>
+        <v>0.1932219758686767</v>
       </c>
       <c r="C72">
-        <v>-2249.421724796618</v>
+        <v>-2091.193441391809</v>
       </c>
       <c r="D72">
-        <v>2511.498275203382</v>
+        <v>2669.726558608191</v>
       </c>
       <c r="E72">
         <v>4007.52</v>
@@ -7197,37 +7197,37 @@
         <v>560.1</v>
       </c>
       <c r="M72">
-        <v>1269.451487485247</v>
+        <v>1190.306687485247</v>
       </c>
       <c r="N72">
-        <v>-709.3514874852468</v>
+        <v>-630.2066874852468</v>
       </c>
       <c r="O72">
-        <v>-156.0573272467543</v>
+        <v>-138.6454712467543</v>
       </c>
       <c r="P72">
-        <v>-553.2941602384925</v>
+        <v>-491.5612162384925</v>
       </c>
       <c r="Q72">
-        <v>148.6058397615075</v>
+        <v>210.3387837615074</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1728139725417536</v>
+        <v>0.1721791542057998</v>
       </c>
       <c r="T72">
-        <v>1.655167005394371</v>
+        <v>1.64714404032498</v>
       </c>
       <c r="U72">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V72">
-        <v>0.09706712010247816</v>
+        <v>0.1035212196113342</v>
       </c>
       <c r="W72">
-        <v>0.2172403280099097</v>
+        <v>0.2022403280099097</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4412141822839917</v>
+        <v>0.4705509982333373</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2058603624183099</v>
+        <v>0.1950199169175237</v>
       </c>
       <c r="C73">
-        <v>-2351.646734219342</v>
+        <v>-2194.577667394919</v>
       </c>
       <c r="D73">
-        <v>2484.649265780658</v>
+        <v>2641.718332605081</v>
       </c>
       <c r="E73">
         <v>4082.896</v>
@@ -7279,37 +7279,37 @@
         <v>560.1</v>
       </c>
       <c r="M73">
-        <v>1287.586508735036</v>
+        <v>1207.311068735036</v>
       </c>
       <c r="N73">
-        <v>-727.486508735036</v>
+        <v>-647.2110687350358</v>
       </c>
       <c r="O73">
-        <v>-160.0470319217079</v>
+        <v>-142.3864351217079</v>
       </c>
       <c r="P73">
-        <v>-567.439476813328</v>
+        <v>-504.8246336133279</v>
       </c>
       <c r="Q73">
-        <v>134.4605231866719</v>
+        <v>197.075366386672</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1771937646983658</v>
+        <v>0.1765370560749653</v>
       </c>
       <c r="T73">
-        <v>1.712241729718315</v>
+        <v>1.703942110681013</v>
       </c>
       <c r="U73">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V73">
-        <v>0.09569997756582355</v>
+        <v>0.1020631742646957</v>
       </c>
       <c r="W73">
-        <v>0.2175692544447659</v>
+        <v>0.2025692544447659</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4349998980264707</v>
+        <v>0.4639235193849806</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2078083034671569</v>
+        <v>0.1968178579663707</v>
       </c>
       <c r="C74">
-        <v>-2453.303760441858</v>
+        <v>-2297.380323461418</v>
       </c>
       <c r="D74">
-        <v>2458.368239558142</v>
+        <v>2614.291676538582</v>
       </c>
       <c r="E74">
         <v>4158.272</v>
@@ -7361,37 +7361,37 @@
         <v>560.1</v>
       </c>
       <c r="M74">
-        <v>1305.721529984825</v>
+        <v>1224.315449984825</v>
       </c>
       <c r="N74">
-        <v>-745.6215299848253</v>
+        <v>-664.2154499848251</v>
       </c>
       <c r="O74">
-        <v>-164.0367365966616</v>
+        <v>-146.1273989966615</v>
       </c>
       <c r="P74">
-        <v>-581.5847933881637</v>
+        <v>-518.0880509881636</v>
       </c>
       <c r="Q74">
-        <v>120.3152066118363</v>
+        <v>183.8119490118364</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1818863991518788</v>
+        <v>0.1812062366490712</v>
       </c>
       <c r="T74">
-        <v>1.773393220065397</v>
+        <v>1.764797186062478</v>
       </c>
       <c r="U74">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V74">
-        <v>0.09437081121074264</v>
+        <v>0.1006456301776861</v>
       </c>
       <c r="W74">
-        <v>0.2178890440342095</v>
+        <v>0.2028890440342095</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.428958232776103</v>
+        <v>0.4574801371713003</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2097562445160039</v>
+        <v>0.1986157990152178</v>
       </c>
       <c r="C75">
-        <v>-2554.410638106679</v>
+        <v>-2399.61933726331</v>
       </c>
       <c r="D75">
-        <v>2432.637361893322</v>
+        <v>2587.42866273669</v>
       </c>
       <c r="E75">
         <v>4233.648</v>
@@ -7443,37 +7443,37 @@
         <v>560.1</v>
       </c>
       <c r="M75">
-        <v>1323.856551234615</v>
+        <v>1241.319831234614</v>
       </c>
       <c r="N75">
-        <v>-763.7565512346147</v>
+        <v>-681.2198312346144</v>
       </c>
       <c r="O75">
-        <v>-168.0264412716152</v>
+        <v>-149.8683628716152</v>
       </c>
       <c r="P75">
-        <v>-595.7301099629994</v>
+        <v>-531.3514683629992</v>
       </c>
       <c r="Q75">
-        <v>106.1698900370005</v>
+        <v>170.5485316370008</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.186926636157504</v>
+        <v>0.1862212824508886</v>
       </c>
       <c r="T75">
-        <v>1.83907445043819</v>
+        <v>1.830160044805533</v>
       </c>
       <c r="U75">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V75">
-        <v>0.09307806037223931</v>
+        <v>0.09926692291497803</v>
       </c>
       <c r="W75">
-        <v>0.2182000722650381</v>
+        <v>0.2032000722650381</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4230820926010879</v>
+        <v>0.4512132859771728</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2117041855648509</v>
+        <v>0.2004137400640648</v>
       </c>
       <c r="C76">
-        <v>-2654.984462914783</v>
+        <v>-2501.311907107822</v>
       </c>
       <c r="D76">
-        <v>2407.439537085218</v>
+        <v>2561.112092892178</v>
       </c>
       <c r="E76">
         <v>4309.024</v>
@@ -7525,37 +7525,37 @@
         <v>560.1</v>
       </c>
       <c r="M76">
-        <v>1341.991572484404</v>
+        <v>1258.324212484404</v>
       </c>
       <c r="N76">
-        <v>-781.8915724844038</v>
+        <v>-698.2242124844039</v>
       </c>
       <c r="O76">
-        <v>-172.0161459465688</v>
+        <v>-153.6093267465689</v>
       </c>
       <c r="P76">
-        <v>-609.875426537835</v>
+        <v>-544.614885737835</v>
       </c>
       <c r="Q76">
-        <v>92.02457346216499</v>
+        <v>157.2851142621649</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1923545837020234</v>
+        <v>0.191622101006692</v>
       </c>
       <c r="T76">
-        <v>1.909808083147351</v>
+        <v>1.900550815759592</v>
       </c>
       <c r="U76">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V76">
-        <v>0.09182024874558745</v>
+        <v>0.09792547801072155</v>
       </c>
       <c r="W76">
-        <v>0.218502694327466</v>
+        <v>0.203502694327466</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4173647670253975</v>
+        <v>0.4451158091396434</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2136521266136979</v>
+        <v>0.2022116811129117</v>
       </c>
       <c r="C77">
-        <v>-2755.041629503903</v>
+        <v>-2602.474538655557</v>
       </c>
       <c r="D77">
-        <v>2382.758370496098</v>
+        <v>2535.325461344444</v>
       </c>
       <c r="E77">
         <v>4384.400000000001</v>
@@ -7607,37 +7607,37 @@
         <v>560.1</v>
       </c>
       <c r="M77">
-        <v>1360.126593734193</v>
+        <v>1275.328593734193</v>
       </c>
       <c r="N77">
-        <v>-800.0265937341932</v>
+        <v>-715.2285937341932</v>
       </c>
       <c r="O77">
-        <v>-176.0058506215225</v>
+        <v>-157.3502906215225</v>
       </c>
       <c r="P77">
-        <v>-624.0207431126706</v>
+        <v>-557.8783031126707</v>
       </c>
       <c r="Q77">
-        <v>77.87925688732935</v>
+        <v>144.0216968873293</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1982167670501043</v>
+        <v>0.1974549850469597</v>
       </c>
       <c r="T77">
-        <v>1.986200406473245</v>
+        <v>1.976572848389976</v>
       </c>
       <c r="U77">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V77">
-        <v>0.09059597876231293</v>
+        <v>0.09661980497057859</v>
       </c>
       <c r="W77">
-        <v>0.2187972464682292</v>
+        <v>0.2037972464682291</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4117999034650588</v>
+        <v>0.4391809316844482</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.215600067662545</v>
+        <v>0.2040096221617588</v>
       </c>
       <c r="C78">
-        <v>-2854.59786702048</v>
+        <v>-2703.123079442571</v>
       </c>
       <c r="D78">
-        <v>2358.57813297952</v>
+        <v>2510.052920557429</v>
       </c>
       <c r="E78">
         <v>4459.776</v>
@@ -7689,37 +7689,37 @@
         <v>560.1</v>
       </c>
       <c r="M78">
-        <v>1378.261614983982</v>
+        <v>1292.332974983982</v>
       </c>
       <c r="N78">
-        <v>-818.1616149839823</v>
+        <v>-732.2329749839822</v>
       </c>
       <c r="O78">
-        <v>-179.9955552964761</v>
+        <v>-161.0912544964761</v>
       </c>
       <c r="P78">
-        <v>-638.1660596875062</v>
+        <v>-571.1417204875061</v>
       </c>
       <c r="Q78">
-        <v>63.73394031249381</v>
+        <v>130.7582795124939</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.204567465677192</v>
+        <v>0.2037739427572497</v>
       </c>
       <c r="T78">
-        <v>2.068958756742964</v>
+        <v>2.058930050406225</v>
       </c>
       <c r="U78">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V78">
-        <v>0.08940392641017725</v>
+        <v>0.09534849174728152</v>
       </c>
       <c r="W78">
-        <v>0.2190840472368669</v>
+        <v>0.2040840472368669</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4063814836826238</v>
+        <v>0.4334022352149159</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.217548008711392</v>
+        <v>0.2058075632106058</v>
       </c>
       <c r="C79">
-        <v>-2953.668272547482</v>
+        <v>-2803.272751358094</v>
       </c>
       <c r="D79">
-        <v>2334.883727452519</v>
+        <v>2485.279248641906</v>
       </c>
       <c r="E79">
         <v>4535.152</v>
@@ -7771,37 +7771,37 @@
         <v>560.1</v>
       </c>
       <c r="M79">
-        <v>1396.396636233771</v>
+        <v>1309.337356233772</v>
       </c>
       <c r="N79">
-        <v>-836.2966362337714</v>
+        <v>-749.2373562337715</v>
       </c>
       <c r="O79">
-        <v>-183.9852599714297</v>
+        <v>-164.8322183714297</v>
       </c>
       <c r="P79">
-        <v>-652.3113762623417</v>
+        <v>-584.4051378623418</v>
       </c>
       <c r="Q79">
-        <v>49.58862373765828</v>
+        <v>117.4948621376582</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2114703989675047</v>
+        <v>0.2106423750510432</v>
       </c>
       <c r="T79">
-        <v>2.158913485297006</v>
+        <v>2.148448748249974</v>
       </c>
       <c r="U79">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V79">
-        <v>0.08824283645679833</v>
+        <v>0.09411019964666748</v>
       </c>
       <c r="W79">
-        <v>0.2193633986348908</v>
+        <v>0.2043633986348908</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4011038020763561</v>
+        <v>0.4277736347575795</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.219495949760239</v>
+        <v>0.2076055042594528</v>
       </c>
       <c r="C80">
-        <v>-3052.267342537343</v>
+        <v>-2902.938181217771</v>
       </c>
       <c r="D80">
-        <v>2311.660657462658</v>
+        <v>2460.98981878223</v>
       </c>
       <c r="E80">
         <v>4610.528</v>
@@ -7853,37 +7853,37 @@
         <v>560.1</v>
       </c>
       <c r="M80">
-        <v>1414.531657483561</v>
+        <v>1326.341737483561</v>
       </c>
       <c r="N80">
-        <v>-854.4316574835608</v>
+        <v>-766.2417374835608</v>
       </c>
       <c r="O80">
-        <v>-187.9749646463834</v>
+        <v>-168.5731822463834</v>
       </c>
       <c r="P80">
-        <v>-666.4566928371775</v>
+        <v>-597.6685552371774</v>
       </c>
       <c r="Q80">
-        <v>35.44330716282252</v>
+        <v>104.2314447628225</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2190008716478458</v>
+        <v>0.218135210280636</v>
       </c>
       <c r="T80">
-        <v>2.25704591644687</v>
+        <v>2.246105509534063</v>
       </c>
       <c r="U80">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V80">
-        <v>0.08711151804068552</v>
+        <v>0.09290365862555636</v>
       </c>
       <c r="W80">
-        <v>0.219635587176555</v>
+        <v>0.204635587176555</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3959614456394797</v>
+        <v>0.4222893573888925</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.221443890809086</v>
+        <v>0.2094034453082998</v>
       </c>
       <c r="C81">
-        <v>-3150.409002387561</v>
+        <v>-3002.133429561427</v>
       </c>
       <c r="D81">
-        <v>2288.89499761244</v>
+        <v>2437.170570438574</v>
       </c>
       <c r="E81">
         <v>4685.904</v>
@@ -7935,37 +7935,37 @@
         <v>560.1</v>
       </c>
       <c r="M81">
-        <v>1432.66667873335</v>
+        <v>1343.34611873335</v>
       </c>
       <c r="N81">
-        <v>-872.5666787333502</v>
+        <v>-783.24611873335</v>
       </c>
       <c r="O81">
-        <v>-191.964669321337</v>
+        <v>-172.314146121337</v>
       </c>
       <c r="P81">
-        <v>-680.6020094120131</v>
+        <v>-610.9319726120131</v>
       </c>
       <c r="Q81">
-        <v>21.29799058798687</v>
+        <v>90.96802738798692</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2272485322025052</v>
+        <v>0.2263416488654282</v>
       </c>
       <c r="T81">
-        <v>2.364524293420531</v>
+        <v>2.353062914749971</v>
       </c>
       <c r="U81">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V81">
-        <v>0.08600884059713254</v>
+        <v>0.09172766294675183</v>
       </c>
       <c r="W81">
-        <v>0.2199008848690632</v>
+        <v>0.2049008848690632</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3909492754415115</v>
+        <v>0.4169439224852356</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.223391831857933</v>
+        <v>0.2112013863571469</v>
       </c>
       <c r="C82">
-        <v>-3248.106634285754</v>
+        <v>-3100.872017794523</v>
       </c>
       <c r="D82">
-        <v>2266.573365714246</v>
+        <v>2413.807982205478</v>
       </c>
       <c r="E82">
         <v>4761.280000000001</v>
@@ -8017,37 +8017,37 @@
         <v>560.1</v>
       </c>
       <c r="M82">
-        <v>1450.801699983139</v>
+        <v>1360.350499983139</v>
       </c>
       <c r="N82">
-        <v>-890.7016999831393</v>
+        <v>-800.2504999831393</v>
       </c>
       <c r="O82">
-        <v>-195.9543739962907</v>
+        <v>-176.0551099962906</v>
       </c>
       <c r="P82">
-        <v>-694.7473259868486</v>
+        <v>-624.1953899868487</v>
       </c>
       <c r="Q82">
-        <v>7.152674013151341</v>
+        <v>77.7046100131513</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2363209588126304</v>
+        <v>0.2353687313086997</v>
       </c>
       <c r="T82">
-        <v>2.482750508091557</v>
+        <v>2.47071606048747</v>
       </c>
       <c r="U82">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V82">
-        <v>0.0849337300896684</v>
+        <v>0.09058106715991743</v>
       </c>
       <c r="W82">
-        <v>0.2201595501192586</v>
+        <v>0.2051595501192587</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3860624094984927</v>
+        <v>0.4117321234541702</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.22533977290678</v>
+        <v>0.2129993274059939</v>
       </c>
       <c r="C83">
-        <v>-3345.373103441143</v>
+        <v>-3199.166953783368</v>
       </c>
       <c r="D83">
-        <v>2244.682896558858</v>
+        <v>2390.889046216633</v>
       </c>
       <c r="E83">
         <v>4836.656000000001</v>
@@ -8099,37 +8099,37 @@
         <v>560.1</v>
       </c>
       <c r="M83">
-        <v>1468.936721232929</v>
+        <v>1377.354881232929</v>
       </c>
       <c r="N83">
-        <v>-908.8367212329287</v>
+        <v>-817.2548812329286</v>
       </c>
       <c r="O83">
-        <v>-199.9440786712443</v>
+        <v>-179.7960738712443</v>
       </c>
       <c r="P83">
-        <v>-708.8926425616844</v>
+        <v>-637.4588073616843</v>
       </c>
       <c r="Q83">
-        <v>-6.99264256168442</v>
+        <v>64.44119263831567</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2463483776975057</v>
+        <v>0.245346032956526</v>
       </c>
       <c r="T83">
-        <v>2.613421587464797</v>
+        <v>2.600753747881547</v>
       </c>
       <c r="U83">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V83">
-        <v>0.08388516552066012</v>
+        <v>0.08946278238016536</v>
       </c>
       <c r="W83">
-        <v>0.220411828573153</v>
+        <v>0.205411828573153</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3812962069120915</v>
+        <v>0.4066490108189335</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.227287713955627</v>
+        <v>0.2147972684548408</v>
       </c>
       <c r="C84">
-        <v>-3442.220782810524</v>
+        <v>-3297.030756005897</v>
       </c>
       <c r="D84">
-        <v>2223.211217189476</v>
+        <v>2368.401243994103</v>
       </c>
       <c r="E84">
         <v>4912.032</v>
@@ -8181,37 +8181,37 @@
         <v>560.1</v>
       </c>
       <c r="M84">
-        <v>1487.071742482718</v>
+        <v>1394.359262482718</v>
       </c>
       <c r="N84">
-        <v>-926.9717424827178</v>
+        <v>-834.2592624827176</v>
       </c>
       <c r="O84">
-        <v>-203.9337833461979</v>
+        <v>-183.5370377461979</v>
       </c>
       <c r="P84">
-        <v>-723.0379591365199</v>
+        <v>-650.7222247365198</v>
       </c>
       <c r="Q84">
-        <v>-21.13795913651995</v>
+        <v>51.17777526348016</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.257489954236256</v>
+        <v>0.2564319236763329</v>
       </c>
       <c r="T84">
-        <v>2.758611675657286</v>
+        <v>2.7452400672083</v>
       </c>
       <c r="U84">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V84">
-        <v>0.08286217569723746</v>
+        <v>0.08837177283894385</v>
       </c>
       <c r="W84">
-        <v>0.2206579538940255</v>
+        <v>0.2056579538940255</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3766462531692611</v>
+        <v>0.4016898765406538</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.229235655004474</v>
+        <v>0.2165952095036879</v>
       </c>
       <c r="C85">
-        <v>-3538.661576418592</v>
+        <v>-3394.475476352237</v>
       </c>
       <c r="D85">
-        <v>2202.146423581408</v>
+        <v>2346.332523647764</v>
       </c>
       <c r="E85">
         <v>4987.408</v>
@@ -8263,37 +8263,37 @@
         <v>560.1</v>
       </c>
       <c r="M85">
-        <v>1505.206763732507</v>
+        <v>1411.363643732507</v>
       </c>
       <c r="N85">
-        <v>-945.1067637325069</v>
+        <v>-851.2636437325069</v>
       </c>
       <c r="O85">
-        <v>-207.9234880211515</v>
+        <v>-187.2780016211515</v>
       </c>
       <c r="P85">
-        <v>-737.1832757113555</v>
+        <v>-663.9856421113554</v>
       </c>
       <c r="Q85">
-        <v>-35.28327571135549</v>
+        <v>37.91435788864453</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2699423044854475</v>
+        <v>0.2688220368337643</v>
       </c>
       <c r="T85">
-        <v>2.92088295069595</v>
+        <v>2.906724777044083</v>
       </c>
       <c r="U85">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V85">
-        <v>0.08186383623100568</v>
+        <v>0.08730705268425777</v>
       </c>
       <c r="W85">
-        <v>0.2208981484842746</v>
+        <v>0.2058981484842747</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3721083465045713</v>
+        <v>0.396850239473899</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2311835960533211</v>
+        <v>0.2183931505525348</v>
       </c>
       <c r="C86">
-        <v>-3634.70694136493</v>
+        <v>-3491.512721662293</v>
       </c>
       <c r="D86">
-        <v>2181.47705863507</v>
+        <v>2324.671278337707</v>
       </c>
       <c r="E86">
         <v>5062.784</v>
@@ -8345,37 +8345,37 @@
         <v>560.1</v>
       </c>
       <c r="M86">
-        <v>1523.341784982296</v>
+        <v>1428.368024982296</v>
       </c>
       <c r="N86">
-        <v>-963.2417849822961</v>
+        <v>-868.268024982296</v>
       </c>
       <c r="O86">
-        <v>-211.9131926961051</v>
+        <v>-191.0189654961051</v>
       </c>
       <c r="P86">
-        <v>-751.3285922861909</v>
+        <v>-677.2490594861908</v>
       </c>
       <c r="Q86">
-        <v>-49.42859228619091</v>
+        <v>24.65094051380913</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2839511985157879</v>
+        <v>0.2827609141358745</v>
       </c>
       <c r="T86">
-        <v>3.103438135114445</v>
+        <v>3.088395075609336</v>
       </c>
       <c r="U86">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V86">
-        <v>0.08088926675206515</v>
+        <v>0.08626768300944519</v>
       </c>
       <c r="W86">
-        <v>0.2211326241557083</v>
+        <v>0.2061326241557083</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3676784852366597</v>
+        <v>0.3921258318611145</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2331315371021681</v>
+        <v>0.2201910916013819</v>
       </c>
       <c r="C87">
-        <v>-3730.3679086032</v>
+        <v>-3588.153674081269</v>
       </c>
       <c r="D87">
-        <v>2161.1920913968</v>
+        <v>2303.406325918731</v>
       </c>
       <c r="E87">
         <v>5138.16</v>
@@ -8427,37 +8427,37 @@
         <v>560.1</v>
       </c>
       <c r="M87">
-        <v>1541.476806232085</v>
+        <v>1445.372406232085</v>
       </c>
       <c r="N87">
-        <v>-981.3768062320854</v>
+        <v>-885.2724062320852</v>
       </c>
       <c r="O87">
-        <v>-215.9028973710588</v>
+        <v>-194.7599293710587</v>
       </c>
       <c r="P87">
-        <v>-765.4739088610266</v>
+        <v>-690.5124768610265</v>
       </c>
       <c r="Q87">
-        <v>-63.57390886102667</v>
+        <v>11.38752313897351</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2998279450835071</v>
+        <v>0.2985583084115995</v>
       </c>
       <c r="T87">
-        <v>3.310334010788742</v>
+        <v>3.294288080649959</v>
       </c>
       <c r="U87">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V87">
-        <v>0.0799376283196879</v>
+        <v>0.08525276909168701</v>
       </c>
       <c r="W87">
-        <v>0.22136158275252</v>
+        <v>0.20636158275252</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3633528559985814</v>
+        <v>0.3875125867803955</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2350794781510151</v>
+        <v>0.2219890326502289</v>
       </c>
       <c r="C88">
-        <v>-3825.655102571676</v>
+        <v>-3684.409110308072</v>
       </c>
       <c r="D88">
-        <v>2141.280897428324</v>
+        <v>2282.526889691928</v>
       </c>
       <c r="E88">
         <v>5213.536</v>
@@ -8509,37 +8509,37 @@
         <v>560.1</v>
       </c>
       <c r="M88">
-        <v>1559.611827481875</v>
+        <v>1462.376787481875</v>
       </c>
       <c r="N88">
-        <v>-999.5118274818748</v>
+        <v>-902.2767874818745</v>
       </c>
       <c r="O88">
-        <v>-219.8926020460125</v>
+        <v>-198.5008932460124</v>
       </c>
       <c r="P88">
-        <v>-779.6192254358623</v>
+        <v>-703.7758942358621</v>
       </c>
       <c r="Q88">
-        <v>-77.71922543586231</v>
+        <v>-1.87589423586212</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3179727983037576</v>
+        <v>0.3166124732981423</v>
       </c>
       <c r="T88">
-        <v>3.546786440130795</v>
+        <v>3.529594372124956</v>
       </c>
       <c r="U88">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V88">
-        <v>0.07900812101364502</v>
+        <v>0.08426145782317902</v>
       </c>
       <c r="W88">
-        <v>0.2215852167308011</v>
+        <v>0.2065852167308011</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3591278227892954</v>
+        <v>0.3830066264689955</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2370274191998621</v>
+        <v>0.2237869736990759</v>
       </c>
       <c r="C89">
-        <v>-3920.578759748558</v>
+        <v>-3780.289419806268</v>
       </c>
       <c r="D89">
-        <v>2121.733240251442</v>
+        <v>2262.022580193732</v>
       </c>
       <c r="E89">
         <v>5288.912</v>
@@ -8591,37 +8591,37 @@
         <v>560.1</v>
       </c>
       <c r="M89">
-        <v>1577.746848731664</v>
+        <v>1479.381168731664</v>
       </c>
       <c r="N89">
-        <v>-1017.646848731664</v>
+        <v>-919.2811687316638</v>
       </c>
       <c r="O89">
-        <v>-223.8823067209661</v>
+        <v>-202.241857120966</v>
       </c>
       <c r="P89">
-        <v>-793.7645420106978</v>
+        <v>-717.0393116106977</v>
       </c>
       <c r="Q89">
-        <v>-91.86454201069785</v>
+        <v>-15.13931161069775</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3389091674040467</v>
+        <v>0.337444202013384</v>
       </c>
       <c r="T89">
-        <v>3.819616166294702</v>
+        <v>3.801101631519183</v>
       </c>
       <c r="U89">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V89">
-        <v>0.07809998169164908</v>
+        <v>0.08329293531946431</v>
       </c>
       <c r="W89">
-        <v>0.2218037096980874</v>
+        <v>0.2068037096980873</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3549999167802231</v>
+        <v>0.3786042514521105</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2389753602487091</v>
+        <v>0.2255849147479229</v>
       </c>
       <c r="C90">
-        <v>-4015.148746200115</v>
+        <v>-3875.804622042222</v>
       </c>
       <c r="D90">
-        <v>2102.539253799886</v>
+        <v>2241.883377957778</v>
       </c>
       <c r="E90">
         <v>5364.288</v>
@@ -8673,37 +8673,37 @@
         <v>560.1</v>
       </c>
       <c r="M90">
-        <v>1595.881869981453</v>
+        <v>1496.385549981453</v>
       </c>
       <c r="N90">
-        <v>-1035.781869981453</v>
+        <v>-936.2855499814531</v>
       </c>
       <c r="O90">
-        <v>-227.8720113959197</v>
+        <v>-205.9828209959197</v>
       </c>
       <c r="P90">
-        <v>-807.9098585855336</v>
+        <v>-730.3027289855333</v>
       </c>
       <c r="Q90">
-        <v>-106.0098585855336</v>
+        <v>-28.40272898553337</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3633349313543839</v>
+        <v>0.3617478855144994</v>
       </c>
       <c r="T90">
-        <v>4.137917513485928</v>
+        <v>4.117860100812449</v>
       </c>
       <c r="U90">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V90">
-        <v>0.07721248189969852</v>
+        <v>0.08234642469083404</v>
       </c>
       <c r="W90">
-        <v>0.2220172369161171</v>
+        <v>0.207017236916117</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3509658268168114</v>
+        <v>0.374301930412882</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2409233012975561</v>
+        <v>0.22738285579677</v>
       </c>
       <c r="C91">
-        <v>-4109.374574184902</v>
+        <v>-3970.96438281051</v>
       </c>
       <c r="D91">
-        <v>2083.689425815098</v>
+        <v>2222.099617189491</v>
       </c>
       <c r="E91">
         <v>5439.664000000001</v>
@@ -8755,37 +8755,37 @@
         <v>560.1</v>
       </c>
       <c r="M91">
-        <v>1614.016891231243</v>
+        <v>1513.389931231242</v>
       </c>
       <c r="N91">
-        <v>-1053.916891231243</v>
+        <v>-953.2899312312423</v>
       </c>
       <c r="O91">
-        <v>-231.8617160708733</v>
+        <v>-209.7237848708733</v>
       </c>
       <c r="P91">
-        <v>-822.0551751603691</v>
+        <v>-743.566146360369</v>
       </c>
       <c r="Q91">
-        <v>-120.1551751603691</v>
+        <v>-41.666146360369</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3922017432956916</v>
+        <v>0.3904704205612721</v>
       </c>
       <c r="T91">
-        <v>4.51409183289374</v>
+        <v>4.492211019068127</v>
       </c>
       <c r="U91">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V91">
-        <v>0.07634492592329742</v>
+        <v>0.08142118396397073</v>
       </c>
       <c r="W91">
-        <v>0.2222259657696967</v>
+        <v>0.2072259657696967</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3470223905604429</v>
+        <v>0.3700962907453216</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2428712423464031</v>
+        <v>0.229180796845617</v>
       </c>
       <c r="C92">
-        <v>-4203.265417872743</v>
+        <v>-4065.778029702501</v>
       </c>
       <c r="D92">
-        <v>2065.174582127257</v>
+        <v>2202.661970297499</v>
       </c>
       <c r="E92">
         <v>5515.04</v>
@@ -8837,37 +8837,37 @@
         <v>560.1</v>
       </c>
       <c r="M92">
-        <v>1632.151912481032</v>
+        <v>1530.394312481032</v>
       </c>
       <c r="N92">
-        <v>-1072.051912481032</v>
+        <v>-970.2943124810316</v>
       </c>
       <c r="O92">
-        <v>-235.851420745827</v>
+        <v>-213.464748745827</v>
       </c>
       <c r="P92">
-        <v>-836.2004917352047</v>
+        <v>-756.8295637352046</v>
       </c>
       <c r="Q92">
-        <v>-134.3004917352047</v>
+        <v>-54.92956373520462</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4268419176252607</v>
+        <v>0.4249374626173993</v>
       </c>
       <c r="T92">
-        <v>4.965501016183114</v>
+        <v>4.94143212097494</v>
       </c>
       <c r="U92">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V92">
-        <v>0.07549664896859413</v>
+        <v>0.08051650414214884</v>
       </c>
       <c r="W92">
-        <v>0.2224300562043078</v>
+        <v>0.2074300562043078</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3431665862208824</v>
+        <v>0.3659841097370402</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2448191833952501</v>
+        <v>0.230978737894464</v>
       </c>
       <c r="C93">
-        <v>-4296.83012823305</v>
+        <v>-4160.254566770131</v>
       </c>
       <c r="D93">
-        <v>2046.98587176695</v>
+        <v>2183.56143322987</v>
       </c>
       <c r="E93">
         <v>5590.416</v>
@@ -8919,37 +8919,37 @@
         <v>560.1</v>
       </c>
       <c r="M93">
-        <v>1650.286933730821</v>
+        <v>1547.398693730821</v>
       </c>
       <c r="N93">
-        <v>-1090.186933730821</v>
+        <v>-987.2986937308209</v>
       </c>
       <c r="O93">
-        <v>-239.8411254207806</v>
+        <v>-217.2057126207806</v>
       </c>
       <c r="P93">
-        <v>-850.3458083100402</v>
+        <v>-770.0929811100403</v>
       </c>
       <c r="Q93">
-        <v>-148.4458083100402</v>
+        <v>-68.19298111004036</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.469179908472512</v>
+        <v>0.4670638473526659</v>
       </c>
       <c r="T93">
-        <v>5.517223351314572</v>
+        <v>5.4904801344166</v>
       </c>
       <c r="U93">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V93">
-        <v>0.07466701546344474</v>
+        <v>0.07963170739333401</v>
       </c>
       <c r="W93">
-        <v>0.2226296611348616</v>
+        <v>0.2076296611348616</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3393955248338398</v>
+        <v>0.3619623063333364</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2467671244440972</v>
+        <v>0.232776678943311</v>
       </c>
       <c r="C94">
-        <v>-4390.077247143259</v>
+        <v>-4254.402688433267</v>
       </c>
       <c r="D94">
-        <v>2029.114752856742</v>
+        <v>2164.789311566733</v>
       </c>
       <c r="E94">
         <v>5665.792</v>
@@ -9001,37 +9001,37 @@
         <v>560.1</v>
       </c>
       <c r="M94">
-        <v>1668.42195498061</v>
+        <v>1564.40307498061</v>
       </c>
       <c r="N94">
-        <v>-1108.32195498061</v>
+        <v>-1004.30307498061</v>
       </c>
       <c r="O94">
-        <v>-243.8308300957343</v>
+        <v>-220.9466764957342</v>
       </c>
       <c r="P94">
-        <v>-864.4911248848761</v>
+        <v>-783.356398484876</v>
       </c>
       <c r="Q94">
-        <v>-162.5911248848761</v>
+        <v>-81.45639848487599</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5221023970315761</v>
+        <v>0.5197218282717493</v>
       </c>
       <c r="T94">
-        <v>6.206876270228896</v>
+        <v>6.176790151218677</v>
       </c>
       <c r="U94">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V94">
-        <v>0.07385541746927686</v>
+        <v>0.07876614535644995</v>
       </c>
       <c r="W94">
-        <v>0.2228249268277946</v>
+        <v>0.2078249268277946</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3357064430421675</v>
+        <v>0.3580279334384089</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2487150654929442</v>
+        <v>0.234574619992158</v>
       </c>
       <c r="C95">
-        <v>-4483.015020764622</v>
+        <v>-4348.230792675833</v>
       </c>
       <c r="D95">
-        <v>2011.552979235379</v>
+        <v>2146.337207324167</v>
       </c>
       <c r="E95">
         <v>5741.168000000001</v>
@@ -9083,37 +9083,37 @@
         <v>560.1</v>
       </c>
       <c r="M95">
-        <v>1686.556976230399</v>
+        <v>1581.407456230399</v>
       </c>
       <c r="N95">
-        <v>-1126.4569762304</v>
+        <v>-1021.307456230399</v>
       </c>
       <c r="O95">
-        <v>-247.8205347706879</v>
+        <v>-224.6876403706879</v>
       </c>
       <c r="P95">
-        <v>-878.6364414597116</v>
+        <v>-796.6198158597116</v>
       </c>
       <c r="Q95">
-        <v>-176.7364414597116</v>
+        <v>-94.71981585971162</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5901455966075155</v>
+        <v>0.5874249465962849</v>
       </c>
       <c r="T95">
-        <v>7.093572880261595</v>
+        <v>7.059188744249917</v>
       </c>
       <c r="U95">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V95">
-        <v>0.07306127319541367</v>
+        <v>0.07791919755691822</v>
       </c>
       <c r="W95">
-        <v>0.2230159932585141</v>
+        <v>0.2080159932585141</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3320966963427894</v>
+        <v>0.3541781707132646</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2506630065417911</v>
+        <v>0.236372561041005</v>
       </c>
       <c r="C96">
-        <v>-4575.651412229364</v>
+        <v>-4441.746993572749</v>
       </c>
       <c r="D96">
-        <v>1994.292587770637</v>
+        <v>2128.197006427252</v>
       </c>
       <c r="E96">
         <v>5816.544000000001</v>
@@ -9165,37 +9165,37 @@
         <v>560.1</v>
       </c>
       <c r="M96">
-        <v>1704.691997480189</v>
+        <v>1598.411837480189</v>
       </c>
       <c r="N96">
-        <v>-1144.591997480189</v>
+        <v>-1038.311837480189</v>
       </c>
       <c r="O96">
-        <v>-251.8102394456415</v>
+        <v>-228.4286042456415</v>
       </c>
       <c r="P96">
-        <v>-892.7817580345471</v>
+        <v>-809.8832332345473</v>
       </c>
       <c r="Q96">
-        <v>-190.8817580345471</v>
+        <v>-107.9832332345474</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6808698627087683</v>
+        <v>0.6776957710289992</v>
       </c>
       <c r="T96">
-        <v>8.275835026971862</v>
+        <v>8.235720201624906</v>
       </c>
       <c r="U96">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V96">
-        <v>0.07228402560822841</v>
+        <v>0.077090269923334</v>
       </c>
       <c r="W96">
-        <v>0.2232029944460267</v>
+        <v>0.2082029944460267</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3285637527646746</v>
+        <v>0.3504103178333362</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2526109475906382</v>
+        <v>0.238170502089852</v>
       </c>
       <c r="C97">
-        <v>-4667.99411368021</v>
+        <v>-4534.959133186943</v>
       </c>
       <c r="D97">
-        <v>1977.325886319791</v>
+        <v>2110.360866813057</v>
       </c>
       <c r="E97">
         <v>5891.920000000001</v>
@@ -9247,37 +9247,37 @@
         <v>560.1</v>
       </c>
       <c r="M97">
-        <v>1722.827018729978</v>
+        <v>1615.416218729978</v>
       </c>
       <c r="N97">
-        <v>-1162.727018729978</v>
+        <v>-1055.316218729978</v>
       </c>
       <c r="O97">
-        <v>-255.7999441205952</v>
+        <v>-232.1695681205952</v>
       </c>
       <c r="P97">
-        <v>-906.927074609383</v>
+        <v>-823.146650609383</v>
       </c>
       <c r="Q97">
-        <v>-205.027074609383</v>
+        <v>-121.246650609383</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8078838352505223</v>
+        <v>0.8040749252347995</v>
       </c>
       <c r="T97">
-        <v>9.931002032366239</v>
+        <v>9.882864241949893</v>
       </c>
       <c r="U97">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V97">
-        <v>0.07152314112814179</v>
+        <v>0.07627879339782521</v>
       </c>
       <c r="W97">
-        <v>0.2233860587664338</v>
+        <v>0.2083860587664338</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.325105186946099</v>
+        <v>0.3467217881719327</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2545588886394852</v>
+        <v>0.239968443138699</v>
       </c>
       <c r="C98">
-        <v>-4760.050557700535</v>
+        <v>-4627.874792873115</v>
       </c>
       <c r="D98">
-        <v>1960.645442299465</v>
+        <v>2092.821207126886</v>
       </c>
       <c r="E98">
         <v>5967.296</v>
@@ -9329,37 +9329,37 @@
         <v>560.1</v>
       </c>
       <c r="M98">
-        <v>1740.962039979767</v>
+        <v>1632.420599979767</v>
       </c>
       <c r="N98">
-        <v>-1180.862039979767</v>
+        <v>-1072.320599979767</v>
       </c>
       <c r="O98">
-        <v>-259.7896487955488</v>
+        <v>-235.9105319955487</v>
       </c>
       <c r="P98">
-        <v>-921.0723911842185</v>
+        <v>-836.4100679842182</v>
       </c>
       <c r="Q98">
-        <v>-219.1723911842186</v>
+        <v>-134.5100679842183</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.9984047940631507</v>
+        <v>0.9936436565434972</v>
       </c>
       <c r="T98">
-        <v>12.41375254045777</v>
+        <v>12.35358030243734</v>
       </c>
       <c r="U98">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V98">
-        <v>0.07077810840805698</v>
+        <v>0.07548422263326453</v>
       </c>
       <c r="W98">
-        <v>0.2235653092468324</v>
+        <v>0.2085653092468324</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3217186745820771</v>
+        <v>0.3431101028784752</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2565068296883322</v>
+        <v>0.241766384187546</v>
       </c>
       <c r="C99">
-        <v>-4851.827928170809</v>
+        <v>-4720.501304022429</v>
       </c>
       <c r="D99">
-        <v>1944.244071829191</v>
+        <v>2075.57069597757</v>
       </c>
       <c r="E99">
         <v>6042.672</v>
@@ -9411,37 +9411,37 @@
         <v>560.1</v>
       </c>
       <c r="M99">
-        <v>1759.097061229556</v>
+        <v>1649.424981229556</v>
       </c>
       <c r="N99">
-        <v>-1198.997061229556</v>
+        <v>-1089.324981229556</v>
       </c>
       <c r="O99">
-        <v>-263.7793534705023</v>
+        <v>-239.6514958705024</v>
       </c>
       <c r="P99">
-        <v>-935.2177077590537</v>
+        <v>-849.6734853590539</v>
       </c>
       <c r="Q99">
-        <v>-233.3177077590537</v>
+        <v>-147.7734853590539</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.315939725417535</v>
+        <v>1.309591542057996</v>
       </c>
       <c r="T99">
-        <v>16.5516700539437</v>
+        <v>16.47144040324978</v>
       </c>
       <c r="U99">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V99">
-        <v>0.07004843718735537</v>
+        <v>0.07470603477106594</v>
       </c>
       <c r="W99">
-        <v>0.2237408638410373</v>
+        <v>0.2087408638410372</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3184019872152518</v>
+        <v>0.339572885323027</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2584547707371792</v>
+        <v>0.2435643252363931</v>
       </c>
       <c r="C100">
-        <v>-4943.333170584667</v>
+        <v>-4812.845758280185</v>
       </c>
       <c r="D100">
-        <v>1928.114829415334</v>
+        <v>2058.602241719815</v>
       </c>
       <c r="E100">
         <v>6118.048</v>
@@ -9493,37 +9493,37 @@
         <v>560.1</v>
       </c>
       <c r="M100">
-        <v>1777.232082479346</v>
+        <v>1666.429362479345</v>
       </c>
       <c r="N100">
-        <v>-1217.132082479346</v>
+        <v>-1106.329362479345</v>
       </c>
       <c r="O100">
-        <v>-267.769058145456</v>
+        <v>-243.392459745456</v>
       </c>
       <c r="P100">
-        <v>-949.3630243338896</v>
+        <v>-862.9369027338895</v>
       </c>
       <c r="Q100">
-        <v>-247.4630243338896</v>
+        <v>-161.0369027338895</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.951009588126302</v>
+        <v>1.941487313086995</v>
       </c>
       <c r="T100">
-        <v>24.82750508091555</v>
+        <v>24.70716060487467</v>
       </c>
       <c r="U100">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V100">
-        <v>0.06933365721605582</v>
+        <v>0.07394372829381016</v>
       </c>
       <c r="W100">
-        <v>0.2239128356884216</v>
+        <v>0.2089128356884216</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3151529873457083</v>
+        <v>0.3361078558809553</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2604027117860263</v>
+        <v>0.24536226628524</v>
       </c>
       <c r="C101">
-        <v>-5034.573001855702</v>
+        <v>-4904.915017266335</v>
       </c>
       <c r="D101">
-        <v>1912.250998144298</v>
+        <v>2041.908982733665</v>
       </c>
       <c r="E101">
         <v>6193.424</v>
@@ -9575,37 +9575,37 @@
         <v>560.1</v>
       </c>
       <c r="M101">
-        <v>1795.367103729135</v>
+        <v>1683.433743729135</v>
       </c>
       <c r="N101">
-        <v>-1235.267103729135</v>
+        <v>-1123.333743729135</v>
       </c>
       <c r="O101">
-        <v>-271.7587628204096</v>
+        <v>-247.1334236204096</v>
       </c>
       <c r="P101">
-        <v>-963.5083409087251</v>
+        <v>-876.2003201087251</v>
       </c>
       <c r="Q101">
-        <v>-261.6083409087252</v>
+        <v>-174.3003201087251</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.856219176252603</v>
+        <v>3.837174626173989</v>
       </c>
       <c r="T101">
-        <v>49.65501016183109</v>
+        <v>49.41432120974935</v>
       </c>
       <c r="U101">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V101">
-        <v>0.06863331724417648</v>
+        <v>0.07319682194740804</v>
       </c>
       <c r="W101">
-        <v>0.2240813333570709</v>
+        <v>0.2090813333570709</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3119696238371659</v>
+        <v>0.3327128270336729</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/greece/greece_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_telecom_services.xlsx
@@ -1139,43 +1139,43 @@
         <v>35.9038461538462</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>98.9524703549335</v>
       </c>
       <c r="G2">
         <v>1.0053882725832</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0597274167987322</v>
       </c>
       <c r="I2">
         <v>0.168329441732116</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>6268.8</v>
       </c>
       <c r="L2">
-        <v>7697.7208730791</v>
+        <v>7618.03959601244</v>
       </c>
       <c r="M2">
         <v>7022.2</v>
       </c>
       <c r="N2">
-        <v>7182.3208730791</v>
+        <v>7178.01559601244</v>
       </c>
       <c r="O2">
         <v>1268.8</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>75.376</v>
       </c>
       <c r="Q2">
         <v>0.0881131242744239</v>
       </c>
       <c r="R2">
-        <v>0.08667580553052059</v>
+        <v>0.0867136127764541</v>
       </c>
       <c r="S2">
         <v>0.063331401810067</v>
@@ -1197,13 +1197,13 @@
         <v>0.0931289246609055</v>
       </c>
       <c r="X2">
-        <v>0.08667580553052059</v>
+        <v>0.08699785733167011</v>
       </c>
       <c r="Y2">
         <v>0.616854549154934</v>
       </c>
       <c r="Z2">
-        <v>0.532748774085323</v>
+        <v>0.536946188669025</v>
       </c>
       <c r="AA2">
         <v>1268.8</v>
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08667580553052057</v>
+        <v>0.08671361277645408</v>
       </c>
       <c r="C2">
-        <v>7697.7208730791</v>
+        <v>7618.039596012441</v>
       </c>
       <c r="D2">
-        <v>7182.3208730791</v>
+        <v>7178.015596012441</v>
       </c>
       <c r="E2">
-        <v>-1268.8</v>
+        <v>-1193.424</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>75.376</v>
       </c>
       <c r="G2">
         <v>515.4</v>
@@ -1457,28 +1457,28 @@
         <v>560.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.66029324978924</v>
       </c>
       <c r="N2">
-        <v>560.1</v>
+        <v>554.4397067502108</v>
       </c>
       <c r="O2">
-        <v>123.222</v>
+        <v>121.9767354850464</v>
       </c>
       <c r="P2">
-        <v>436.878</v>
+        <v>432.4629712651644</v>
       </c>
       <c r="Q2">
-        <v>1138.778</v>
+        <v>1134.362971265164</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08667580553052057</v>
+        <v>0.08699785733167012</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5369461886690254</v>
       </c>
       <c r="U2">
         <v>0.07509410488470122</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>98.95247035493351</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08671361277645408</v>
+        <v>0.08675142002238763</v>
       </c>
       <c r="C3">
-        <v>7618.039596012441</v>
+        <v>7538.363477252397</v>
       </c>
       <c r="D3">
-        <v>7178.015596012441</v>
+        <v>7173.715477252398</v>
       </c>
       <c r="E3">
-        <v>-1193.424</v>
+        <v>-1118.048</v>
       </c>
       <c r="F3">
-        <v>75.376</v>
+        <v>150.752</v>
       </c>
       <c r="G3">
         <v>515.4</v>
@@ -1539,28 +1539,28 @@
         <v>560.1</v>
       </c>
       <c r="M3">
-        <v>5.66029324978924</v>
+        <v>11.32058649957848</v>
       </c>
       <c r="N3">
-        <v>554.4397067502108</v>
+        <v>548.7794135004216</v>
       </c>
       <c r="O3">
-        <v>121.9767354850464</v>
+        <v>120.7314709700927</v>
       </c>
       <c r="P3">
-        <v>432.4629712651644</v>
+        <v>428.0479425303288</v>
       </c>
       <c r="Q3">
-        <v>1134.362971265164</v>
+        <v>1129.947942530329</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08699785733167012</v>
+        <v>0.08732648161855744</v>
       </c>
       <c r="T3">
-        <v>0.5369461886690254</v>
+        <v>0.5412292647748445</v>
       </c>
       <c r="U3">
         <v>0.07509410488470122</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>98.95247035493351</v>
+        <v>49.47623517746676</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08675142002238763</v>
+        <v>0.08678922726832115</v>
       </c>
       <c r="C4">
-        <v>7538.363477252397</v>
+        <v>7458.692507534</v>
       </c>
       <c r="D4">
-        <v>7173.715477252398</v>
+        <v>7169.420507534001</v>
       </c>
       <c r="E4">
-        <v>-1118.048</v>
+        <v>-1042.672</v>
       </c>
       <c r="F4">
-        <v>150.752</v>
+        <v>226.128</v>
       </c>
       <c r="G4">
         <v>515.4</v>
@@ -1621,28 +1621,28 @@
         <v>560.1</v>
       </c>
       <c r="M4">
-        <v>11.32058649957848</v>
+        <v>16.98087974936772</v>
       </c>
       <c r="N4">
-        <v>548.7794135004216</v>
+        <v>543.1191202506322</v>
       </c>
       <c r="O4">
-        <v>120.7314709700927</v>
+        <v>119.4862064551391</v>
       </c>
       <c r="P4">
-        <v>428.0479425303288</v>
+        <v>423.6329137954932</v>
       </c>
       <c r="Q4">
-        <v>1129.947942530329</v>
+        <v>1125.532913795493</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08732648161855744</v>
+        <v>0.08766188166393726</v>
       </c>
       <c r="T4">
-        <v>0.5412292647748445</v>
+        <v>0.545600651728206</v>
       </c>
       <c r="U4">
         <v>0.07509410488470122</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>49.47623517746676</v>
+        <v>32.98415678497783</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08678922726832115</v>
+        <v>0.08682703451425468</v>
       </c>
       <c r="C5">
-        <v>7458.692507534</v>
+        <v>7379.026677614442</v>
       </c>
       <c r="D5">
-        <v>7169.420507534001</v>
+        <v>7165.130677614442</v>
       </c>
       <c r="E5">
-        <v>-1042.672</v>
+        <v>-967.2959999999999</v>
       </c>
       <c r="F5">
-        <v>226.128</v>
+        <v>301.504</v>
       </c>
       <c r="G5">
         <v>515.4</v>
@@ -1703,28 +1703,28 @@
         <v>560.1</v>
       </c>
       <c r="M5">
-        <v>16.98087974936772</v>
+        <v>22.64117299915696</v>
       </c>
       <c r="N5">
-        <v>543.1191202506322</v>
+        <v>537.458827000843</v>
       </c>
       <c r="O5">
-        <v>119.4862064551391</v>
+        <v>118.2409419401855</v>
       </c>
       <c r="P5">
-        <v>423.6329137954932</v>
+        <v>419.2178850606576</v>
       </c>
       <c r="Q5">
-        <v>1125.532913795493</v>
+        <v>1121.117885060657</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08766188166393726</v>
+        <v>0.0880042692102625</v>
       </c>
       <c r="T5">
-        <v>0.545600651728206</v>
+        <v>0.550063109243096</v>
       </c>
       <c r="U5">
         <v>0.07509410488470122</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>32.98415678497783</v>
+        <v>24.73811758873337</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08682703451425468</v>
+        <v>0.0868648417601882</v>
       </c>
       <c r="C6">
-        <v>7379.026677614442</v>
+        <v>7299.365978273029</v>
       </c>
       <c r="D6">
-        <v>7165.130677614442</v>
+        <v>7160.84597827303</v>
       </c>
       <c r="E6">
-        <v>-967.2959999999999</v>
+        <v>-891.9199999999998</v>
       </c>
       <c r="F6">
-        <v>301.504</v>
+        <v>376.8800000000001</v>
       </c>
       <c r="G6">
         <v>515.4</v>
@@ -1785,28 +1785,28 @@
         <v>560.1</v>
       </c>
       <c r="M6">
-        <v>22.64117299915696</v>
+        <v>28.3014662489462</v>
       </c>
       <c r="N6">
-        <v>537.458827000843</v>
+        <v>531.7985337510538</v>
       </c>
       <c r="O6">
-        <v>118.2409419401855</v>
+        <v>116.9956774252318</v>
       </c>
       <c r="P6">
-        <v>419.2178850606576</v>
+        <v>414.8028563258219</v>
       </c>
       <c r="Q6">
-        <v>1121.117885060657</v>
+        <v>1116.702856325822</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0880042692102625</v>
+        <v>0.08835386491545774</v>
       </c>
       <c r="T6">
-        <v>0.550063109243096</v>
+        <v>0.5546195132319837</v>
       </c>
       <c r="U6">
         <v>0.07509410488470122</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>24.73811758873337</v>
+        <v>19.7904940709867</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0868648417601882</v>
+        <v>0.08690264900612171</v>
       </c>
       <c r="C7">
-        <v>7299.365978273029</v>
+        <v>7219.710400311111</v>
       </c>
       <c r="D7">
-        <v>7160.84597827303</v>
+        <v>7156.566400311111</v>
       </c>
       <c r="E7">
-        <v>-891.9199999999998</v>
+        <v>-816.5439999999999</v>
       </c>
       <c r="F7">
-        <v>376.8800000000001</v>
+        <v>452.2560000000001</v>
       </c>
       <c r="G7">
         <v>515.4</v>
@@ -1867,28 +1867,28 @@
         <v>560.1</v>
       </c>
       <c r="M7">
-        <v>28.3014662489462</v>
+        <v>33.96175949873545</v>
       </c>
       <c r="N7">
-        <v>531.7985337510538</v>
+        <v>526.1382405012646</v>
       </c>
       <c r="O7">
-        <v>116.9956774252318</v>
+        <v>115.7504129102782</v>
       </c>
       <c r="P7">
-        <v>414.8028563258219</v>
+        <v>410.3878275909864</v>
       </c>
       <c r="Q7">
-        <v>1116.702856325822</v>
+        <v>1112.287827590986</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08835386491545774</v>
+        <v>0.08871089882714649</v>
       </c>
       <c r="T7">
-        <v>0.5546195132319837</v>
+        <v>0.5592728619865922</v>
       </c>
       <c r="U7">
         <v>0.07509410488470122</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.7904940709867</v>
+        <v>16.49207839248891</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08690264900612171</v>
+        <v>0.08694045625205524</v>
       </c>
       <c r="C8">
-        <v>7219.710400311111</v>
+        <v>7140.05993455201</v>
       </c>
       <c r="D8">
-        <v>7156.566400311111</v>
+        <v>7152.291934552009</v>
       </c>
       <c r="E8">
-        <v>-816.5439999999999</v>
+        <v>-741.168</v>
       </c>
       <c r="F8">
-        <v>452.256</v>
+        <v>527.6319999999999</v>
       </c>
       <c r="G8">
         <v>515.4</v>
@@ -1949,28 +1949,28 @@
         <v>560.1</v>
       </c>
       <c r="M8">
-        <v>33.96175949873544</v>
+        <v>39.62205274852467</v>
       </c>
       <c r="N8">
-        <v>526.1382405012646</v>
+        <v>520.4779472514754</v>
       </c>
       <c r="O8">
-        <v>115.7504129102782</v>
+        <v>114.5051483953246</v>
       </c>
       <c r="P8">
-        <v>410.3878275909864</v>
+        <v>405.9727988561508</v>
       </c>
       <c r="Q8">
-        <v>1112.287827590986</v>
+        <v>1107.872798856151</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08871089882714649</v>
+        <v>0.08907561088747371</v>
       </c>
       <c r="T8">
-        <v>0.5592728619865922</v>
+        <v>0.5640262827574289</v>
       </c>
       <c r="U8">
         <v>0.07509410488470122</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.49207839248892</v>
+        <v>14.13606719356193</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08694045625205525</v>
+        <v>0.08697826349798876</v>
       </c>
       <c r="C9">
-        <v>7140.059934552008</v>
+        <v>7060.414571840963</v>
       </c>
       <c r="D9">
-        <v>7152.291934552009</v>
+        <v>7148.022571840963</v>
       </c>
       <c r="E9">
-        <v>-741.1679999999999</v>
+        <v>-665.7919999999999</v>
       </c>
       <c r="F9">
-        <v>527.6320000000001</v>
+        <v>603.008</v>
       </c>
       <c r="G9">
         <v>515.4</v>
@@ -2031,28 +2031,28 @@
         <v>560.1</v>
       </c>
       <c r="M9">
-        <v>39.62205274852468</v>
+        <v>45.28234599831392</v>
       </c>
       <c r="N9">
-        <v>520.4779472514754</v>
+        <v>514.8176540016862</v>
       </c>
       <c r="O9">
-        <v>114.5051483953246</v>
+        <v>113.2598838803709</v>
       </c>
       <c r="P9">
-        <v>405.9727988561508</v>
+        <v>401.5577701213152</v>
       </c>
       <c r="Q9">
-        <v>1107.872798856151</v>
+        <v>1103.457770121315</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08907561088747372</v>
+        <v>0.08944825147085153</v>
       </c>
       <c r="T9">
-        <v>0.5640262827574291</v>
+        <v>0.5688830387624144</v>
       </c>
       <c r="U9">
         <v>0.07509410488470122</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.13606719356193</v>
+        <v>12.36905879436669</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08697826349798876</v>
+        <v>0.08701607074392229</v>
       </c>
       <c r="C10">
-        <v>7060.414571840963</v>
+        <v>6980.774303045053</v>
       </c>
       <c r="D10">
-        <v>7148.022571840963</v>
+        <v>7143.758303045053</v>
       </c>
       <c r="E10">
-        <v>-665.7919999999999</v>
+        <v>-590.4159999999999</v>
       </c>
       <c r="F10">
-        <v>603.008</v>
+        <v>678.384</v>
       </c>
       <c r="G10">
         <v>515.4</v>
@@ -2113,28 +2113,28 @@
         <v>560.1</v>
       </c>
       <c r="M10">
-        <v>45.28234599831392</v>
+        <v>50.94263924810316</v>
       </c>
       <c r="N10">
-        <v>514.8176540016862</v>
+        <v>509.1573607518969</v>
       </c>
       <c r="O10">
-        <v>113.2598838803709</v>
+        <v>112.0146193654173</v>
       </c>
       <c r="P10">
-        <v>401.5577701213152</v>
+        <v>397.1427413864795</v>
       </c>
       <c r="Q10">
-        <v>1103.457770121315</v>
+        <v>1099.04274138648</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08944825147085153</v>
+        <v>0.08982908195716073</v>
       </c>
       <c r="T10">
-        <v>0.5688830387624144</v>
+        <v>0.5738465366576193</v>
       </c>
       <c r="U10">
         <v>0.07509410488470122</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.36905879436669</v>
+        <v>10.99471892832595</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08701607074392229</v>
+        <v>0.08705387798985581</v>
       </c>
       <c r="C11">
-        <v>6980.774303045053</v>
+        <v>6901.139119053142</v>
       </c>
       <c r="D11">
-        <v>7143.758303045053</v>
+        <v>7139.499119053143</v>
       </c>
       <c r="E11">
-        <v>-590.4159999999999</v>
+        <v>-515.04</v>
       </c>
       <c r="F11">
-        <v>678.384</v>
+        <v>753.76</v>
       </c>
       <c r="G11">
         <v>515.4</v>
@@ -2195,28 +2195,28 @@
         <v>560.1</v>
       </c>
       <c r="M11">
-        <v>50.94263924810316</v>
+        <v>56.6029324978924</v>
       </c>
       <c r="N11">
-        <v>509.1573607518969</v>
+        <v>503.4970675021076</v>
       </c>
       <c r="O11">
-        <v>112.0146193654173</v>
+        <v>110.7693548504637</v>
       </c>
       <c r="P11">
-        <v>397.1427413864795</v>
+        <v>392.7277126516439</v>
       </c>
       <c r="Q11">
-        <v>1099.04274138648</v>
+        <v>1094.627712651644</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08982908195716073</v>
+        <v>0.09021837534316568</v>
       </c>
       <c r="T11">
-        <v>0.5738465366576193</v>
+        <v>0.578920334506051</v>
       </c>
       <c r="U11">
         <v>0.07509410488470122</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>10.99471892832595</v>
+        <v>9.895247035493352</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08705387798985581</v>
+        <v>0.08709168523578935</v>
       </c>
       <c r="C12">
-        <v>6901.139119053142</v>
+        <v>6821.509010775806</v>
       </c>
       <c r="D12">
-        <v>7139.499119053143</v>
+        <v>7135.245010775807</v>
       </c>
       <c r="E12">
-        <v>-515.0399999999998</v>
+        <v>-439.6639999999999</v>
       </c>
       <c r="F12">
-        <v>753.7600000000001</v>
+        <v>829.1360000000001</v>
       </c>
       <c r="G12">
         <v>515.4</v>
@@ -2277,28 +2277,28 @@
         <v>560.1</v>
       </c>
       <c r="M12">
-        <v>56.6029324978924</v>
+        <v>62.26322574768164</v>
       </c>
       <c r="N12">
-        <v>503.4970675021076</v>
+        <v>497.8367742523184</v>
       </c>
       <c r="O12">
-        <v>110.7693548504637</v>
+        <v>109.52409033551</v>
       </c>
       <c r="P12">
-        <v>392.7277126516439</v>
+        <v>388.3126839168083</v>
       </c>
       <c r="Q12">
-        <v>1094.627712651644</v>
+        <v>1090.212683916808</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09021837534316568</v>
+        <v>0.09061641689514829</v>
       </c>
       <c r="T12">
-        <v>0.578920334506051</v>
+        <v>0.5841081502836609</v>
       </c>
       <c r="U12">
         <v>0.07509410488470122</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.89524703549335</v>
+        <v>8.995679123175773</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08709168523578935</v>
+        <v>0.08726989248172287</v>
       </c>
       <c r="C13">
-        <v>6821.509010775806</v>
+        <v>6726.149032507692</v>
       </c>
       <c r="D13">
-        <v>7135.245010775807</v>
+        <v>7115.261032507692</v>
       </c>
       <c r="E13">
-        <v>-439.6639999999999</v>
+        <v>-364.2879999999999</v>
       </c>
       <c r="F13">
-        <v>829.1360000000001</v>
+        <v>904.5120000000001</v>
       </c>
       <c r="G13">
         <v>515.4</v>
@@ -2359,45 +2359,45 @@
         <v>560.1</v>
       </c>
       <c r="M13">
-        <v>62.26322574768164</v>
+        <v>69.28028699747088</v>
       </c>
       <c r="N13">
-        <v>497.8367742523184</v>
+        <v>490.8197130025292</v>
       </c>
       <c r="O13">
-        <v>109.52409033551</v>
+        <v>107.9803368605564</v>
       </c>
       <c r="P13">
-        <v>388.3126839168083</v>
+        <v>382.8393761419728</v>
       </c>
       <c r="Q13">
-        <v>1090.212683916808</v>
+        <v>1084.739376141973</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09061641689514829</v>
+        <v>0.09102350484603958</v>
       </c>
       <c r="T13">
-        <v>0.5841081502836609</v>
+        <v>0.5894138709653074</v>
       </c>
       <c r="U13">
-        <v>0.07509410488470122</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.05857340181006696</v>
+        <v>0.05974340181006696</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>8.995679123175773</v>
+        <v>8.084550804768561</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08726989248172287</v>
+        <v>0.0873193997276564</v>
       </c>
       <c r="C14">
-        <v>6726.149032507692</v>
+        <v>6645.241193581566</v>
       </c>
       <c r="D14">
-        <v>7115.261032507692</v>
+        <v>7109.729193581567</v>
       </c>
       <c r="E14">
-        <v>-364.2879999999999</v>
+        <v>-288.9119999999999</v>
       </c>
       <c r="F14">
-        <v>904.5120000000001</v>
+        <v>979.888</v>
       </c>
       <c r="G14">
         <v>515.4</v>
@@ -2441,28 +2441,28 @@
         <v>560.1</v>
       </c>
       <c r="M14">
-        <v>69.28028699747088</v>
+        <v>75.05364424726012</v>
       </c>
       <c r="N14">
-        <v>490.8197130025292</v>
+        <v>485.0463557527399</v>
       </c>
       <c r="O14">
-        <v>107.9803368605564</v>
+        <v>106.7101982656028</v>
       </c>
       <c r="P14">
-        <v>382.8393761419728</v>
+        <v>378.3361574871371</v>
       </c>
       <c r="Q14">
-        <v>1084.739376141973</v>
+        <v>1080.236157487137</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09102350484603958</v>
+        <v>0.09143995114062953</v>
       </c>
       <c r="T14">
-        <v>0.5894138709653074</v>
+        <v>0.5948415622373364</v>
       </c>
       <c r="U14">
         <v>0.07659410488470123</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.084550804768561</v>
+        <v>7.462662281324825</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0873193997276564</v>
+        <v>0.08736890697358991</v>
       </c>
       <c r="C15">
-        <v>6645.241193581566</v>
+        <v>6564.341949552797</v>
       </c>
       <c r="D15">
-        <v>7109.729193581567</v>
+        <v>7104.205949552797</v>
       </c>
       <c r="E15">
-        <v>-288.9119999999999</v>
+        <v>-213.5359999999998</v>
       </c>
       <c r="F15">
-        <v>979.888</v>
+        <v>1055.264</v>
       </c>
       <c r="G15">
         <v>515.4</v>
@@ -2523,28 +2523,28 @@
         <v>560.1</v>
       </c>
       <c r="M15">
-        <v>75.05364424726012</v>
+        <v>80.82700149704937</v>
       </c>
       <c r="N15">
-        <v>485.0463557527399</v>
+        <v>479.2729985029507</v>
       </c>
       <c r="O15">
-        <v>106.7101982656028</v>
+        <v>105.4400596706491</v>
       </c>
       <c r="P15">
-        <v>378.3361574871371</v>
+        <v>373.8329388323015</v>
       </c>
       <c r="Q15">
-        <v>1080.236157487137</v>
+        <v>1075.732938832301</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09143995114062953</v>
+        <v>0.09186608223276807</v>
       </c>
       <c r="T15">
-        <v>0.5948415622373364</v>
+        <v>0.6003954788877849</v>
       </c>
       <c r="U15">
         <v>0.07659410488470123</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.462662281324825</v>
+        <v>6.929614975515908</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08736890697358991</v>
+        <v>0.08761731421952344</v>
       </c>
       <c r="C16">
-        <v>6564.341949552797</v>
+        <v>6461.381606876657</v>
       </c>
       <c r="D16">
-        <v>7104.205949552797</v>
+        <v>7076.621606876658</v>
       </c>
       <c r="E16">
-        <v>-213.5359999999998</v>
+        <v>-138.1599999999996</v>
       </c>
       <c r="F16">
-        <v>1055.264</v>
+        <v>1130.64</v>
       </c>
       <c r="G16">
         <v>515.4</v>
@@ -2605,45 +2605,45 @@
         <v>560.1</v>
       </c>
       <c r="M16">
-        <v>80.82700149704937</v>
+        <v>88.52244674683861</v>
       </c>
       <c r="N16">
-        <v>479.2729985029507</v>
+        <v>471.5775532531614</v>
       </c>
       <c r="O16">
-        <v>105.4400596706491</v>
+        <v>103.7470617156955</v>
       </c>
       <c r="P16">
-        <v>373.8329388323015</v>
+        <v>367.8304915374659</v>
       </c>
       <c r="Q16">
-        <v>1075.732938832301</v>
+        <v>1069.730491537466</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09186608223276807</v>
+        <v>0.09230223993883929</v>
       </c>
       <c r="T16">
-        <v>0.6003954788877849</v>
+        <v>0.6060800759300086</v>
       </c>
       <c r="U16">
-        <v>0.07659410488470123</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.05974340181006696</v>
+        <v>0.06106940181006695</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.929614975515908</v>
+        <v>6.327208754202253</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08761731421952344</v>
+        <v>0.08768008146545696</v>
       </c>
       <c r="C17">
-        <v>6461.381606876657</v>
+        <v>6379.069496368156</v>
       </c>
       <c r="D17">
-        <v>7076.621606876658</v>
+        <v>7069.685496368156</v>
       </c>
       <c r="E17">
-        <v>-138.1599999999999</v>
+        <v>-62.78399999999988</v>
       </c>
       <c r="F17">
-        <v>1130.64</v>
+        <v>1206.016</v>
       </c>
       <c r="G17">
         <v>515.4</v>
@@ -2687,28 +2687,28 @@
         <v>560.1</v>
       </c>
       <c r="M17">
-        <v>88.5224467468386</v>
+        <v>94.42394319662783</v>
       </c>
       <c r="N17">
-        <v>471.5775532531615</v>
+        <v>465.6760568033722</v>
       </c>
       <c r="O17">
-        <v>103.7470617156955</v>
+        <v>102.4487324967419</v>
       </c>
       <c r="P17">
-        <v>367.8304915374659</v>
+        <v>363.2273243066303</v>
       </c>
       <c r="Q17">
-        <v>1069.730491537466</v>
+        <v>1065.12732430663</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09230223993883929</v>
+        <v>0.09274878235219791</v>
       </c>
       <c r="T17">
-        <v>0.6060800759300086</v>
+        <v>0.6119000205208567</v>
       </c>
       <c r="U17">
         <v>0.07829410488470122</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.327208754202254</v>
+        <v>5.931758207064614</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08768008146545696</v>
+        <v>0.08774284871139049</v>
       </c>
       <c r="C18">
-        <v>6379.069496368156</v>
+        <v>6296.770969324601</v>
       </c>
       <c r="D18">
-        <v>7069.685496368156</v>
+        <v>7062.762969324601</v>
       </c>
       <c r="E18">
-        <v>-62.78399999999988</v>
+        <v>12.5920000000001</v>
       </c>
       <c r="F18">
-        <v>1206.016</v>
+        <v>1281.392</v>
       </c>
       <c r="G18">
         <v>515.4</v>
@@ -2769,28 +2769,28 @@
         <v>560.1</v>
       </c>
       <c r="M18">
-        <v>94.42394319662783</v>
+        <v>100.3254396464171</v>
       </c>
       <c r="N18">
-        <v>465.6760568033722</v>
+        <v>459.774560353583</v>
       </c>
       <c r="O18">
-        <v>102.4487324967419</v>
+        <v>101.1504032777883</v>
       </c>
       <c r="P18">
-        <v>363.2273243066303</v>
+        <v>358.6241570757947</v>
       </c>
       <c r="Q18">
-        <v>1065.12732430663</v>
+        <v>1060.524157075795</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09274878235219791</v>
+        <v>0.09320608482370976</v>
       </c>
       <c r="T18">
-        <v>0.6119000205208567</v>
+        <v>0.6178602047403999</v>
       </c>
       <c r="U18">
         <v>0.07829410488470122</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.931758207064614</v>
+        <v>5.582831253707872</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08774284871139049</v>
+        <v>0.087917935957324</v>
       </c>
       <c r="C19">
-        <v>6296.770969324601</v>
+        <v>6202.156256162879</v>
       </c>
       <c r="D19">
-        <v>7062.762969324601</v>
+        <v>7043.524256162879</v>
       </c>
       <c r="E19">
-        <v>12.5920000000001</v>
+        <v>87.9680000000003</v>
       </c>
       <c r="F19">
-        <v>1281.392</v>
+        <v>1356.768</v>
       </c>
       <c r="G19">
         <v>515.4</v>
@@ -2851,45 +2851,45 @@
         <v>560.1</v>
       </c>
       <c r="M19">
-        <v>100.3254396464171</v>
+        <v>107.3123504962063</v>
       </c>
       <c r="N19">
-        <v>459.774560353583</v>
+        <v>452.7876495037937</v>
       </c>
       <c r="O19">
-        <v>101.1504032777883</v>
+        <v>99.61328289083461</v>
       </c>
       <c r="P19">
-        <v>358.6241570757947</v>
+        <v>353.174366612959</v>
       </c>
       <c r="Q19">
-        <v>1060.524157075795</v>
+        <v>1055.074366612959</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09320608482370976</v>
+        <v>0.09367454101403898</v>
       </c>
       <c r="T19">
-        <v>0.6178602047403999</v>
+        <v>0.6239657593067612</v>
       </c>
       <c r="U19">
-        <v>0.07829410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.06106940181006695</v>
+        <v>0.06169340181006696</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>5.582831253707872</v>
+        <v>5.219343322647662</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.087917935957324</v>
+        <v>0.08798694320325753</v>
       </c>
       <c r="C20">
-        <v>6202.156256162879</v>
+        <v>6119.226454473512</v>
       </c>
       <c r="D20">
-        <v>7043.524256162879</v>
+        <v>7035.970454473512</v>
       </c>
       <c r="E20">
-        <v>87.96800000000007</v>
+        <v>163.3440000000001</v>
       </c>
       <c r="F20">
-        <v>1356.768</v>
+        <v>1432.144</v>
       </c>
       <c r="G20">
         <v>515.4</v>
@@ -2933,28 +2933,28 @@
         <v>560.1</v>
       </c>
       <c r="M20">
-        <v>107.3123504962063</v>
+        <v>113.2741477459955</v>
       </c>
       <c r="N20">
-        <v>452.7876495037937</v>
+        <v>446.8258522540045</v>
       </c>
       <c r="O20">
-        <v>99.61328289083461</v>
+        <v>98.30168749588098</v>
       </c>
       <c r="P20">
-        <v>353.1743666129591</v>
+        <v>348.5241647581235</v>
       </c>
       <c r="Q20">
-        <v>1055.074366612959</v>
+        <v>1050.424164758123</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09367454101403896</v>
+        <v>0.09415456402388248</v>
       </c>
       <c r="T20">
-        <v>0.6239657593067611</v>
+        <v>0.6302220683068598</v>
       </c>
       <c r="U20">
         <v>0.07909410488470123</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.219343322647663</v>
+        <v>4.944641042508312</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08798694320325753</v>
+        <v>0.08805595044919105</v>
       </c>
       <c r="C21">
-        <v>6119.226454473512</v>
+        <v>6036.312837520578</v>
       </c>
       <c r="D21">
-        <v>7035.970454473512</v>
+        <v>7028.432837520579</v>
       </c>
       <c r="E21">
-        <v>163.3440000000001</v>
+        <v>238.7200000000003</v>
       </c>
       <c r="F21">
-        <v>1432.144</v>
+        <v>1507.52</v>
       </c>
       <c r="G21">
         <v>515.4</v>
@@ -3015,28 +3015,28 @@
         <v>560.1</v>
       </c>
       <c r="M21">
-        <v>113.2741477459955</v>
+        <v>119.2359449957848</v>
       </c>
       <c r="N21">
-        <v>446.8258522540045</v>
+        <v>440.8640550042152</v>
       </c>
       <c r="O21">
-        <v>98.30168749588098</v>
+        <v>96.99009210092736</v>
       </c>
       <c r="P21">
-        <v>348.5241647581235</v>
+        <v>343.8739629032879</v>
       </c>
       <c r="Q21">
-        <v>1050.424164758123</v>
+        <v>1045.773962903288</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09415456402388248</v>
+        <v>0.09464658760897207</v>
       </c>
       <c r="T21">
-        <v>0.6302220683068598</v>
+        <v>0.6366347850319609</v>
       </c>
       <c r="U21">
         <v>0.07909410488470123</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.944641042508312</v>
+        <v>4.697408990382896</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08805595044919105</v>
+        <v>0.0881249576951246</v>
       </c>
       <c r="C22">
-        <v>6036.312837520578</v>
+        <v>5953.415353343738</v>
       </c>
       <c r="D22">
-        <v>7028.432837520579</v>
+        <v>7020.911353343739</v>
       </c>
       <c r="E22">
-        <v>238.7200000000003</v>
+        <v>314.0960000000002</v>
       </c>
       <c r="F22">
-        <v>1507.52</v>
+        <v>1582.896</v>
       </c>
       <c r="G22">
         <v>515.4</v>
@@ -3097,28 +3097,28 @@
         <v>560.1</v>
       </c>
       <c r="M22">
-        <v>119.2359449957848</v>
+        <v>125.197742245574</v>
       </c>
       <c r="N22">
-        <v>440.8640550042152</v>
+        <v>434.902257754426</v>
       </c>
       <c r="O22">
-        <v>96.99009210092736</v>
+        <v>95.67849670597371</v>
       </c>
       <c r="P22">
-        <v>343.8739629032879</v>
+        <v>339.2237610484523</v>
       </c>
       <c r="Q22">
-        <v>1045.773962903288</v>
+        <v>1041.123761048452</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09464658760897207</v>
+        <v>0.09515106748735509</v>
       </c>
       <c r="T22">
-        <v>0.6366347850319609</v>
+        <v>0.6432098490159254</v>
       </c>
       <c r="U22">
         <v>0.07909410488470123</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.697408990382896</v>
+        <v>4.47372284798371</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08812495769512457</v>
+        <v>0.08819396494105811</v>
       </c>
       <c r="C23">
-        <v>5953.415353343742</v>
+        <v>5870.533950204852</v>
       </c>
       <c r="D23">
-        <v>7020.911353343742</v>
+        <v>7013.405950204852</v>
       </c>
       <c r="E23">
-        <v>314.096</v>
+        <v>389.4720000000002</v>
       </c>
       <c r="F23">
-        <v>1582.896</v>
+        <v>1658.272</v>
       </c>
       <c r="G23">
         <v>515.4</v>
@@ -3179,28 +3179,28 @@
         <v>560.1</v>
       </c>
       <c r="M23">
-        <v>125.197742245574</v>
+        <v>131.1595394953633</v>
       </c>
       <c r="N23">
-        <v>434.902257754426</v>
+        <v>428.9404605046367</v>
       </c>
       <c r="O23">
-        <v>95.67849670597371</v>
+        <v>94.36690131102009</v>
       </c>
       <c r="P23">
-        <v>339.2237610484523</v>
+        <v>334.5735591936167</v>
       </c>
       <c r="Q23">
-        <v>1041.123761048452</v>
+        <v>1036.473559193617</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09515106748735508</v>
+        <v>0.09566848274723509</v>
       </c>
       <c r="T23">
-        <v>0.6432098490159253</v>
+        <v>0.6499535043840939</v>
       </c>
       <c r="U23">
         <v>0.07909410488470123</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.47372284798371</v>
+        <v>4.270371809438997</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08819396494105811</v>
+        <v>0.08844237218699162</v>
       </c>
       <c r="C24">
-        <v>5870.533950204852</v>
+        <v>5768.272887024945</v>
       </c>
       <c r="D24">
-        <v>7013.405950204852</v>
+        <v>6986.520887024945</v>
       </c>
       <c r="E24">
-        <v>389.4720000000002</v>
+        <v>464.8480000000002</v>
       </c>
       <c r="F24">
-        <v>1658.272</v>
+        <v>1733.648</v>
       </c>
       <c r="G24">
         <v>515.4</v>
@@ -3261,45 +3261,45 @@
         <v>560.1</v>
       </c>
       <c r="M24">
-        <v>131.1595394953633</v>
+        <v>138.8549847451525</v>
       </c>
       <c r="N24">
-        <v>428.9404605046367</v>
+        <v>421.2450152548475</v>
       </c>
       <c r="O24">
-        <v>94.36690131102009</v>
+        <v>92.67390335606645</v>
       </c>
       <c r="P24">
-        <v>334.5735591936167</v>
+        <v>328.5711118987811</v>
       </c>
       <c r="Q24">
-        <v>1036.473559193617</v>
+        <v>1030.471111898781</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09566848274723509</v>
+        <v>0.09619933736451458</v>
       </c>
       <c r="T24">
-        <v>0.6499535043840939</v>
+        <v>0.6568723196319554</v>
       </c>
       <c r="U24">
-        <v>0.07909410488470123</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.06169340181006696</v>
+        <v>0.06247340181006696</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.270371809438997</v>
+        <v>4.033704666980299</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08844237218699162</v>
+        <v>0.08851917943292516</v>
       </c>
       <c r="C25">
-        <v>5768.272887024945</v>
+        <v>5684.625725080169</v>
       </c>
       <c r="D25">
-        <v>6986.520887024945</v>
+        <v>6978.24972508017</v>
       </c>
       <c r="E25">
-        <v>464.8480000000002</v>
+        <v>540.2240000000004</v>
       </c>
       <c r="F25">
-        <v>1733.648</v>
+        <v>1809.024</v>
       </c>
       <c r="G25">
         <v>515.4</v>
@@ -3343,28 +3343,28 @@
         <v>560.1</v>
       </c>
       <c r="M25">
-        <v>138.8549847451525</v>
+        <v>144.8921579949418</v>
       </c>
       <c r="N25">
-        <v>421.2450152548475</v>
+        <v>415.2078420050582</v>
       </c>
       <c r="O25">
-        <v>92.67390335606645</v>
+        <v>91.34572524111282</v>
       </c>
       <c r="P25">
-        <v>328.5711118987811</v>
+        <v>323.8621167639454</v>
       </c>
       <c r="Q25">
-        <v>1030.471111898781</v>
+        <v>1025.762116763945</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09619933736451458</v>
+        <v>0.09674416184014353</v>
       </c>
       <c r="T25">
-        <v>0.6568723196319554</v>
+        <v>0.6639732089652868</v>
       </c>
       <c r="U25">
         <v>0.08009410488470123</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.033704666980299</v>
+        <v>3.865633639189453</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08851917943292516</v>
+        <v>0.08859598667885868</v>
       </c>
       <c r="C26">
-        <v>5684.625725080169</v>
+        <v>5600.998124008524</v>
       </c>
       <c r="D26">
-        <v>6978.24972508017</v>
+        <v>6969.998124008524</v>
       </c>
       <c r="E26">
-        <v>540.2240000000002</v>
+        <v>615.6000000000001</v>
       </c>
       <c r="F26">
-        <v>1809.024</v>
+        <v>1884.4</v>
       </c>
       <c r="G26">
         <v>515.4</v>
@@ -3425,28 +3425,28 @@
         <v>560.1</v>
       </c>
       <c r="M26">
-        <v>144.8921579949418</v>
+        <v>150.929331244731</v>
       </c>
       <c r="N26">
-        <v>415.2078420050583</v>
+        <v>409.170668755269</v>
       </c>
       <c r="O26">
-        <v>91.34572524111283</v>
+        <v>90.01754712615919</v>
       </c>
       <c r="P26">
-        <v>323.8621167639454</v>
+        <v>319.1531216291099</v>
       </c>
       <c r="Q26">
-        <v>1025.762116763945</v>
+        <v>1021.05312162911</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09674416184014353</v>
+        <v>0.09730351496845592</v>
       </c>
       <c r="T26">
-        <v>0.6639732089652868</v>
+        <v>0.671263455347507</v>
       </c>
       <c r="U26">
         <v>0.08009410488470123</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.865633639189454</v>
+        <v>3.711008293621876</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08859598667885868</v>
+        <v>0.08867279392479221</v>
       </c>
       <c r="C27">
-        <v>5600.998124008524</v>
+        <v>5517.390014501272</v>
       </c>
       <c r="D27">
-        <v>6969.998124008524</v>
+        <v>6961.766014501272</v>
       </c>
       <c r="E27">
-        <v>615.6000000000001</v>
+        <v>690.9760000000001</v>
       </c>
       <c r="F27">
-        <v>1884.4</v>
+        <v>1959.776</v>
       </c>
       <c r="G27">
         <v>515.4</v>
@@ -3507,28 +3507,28 @@
         <v>560.1</v>
       </c>
       <c r="M27">
-        <v>150.929331244731</v>
+        <v>156.9665044945203</v>
       </c>
       <c r="N27">
-        <v>409.170668755269</v>
+        <v>403.1334955054798</v>
       </c>
       <c r="O27">
-        <v>90.01754712615919</v>
+        <v>88.68936901120556</v>
       </c>
       <c r="P27">
-        <v>319.1531216291099</v>
+        <v>314.4441264942743</v>
       </c>
       <c r="Q27">
-        <v>1021.05312162911</v>
+        <v>1016.344126494274</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09730351496845592</v>
+        <v>0.09787798574888487</v>
       </c>
       <c r="T27">
-        <v>0.671263455347507</v>
+        <v>0.6787507354157332</v>
       </c>
       <c r="U27">
         <v>0.08009410488470123</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.711008293621876</v>
+        <v>3.56827720540565</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08867279392479221</v>
+        <v>0.08874960117072572</v>
       </c>
       <c r="C28">
-        <v>5517.390014501272</v>
+        <v>5433.801327576733</v>
       </c>
       <c r="D28">
-        <v>6961.766014501272</v>
+        <v>6953.553327576733</v>
       </c>
       <c r="E28">
-        <v>690.9760000000001</v>
+        <v>766.3520000000003</v>
       </c>
       <c r="F28">
-        <v>1959.776</v>
+        <v>2035.152</v>
       </c>
       <c r="G28">
         <v>515.4</v>
@@ -3589,28 +3589,28 @@
         <v>560.1</v>
       </c>
       <c r="M28">
-        <v>156.9665044945203</v>
+        <v>163.0036777443095</v>
       </c>
       <c r="N28">
-        <v>403.1334955054798</v>
+        <v>397.0963222556906</v>
       </c>
       <c r="O28">
-        <v>88.68936901120556</v>
+        <v>87.36119089625193</v>
       </c>
       <c r="P28">
-        <v>314.4441264942743</v>
+        <v>309.7351313594386</v>
       </c>
       <c r="Q28">
-        <v>1016.344126494274</v>
+        <v>1011.635131359439</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09787798574888487</v>
+        <v>0.09846819545480501</v>
       </c>
       <c r="T28">
-        <v>0.6787507354157332</v>
+        <v>0.6864431464447326</v>
       </c>
       <c r="U28">
         <v>0.08009410488470123</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.56827720540565</v>
+        <v>3.436118790390625</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08874960117072572</v>
+        <v>0.08882640841665926</v>
       </c>
       <c r="C29">
-        <v>5433.801327576733</v>
+        <v>5350.231994578338</v>
       </c>
       <c r="D29">
-        <v>6953.553327576733</v>
+        <v>6945.359994578339</v>
       </c>
       <c r="E29">
-        <v>766.3520000000003</v>
+        <v>841.7280000000003</v>
       </c>
       <c r="F29">
-        <v>2035.152</v>
+        <v>2110.528</v>
       </c>
       <c r="G29">
         <v>515.4</v>
@@ -3671,28 +3671,28 @@
         <v>560.1</v>
       </c>
       <c r="M29">
-        <v>163.0036777443095</v>
+        <v>169.0408509940987</v>
       </c>
       <c r="N29">
-        <v>397.0963222556906</v>
+        <v>391.0591490059013</v>
       </c>
       <c r="O29">
-        <v>87.36119089625193</v>
+        <v>86.03301278129828</v>
       </c>
       <c r="P29">
-        <v>309.7351313594386</v>
+        <v>305.026136224603</v>
       </c>
       <c r="Q29">
-        <v>1011.635131359439</v>
+        <v>1006.926136224603</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09846819545480501</v>
+        <v>0.09907479987477849</v>
       </c>
       <c r="T29">
-        <v>0.6864431464447326</v>
+        <v>0.694349235557871</v>
       </c>
       <c r="U29">
         <v>0.08009410488470123</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.436118790390625</v>
+        <v>3.313400262162388</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08882640841665926</v>
+        <v>0.08890321566259278</v>
       </c>
       <c r="C30">
-        <v>5350.231994578338</v>
+        <v>5266.681947172741</v>
       </c>
       <c r="D30">
-        <v>6945.359994578339</v>
+        <v>6937.185947172742</v>
       </c>
       <c r="E30">
-        <v>841.7280000000003</v>
+        <v>917.1040000000005</v>
       </c>
       <c r="F30">
-        <v>2110.528</v>
+        <v>2185.904</v>
       </c>
       <c r="G30">
         <v>515.4</v>
@@ -3753,28 +3753,28 @@
         <v>560.1</v>
       </c>
       <c r="M30">
-        <v>169.0408509940987</v>
+        <v>175.078024243888</v>
       </c>
       <c r="N30">
-        <v>391.0591490059013</v>
+        <v>385.0219757561121</v>
       </c>
       <c r="O30">
-        <v>86.03301278129828</v>
+        <v>84.70483466634465</v>
       </c>
       <c r="P30">
-        <v>305.026136224603</v>
+        <v>300.3171410897674</v>
       </c>
       <c r="Q30">
-        <v>1006.926136224603</v>
+        <v>1002.217141089767</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09907479987477849</v>
+        <v>0.09969849174320192</v>
       </c>
       <c r="T30">
-        <v>0.694349235557871</v>
+        <v>0.7024780314065907</v>
       </c>
       <c r="U30">
         <v>0.08009410488470123</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.313400262162388</v>
+        <v>3.199145080708513</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08890321566259277</v>
+        <v>0.08898002290852629</v>
       </c>
       <c r="C31">
-        <v>5266.681947172743</v>
+        <v>5183.151117347901</v>
       </c>
       <c r="D31">
-        <v>6937.185947172744</v>
+        <v>6929.031117347901</v>
       </c>
       <c r="E31">
-        <v>917.104</v>
+        <v>992.4800000000002</v>
       </c>
       <c r="F31">
-        <v>2185.904</v>
+        <v>2261.28</v>
       </c>
       <c r="G31">
         <v>515.4</v>
@@ -3835,28 +3835,28 @@
         <v>560.1</v>
       </c>
       <c r="M31">
-        <v>175.078024243888</v>
+        <v>181.1151974936772</v>
       </c>
       <c r="N31">
-        <v>385.0219757561121</v>
+        <v>378.9848025063228</v>
       </c>
       <c r="O31">
-        <v>84.70483466634465</v>
+        <v>83.37665655139102</v>
       </c>
       <c r="P31">
-        <v>300.3171410897674</v>
+        <v>295.6081459549318</v>
       </c>
       <c r="Q31">
-        <v>1002.217141089767</v>
+        <v>997.5081459549317</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09969849174320192</v>
+        <v>0.1003400033792946</v>
       </c>
       <c r="T31">
-        <v>0.7024780314065907</v>
+        <v>0.7108390785652737</v>
       </c>
       <c r="U31">
         <v>0.08009410488470123</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.199145080708513</v>
+        <v>3.092506911351563</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08898002290852629</v>
+        <v>0.08966133015445983</v>
       </c>
       <c r="C32">
-        <v>5183.151117347901</v>
+        <v>5036.269556618648</v>
       </c>
       <c r="D32">
-        <v>6929.031117347901</v>
+        <v>6857.525556618649</v>
       </c>
       <c r="E32">
-        <v>992.4800000000002</v>
+        <v>1067.856</v>
       </c>
       <c r="F32">
-        <v>2261.28</v>
+        <v>2336.656</v>
       </c>
       <c r="G32">
         <v>515.4</v>
@@ -3917,45 +3917,45 @@
         <v>560.1</v>
       </c>
       <c r="M32">
-        <v>181.1151974936772</v>
+        <v>192.9940107434664</v>
       </c>
       <c r="N32">
-        <v>378.9848025063228</v>
+        <v>367.1059892565336</v>
       </c>
       <c r="O32">
-        <v>83.37665655139102</v>
+        <v>80.76331763643739</v>
       </c>
       <c r="P32">
-        <v>295.6081459549318</v>
+        <v>286.3426716200962</v>
       </c>
       <c r="Q32">
-        <v>997.5081459549317</v>
+        <v>988.2426716200962</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1003400033792946</v>
+        <v>0.1010001095555639</v>
       </c>
       <c r="T32">
-        <v>0.7108390785652737</v>
+        <v>0.7194424749169622</v>
       </c>
       <c r="U32">
-        <v>0.08009410488470123</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V32">
         <v>0.22</v>
       </c>
       <c r="W32">
-        <v>0.06247340181006696</v>
+        <v>0.06442340181006696</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.092506911351563</v>
+        <v>2.902162599980898</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08966133015445983</v>
+        <v>0.08975763740039336</v>
       </c>
       <c r="C33">
-        <v>5036.269556618648</v>
+        <v>4950.904657509687</v>
       </c>
       <c r="D33">
-        <v>6857.525556618649</v>
+        <v>6847.536657509688</v>
       </c>
       <c r="E33">
-        <v>1067.856</v>
+        <v>1143.232</v>
       </c>
       <c r="F33">
-        <v>2336.656</v>
+        <v>2412.032</v>
       </c>
       <c r="G33">
         <v>515.4</v>
@@ -3999,28 +3999,28 @@
         <v>560.1</v>
       </c>
       <c r="M33">
-        <v>192.9940107434664</v>
+        <v>199.2196239932557</v>
       </c>
       <c r="N33">
-        <v>367.1059892565336</v>
+        <v>360.8803760067443</v>
       </c>
       <c r="O33">
-        <v>80.76331763643739</v>
+        <v>79.39368272148376</v>
       </c>
       <c r="P33">
-        <v>286.3426716200962</v>
+        <v>281.4866932852606</v>
       </c>
       <c r="Q33">
-        <v>988.2426716200962</v>
+        <v>983.3866932852605</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1010001095555639</v>
+        <v>0.1016796306193705</v>
       </c>
       <c r="T33">
-        <v>0.7194424749169622</v>
+        <v>0.7282989123378181</v>
       </c>
       <c r="U33">
         <v>0.08259410488470123</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.902162599980898</v>
+        <v>2.811470018731495</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08975763740039336</v>
+        <v>0.08985394464632687</v>
       </c>
       <c r="C34">
-        <v>4950.904657509687</v>
+        <v>4865.568816397199</v>
       </c>
       <c r="D34">
-        <v>6847.536657509688</v>
+        <v>6837.5768163972</v>
       </c>
       <c r="E34">
-        <v>1143.232</v>
+        <v>1218.608</v>
       </c>
       <c r="F34">
-        <v>2412.032</v>
+        <v>2487.408</v>
       </c>
       <c r="G34">
         <v>515.4</v>
@@ -4081,28 +4081,28 @@
         <v>560.1</v>
       </c>
       <c r="M34">
-        <v>199.2196239932557</v>
+        <v>205.4452372430449</v>
       </c>
       <c r="N34">
-        <v>360.8803760067443</v>
+        <v>354.6547627569551</v>
       </c>
       <c r="O34">
-        <v>79.39368272148376</v>
+        <v>78.02404780653011</v>
       </c>
       <c r="P34">
-        <v>281.4866932852606</v>
+        <v>276.6307149504249</v>
       </c>
       <c r="Q34">
-        <v>983.3866932852605</v>
+        <v>978.5307149504249</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1016796306193705</v>
+        <v>0.102379435894037</v>
       </c>
       <c r="T34">
-        <v>0.7282989123378181</v>
+        <v>0.7374197210249679</v>
       </c>
       <c r="U34">
         <v>0.08259410488470123</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.811470018731495</v>
+        <v>2.726273957557813</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08985394464632687</v>
+        <v>0.08995025189226039</v>
       </c>
       <c r="C35">
-        <v>4865.568816397199</v>
+        <v>4780.261906669512</v>
       </c>
       <c r="D35">
-        <v>6837.5768163972</v>
+        <v>6827.645906669512</v>
       </c>
       <c r="E35">
-        <v>1218.608</v>
+        <v>1293.984</v>
       </c>
       <c r="F35">
-        <v>2487.408</v>
+        <v>2562.784</v>
       </c>
       <c r="G35">
         <v>515.4</v>
@@ -4163,28 +4163,28 @@
         <v>560.1</v>
       </c>
       <c r="M35">
-        <v>205.4452372430449</v>
+        <v>211.6708504928342</v>
       </c>
       <c r="N35">
-        <v>354.6547627569551</v>
+        <v>348.4291495071658</v>
       </c>
       <c r="O35">
-        <v>78.02404780653011</v>
+        <v>76.65441289157648</v>
       </c>
       <c r="P35">
-        <v>276.6307149504249</v>
+        <v>271.7747366155893</v>
       </c>
       <c r="Q35">
-        <v>978.5307149504249</v>
+        <v>973.6747366155894</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.102379435894037</v>
+        <v>0.1031004473891479</v>
       </c>
       <c r="T35">
-        <v>0.7374197210249679</v>
+        <v>0.7468169178541527</v>
       </c>
       <c r="U35">
         <v>0.08259410488470123</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.726273957557813</v>
+        <v>2.646089429394348</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08995025189226039</v>
+        <v>0.09004655913819393</v>
       </c>
       <c r="C36">
-        <v>4780.261906669512</v>
+        <v>4694.983802449449</v>
       </c>
       <c r="D36">
-        <v>6827.645906669512</v>
+        <v>6817.74380244945</v>
       </c>
       <c r="E36">
-        <v>1293.984</v>
+        <v>1369.36</v>
       </c>
       <c r="F36">
-        <v>2562.784</v>
+        <v>2638.16</v>
       </c>
       <c r="G36">
         <v>515.4</v>
@@ -4245,28 +4245,28 @@
         <v>560.1</v>
       </c>
       <c r="M36">
-        <v>211.6708504928342</v>
+        <v>217.8964637426234</v>
       </c>
       <c r="N36">
-        <v>348.4291495071658</v>
+        <v>342.2035362573766</v>
       </c>
       <c r="O36">
-        <v>76.65441289157648</v>
+        <v>75.28477797662286</v>
       </c>
       <c r="P36">
-        <v>271.7747366155893</v>
+        <v>266.9187582807538</v>
       </c>
       <c r="Q36">
-        <v>973.6747366155894</v>
+        <v>968.8187582807537</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1031004473891479</v>
+        <v>0.1038436438533392</v>
       </c>
       <c r="T36">
-        <v>0.7468169178541527</v>
+        <v>0.7565032592011587</v>
       </c>
       <c r="U36">
         <v>0.08259410488470123</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.646089429394348</v>
+        <v>2.570486874268796</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09004655913819393</v>
+        <v>0.09112566638412745</v>
       </c>
       <c r="C37">
-        <v>4694.983802449449</v>
+        <v>4510.588819409522</v>
       </c>
       <c r="D37">
-        <v>6817.74380244945</v>
+        <v>6708.724819409523</v>
       </c>
       <c r="E37">
-        <v>1369.36</v>
+        <v>1444.736000000001</v>
       </c>
       <c r="F37">
-        <v>2638.16</v>
+        <v>2713.536000000001</v>
       </c>
       <c r="G37">
         <v>515.4</v>
@@ -4327,45 +4327,45 @@
         <v>560.1</v>
       </c>
       <c r="M37">
-        <v>217.8964637426234</v>
+        <v>233.6194529924126</v>
       </c>
       <c r="N37">
-        <v>342.2035362573766</v>
+        <v>326.4805470075873</v>
       </c>
       <c r="O37">
-        <v>75.28477797662286</v>
+        <v>71.82572034166921</v>
       </c>
       <c r="P37">
-        <v>266.9187582807538</v>
+        <v>254.6548266659181</v>
       </c>
       <c r="Q37">
-        <v>968.8187582807537</v>
+        <v>956.5548266659181</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1038436438533392</v>
+        <v>0.1046100652070365</v>
       </c>
       <c r="T37">
-        <v>0.7565032592011587</v>
+        <v>0.7664922987152585</v>
       </c>
       <c r="U37">
-        <v>0.08259410488470123</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V37">
         <v>0.22</v>
       </c>
       <c r="W37">
-        <v>0.06442340181006696</v>
+        <v>0.06715340181006696</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.570486874268796</v>
+        <v>2.397488705780809</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09112566638412745</v>
+        <v>0.09124927363006097</v>
       </c>
       <c r="C38">
-        <v>4510.588819409522</v>
+        <v>4422.947298303839</v>
       </c>
       <c r="D38">
-        <v>6708.724819409523</v>
+        <v>6696.459298303839</v>
       </c>
       <c r="E38">
-        <v>1444.736</v>
+        <v>1520.112</v>
       </c>
       <c r="F38">
-        <v>2713.536</v>
+        <v>2788.912</v>
       </c>
       <c r="G38">
         <v>515.4</v>
@@ -4409,28 +4409,28 @@
         <v>560.1</v>
       </c>
       <c r="M38">
-        <v>233.6194529924126</v>
+        <v>240.1088822422019</v>
       </c>
       <c r="N38">
-        <v>326.4805470075874</v>
+        <v>319.9911177577982</v>
       </c>
       <c r="O38">
-        <v>71.82572034166922</v>
+        <v>70.39804590671559</v>
       </c>
       <c r="P38">
-        <v>254.6548266659182</v>
+        <v>249.5930718510826</v>
       </c>
       <c r="Q38">
-        <v>956.5548266659182</v>
+        <v>951.4930718510825</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1046100652070365</v>
+        <v>0.105400817397359</v>
       </c>
       <c r="T38">
-        <v>0.7664922987152584</v>
+        <v>0.7767984505948852</v>
       </c>
       <c r="U38">
         <v>0.08609410488470122</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.39748870578081</v>
+        <v>2.33269171373268</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09124927363006097</v>
+        <v>0.09137288087599449</v>
       </c>
       <c r="C39">
-        <v>4422.947298303839</v>
+        <v>4335.350545305346</v>
       </c>
       <c r="D39">
-        <v>6696.459298303839</v>
+        <v>6684.238545305346</v>
       </c>
       <c r="E39">
-        <v>1520.112</v>
+        <v>1595.488</v>
       </c>
       <c r="F39">
-        <v>2788.912</v>
+        <v>2864.288</v>
       </c>
       <c r="G39">
         <v>515.4</v>
@@ -4491,28 +4491,28 @@
         <v>560.1</v>
       </c>
       <c r="M39">
-        <v>240.1088822422019</v>
+        <v>246.5983114919911</v>
       </c>
       <c r="N39">
-        <v>319.9911177577982</v>
+        <v>313.5016885080089</v>
       </c>
       <c r="O39">
-        <v>70.39804590671559</v>
+        <v>68.97037147176196</v>
       </c>
       <c r="P39">
-        <v>249.5930718510826</v>
+        <v>244.5313170362469</v>
       </c>
       <c r="Q39">
-        <v>951.4930718510825</v>
+        <v>946.4313170362469</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.105400817397359</v>
+        <v>0.1062170777228533</v>
       </c>
       <c r="T39">
-        <v>0.7767984505948852</v>
+        <v>0.787437058986758</v>
       </c>
       <c r="U39">
         <v>0.08609410488470122</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.33269171373268</v>
+        <v>2.271305089687083</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09137288087599449</v>
+        <v>0.09234824812192802</v>
       </c>
       <c r="C40">
-        <v>4335.350545305346</v>
+        <v>4165.084759886851</v>
       </c>
       <c r="D40">
-        <v>6684.238545305346</v>
+        <v>6589.348759886852</v>
       </c>
       <c r="E40">
-        <v>1595.488</v>
+        <v>1670.864</v>
       </c>
       <c r="F40">
-        <v>2864.288</v>
+        <v>2939.664</v>
       </c>
       <c r="G40">
         <v>515.4</v>
@@ -4573,45 +4573,45 @@
         <v>560.1</v>
       </c>
       <c r="M40">
-        <v>246.5983114919911</v>
+        <v>261.3187999417804</v>
       </c>
       <c r="N40">
-        <v>313.5016885080089</v>
+        <v>298.7812000582197</v>
       </c>
       <c r="O40">
-        <v>68.97037147176196</v>
+        <v>65.73186401280833</v>
       </c>
       <c r="P40">
-        <v>244.5313170362469</v>
+        <v>233.0493360454113</v>
       </c>
       <c r="Q40">
-        <v>946.4313170362469</v>
+        <v>934.9493360454113</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1062170777228533</v>
+        <v>0.1070601006819703</v>
       </c>
       <c r="T40">
-        <v>0.787437058986758</v>
+        <v>0.7984244742111513</v>
       </c>
       <c r="U40">
-        <v>0.08609410488470122</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V40">
         <v>0.22</v>
       </c>
       <c r="W40">
-        <v>0.06715340181006696</v>
+        <v>0.06933740181006696</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.271305089687083</v>
+        <v>2.143358993401109</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09234824812192802</v>
+        <v>0.09249369536786155</v>
       </c>
       <c r="C41">
-        <v>4165.084759886851</v>
+        <v>4075.789089304499</v>
       </c>
       <c r="D41">
-        <v>6589.348759886852</v>
+        <v>6575.4290893045</v>
       </c>
       <c r="E41">
-        <v>1670.864</v>
+        <v>1746.24</v>
       </c>
       <c r="F41">
-        <v>2939.664</v>
+        <v>3015.04</v>
       </c>
       <c r="G41">
         <v>515.4</v>
@@ -4655,28 +4655,28 @@
         <v>560.1</v>
       </c>
       <c r="M41">
-        <v>261.3187999417804</v>
+        <v>268.0192819915696</v>
       </c>
       <c r="N41">
-        <v>298.7812000582197</v>
+        <v>292.0807180084304</v>
       </c>
       <c r="O41">
-        <v>65.73186401280833</v>
+        <v>64.25775796185468</v>
       </c>
       <c r="P41">
-        <v>233.0493360454113</v>
+        <v>227.8229600465757</v>
       </c>
       <c r="Q41">
-        <v>934.9493360454113</v>
+        <v>929.7229600465757</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1070601006819703</v>
+        <v>0.1079312244063913</v>
       </c>
       <c r="T41">
-        <v>0.7984244742111513</v>
+        <v>0.8097781366096909</v>
       </c>
       <c r="U41">
         <v>0.08889410488470123</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.143358993401109</v>
+        <v>2.089775018566081</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09249369536786155</v>
+        <v>0.09263914261379508</v>
       </c>
       <c r="C42">
-        <v>4075.789089304499</v>
+        <v>3986.552103972082</v>
       </c>
       <c r="D42">
-        <v>6575.4290893045</v>
+        <v>6561.568103972083</v>
       </c>
       <c r="E42">
-        <v>1746.24</v>
+        <v>1821.616</v>
       </c>
       <c r="F42">
-        <v>3015.04</v>
+        <v>3090.416</v>
       </c>
       <c r="G42">
         <v>515.4</v>
@@ -4737,28 +4737,28 @@
         <v>560.1</v>
       </c>
       <c r="M42">
-        <v>268.0192819915696</v>
+        <v>274.7197640413589</v>
       </c>
       <c r="N42">
-        <v>292.0807180084304</v>
+        <v>285.3802359586412</v>
       </c>
       <c r="O42">
-        <v>64.25775796185468</v>
+        <v>62.78365191090106</v>
       </c>
       <c r="P42">
-        <v>227.8229600465757</v>
+        <v>222.5965840477401</v>
       </c>
       <c r="Q42">
-        <v>929.7229600465757</v>
+        <v>924.49658404774</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1079312244063913</v>
+        <v>0.1088318777485892</v>
       </c>
       <c r="T42">
-        <v>0.8097781366096909</v>
+        <v>0.8215166689200455</v>
       </c>
       <c r="U42">
         <v>0.08889410488470123</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.089775018566081</v>
+        <v>2.03880489616203</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09263914261379508</v>
+        <v>0.09533986985972859</v>
       </c>
       <c r="C43">
-        <v>3986.552103972082</v>
+        <v>3664.016274008398</v>
       </c>
       <c r="D43">
-        <v>6561.568103972083</v>
+        <v>6314.408274008399</v>
       </c>
       <c r="E43">
-        <v>1821.616</v>
+        <v>1896.992</v>
       </c>
       <c r="F43">
-        <v>3090.416</v>
+        <v>3165.792</v>
       </c>
       <c r="G43">
         <v>515.4</v>
@@ -4819,45 +4819,45 @@
         <v>560.1</v>
       </c>
       <c r="M43">
-        <v>274.7197640413589</v>
+        <v>306.1134236911481</v>
       </c>
       <c r="N43">
-        <v>285.3802359586412</v>
+        <v>253.9865763088519</v>
       </c>
       <c r="O43">
-        <v>62.78365191090106</v>
+        <v>55.87704678794742</v>
       </c>
       <c r="P43">
-        <v>222.5965840477401</v>
+        <v>198.1095295209045</v>
       </c>
       <c r="Q43">
-        <v>924.49658404774</v>
+        <v>900.0095295209045</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1088318777485892</v>
+        <v>0.109763588102587</v>
       </c>
       <c r="T43">
-        <v>0.8215166689200455</v>
+        <v>0.8336599782066192</v>
       </c>
       <c r="U43">
-        <v>0.08889410488470123</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V43">
         <v>0.22</v>
       </c>
       <c r="W43">
-        <v>0.06933740181006696</v>
+        <v>0.07542140181006696</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.03880489616203</v>
+        <v>1.829713944740661</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0953398698597286</v>
+        <v>0.09554615710566211</v>
       </c>
       <c r="C44">
-        <v>3664.016274008398</v>
+        <v>3570.524920087389</v>
       </c>
       <c r="D44">
-        <v>6314.408274008399</v>
+        <v>6296.29292008739</v>
       </c>
       <c r="E44">
-        <v>1896.992</v>
+        <v>1972.368</v>
       </c>
       <c r="F44">
-        <v>3165.792</v>
+        <v>3241.168</v>
       </c>
       <c r="G44">
         <v>515.4</v>
@@ -4901,28 +4901,28 @@
         <v>560.1</v>
       </c>
       <c r="M44">
-        <v>306.1134236911481</v>
+        <v>313.4018385409373</v>
       </c>
       <c r="N44">
-        <v>253.986576308852</v>
+        <v>246.6981614590627</v>
       </c>
       <c r="O44">
-        <v>55.87704678794744</v>
+        <v>54.27359552099379</v>
       </c>
       <c r="P44">
-        <v>198.1095295209045</v>
+        <v>192.4245659380689</v>
       </c>
       <c r="Q44">
-        <v>900.0095295209045</v>
+        <v>894.3245659380689</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.109763588102587</v>
+        <v>0.1107279900479532</v>
       </c>
       <c r="T44">
-        <v>0.8336599782066192</v>
+        <v>0.8462293685207919</v>
       </c>
       <c r="U44">
         <v>0.09669410488470123</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.829713944740662</v>
+        <v>1.78716245765367</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09554615710566211</v>
+        <v>0.09709092435159565</v>
       </c>
       <c r="C45">
-        <v>3570.524920087389</v>
+        <v>3362.727447945727</v>
       </c>
       <c r="D45">
-        <v>6296.29292008739</v>
+        <v>6163.871447945728</v>
       </c>
       <c r="E45">
-        <v>1972.368</v>
+        <v>2047.744</v>
       </c>
       <c r="F45">
-        <v>3241.168</v>
+        <v>3316.544</v>
       </c>
       <c r="G45">
         <v>515.4</v>
@@ -4983,45 +4983,45 @@
         <v>560.1</v>
       </c>
       <c r="M45">
-        <v>313.4018385409373</v>
+        <v>333.6247749907266</v>
       </c>
       <c r="N45">
-        <v>246.6981614590627</v>
+        <v>226.4752250092735</v>
       </c>
       <c r="O45">
-        <v>54.27359552099379</v>
+        <v>49.82454950204016</v>
       </c>
       <c r="P45">
-        <v>192.4245659380689</v>
+        <v>176.6506755072333</v>
       </c>
       <c r="Q45">
-        <v>894.3245659380689</v>
+        <v>878.5506755072333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1107279900479532</v>
+        <v>0.1117268349199396</v>
       </c>
       <c r="T45">
-        <v>0.8462293685207919</v>
+        <v>0.8592476656318995</v>
       </c>
       <c r="U45">
-        <v>0.09669410488470123</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V45">
         <v>0.22</v>
       </c>
       <c r="W45">
-        <v>0.07542140181006696</v>
+        <v>0.07846340181006696</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y45">
-        <v>1.78716245765367</v>
+        <v>1.678832155122678</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09709092435159565</v>
+        <v>0.09732763159752916</v>
       </c>
       <c r="C46">
-        <v>3362.727447945727</v>
+        <v>3267.550854679342</v>
       </c>
       <c r="D46">
-        <v>6163.871447945728</v>
+        <v>6144.070854679342</v>
       </c>
       <c r="E46">
-        <v>2047.744</v>
+        <v>2123.12</v>
       </c>
       <c r="F46">
-        <v>3316.544</v>
+        <v>3391.92</v>
       </c>
       <c r="G46">
         <v>515.4</v>
@@ -5065,28 +5065,28 @@
         <v>560.1</v>
       </c>
       <c r="M46">
-        <v>333.6247749907266</v>
+        <v>341.2071562405158</v>
       </c>
       <c r="N46">
-        <v>226.4752250092735</v>
+        <v>218.8928437594843</v>
       </c>
       <c r="O46">
-        <v>49.82454950204016</v>
+        <v>48.15642562708654</v>
       </c>
       <c r="P46">
-        <v>176.6506755072333</v>
+        <v>170.7364181323977</v>
       </c>
       <c r="Q46">
-        <v>878.5506755072333</v>
+        <v>872.6364181323977</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1117268349199396</v>
+        <v>0.1127620014236346</v>
       </c>
       <c r="T46">
-        <v>0.8592476656318995</v>
+        <v>0.8727393553652291</v>
       </c>
       <c r="U46">
         <v>0.1005941048847012</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.678832155122678</v>
+        <v>1.64152477389773</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09732763159752916</v>
+        <v>0.09756433884346269</v>
       </c>
       <c r="C47">
-        <v>3267.550854679342</v>
+        <v>3172.501067456706</v>
       </c>
       <c r="D47">
-        <v>6144.070854679342</v>
+        <v>6124.397067456706</v>
       </c>
       <c r="E47">
-        <v>2123.12</v>
+        <v>2198.496</v>
       </c>
       <c r="F47">
-        <v>3391.92</v>
+        <v>3467.296</v>
       </c>
       <c r="G47">
         <v>515.4</v>
@@ -5147,28 +5147,28 @@
         <v>560.1</v>
       </c>
       <c r="M47">
-        <v>341.2071562405158</v>
+        <v>348.789537490305</v>
       </c>
       <c r="N47">
-        <v>218.8928437594843</v>
+        <v>211.310462509695</v>
       </c>
       <c r="O47">
-        <v>48.15642562708654</v>
+        <v>46.48830175213291</v>
       </c>
       <c r="P47">
-        <v>170.7364181323977</v>
+        <v>164.8221607575621</v>
       </c>
       <c r="Q47">
-        <v>872.6364181323977</v>
+        <v>866.7221607575621</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1127620014236346</v>
+        <v>0.1138355074274665</v>
       </c>
       <c r="T47">
-        <v>0.8727393553652291</v>
+        <v>0.8867307373109041</v>
       </c>
       <c r="U47">
         <v>0.1005941048847012</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.64152477389773</v>
+        <v>1.60583945272604</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09756433884346269</v>
+        <v>0.09780104608939622</v>
       </c>
       <c r="C48">
-        <v>3172.501067456706</v>
+        <v>3077.576872037809</v>
       </c>
       <c r="D48">
-        <v>6124.397067456706</v>
+        <v>6104.84887203781</v>
       </c>
       <c r="E48">
-        <v>2198.496</v>
+        <v>2273.872</v>
       </c>
       <c r="F48">
-        <v>3467.296</v>
+        <v>3542.672</v>
       </c>
       <c r="G48">
         <v>515.4</v>
@@ -5229,28 +5229,28 @@
         <v>560.1</v>
       </c>
       <c r="M48">
-        <v>348.789537490305</v>
+        <v>356.3719187400943</v>
       </c>
       <c r="N48">
-        <v>211.310462509695</v>
+        <v>203.7280812599058</v>
       </c>
       <c r="O48">
-        <v>46.48830175213291</v>
+        <v>44.82017787717927</v>
       </c>
       <c r="P48">
-        <v>164.8221607575621</v>
+        <v>158.9079033827265</v>
       </c>
       <c r="Q48">
-        <v>866.7221607575621</v>
+        <v>860.8079033827264</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1138355074274665</v>
+        <v>0.1149495230918203</v>
       </c>
       <c r="T48">
-        <v>0.8867307373109041</v>
+        <v>0.9012500959337747</v>
       </c>
       <c r="U48">
         <v>0.1005941048847012</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.60583945272604</v>
+        <v>1.571672655859528</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09780104608939622</v>
+        <v>0.09803775333532974</v>
       </c>
       <c r="C49">
-        <v>3077.576872037809</v>
+        <v>2982.777069636032</v>
       </c>
       <c r="D49">
-        <v>6104.84887203781</v>
+        <v>6085.425069636033</v>
       </c>
       <c r="E49">
-        <v>2273.872</v>
+        <v>2349.248000000001</v>
       </c>
       <c r="F49">
-        <v>3542.672</v>
+        <v>3618.048000000001</v>
       </c>
       <c r="G49">
         <v>515.4</v>
@@ -5311,28 +5311,28 @@
         <v>560.1</v>
       </c>
       <c r="M49">
-        <v>356.3719187400943</v>
+        <v>363.9542999898836</v>
       </c>
       <c r="N49">
-        <v>203.7280812599058</v>
+        <v>196.1457000101165</v>
       </c>
       <c r="O49">
-        <v>44.82017787717927</v>
+        <v>43.15205400222562</v>
       </c>
       <c r="P49">
-        <v>158.9079033827265</v>
+        <v>152.9936460078908</v>
       </c>
       <c r="Q49">
-        <v>860.8079033827264</v>
+        <v>854.8936460078908</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1149495230918203</v>
+        <v>0.1161063855124954</v>
       </c>
       <c r="T49">
-        <v>0.9012500959337747</v>
+        <v>0.9163278914267555</v>
       </c>
       <c r="U49">
         <v>0.1005941048847012</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.571672655859528</v>
+        <v>1.538929475529121</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09803775333532974</v>
+        <v>0.09827446058126325</v>
       </c>
       <c r="C50">
-        <v>2982.777069636033</v>
+        <v>2888.100476673092</v>
       </c>
       <c r="D50">
-        <v>6085.425069636033</v>
+        <v>6066.124476673092</v>
       </c>
       <c r="E50">
-        <v>2349.248000000001</v>
+        <v>2424.624</v>
       </c>
       <c r="F50">
-        <v>3618.048</v>
+        <v>3693.424</v>
       </c>
       <c r="G50">
         <v>515.4</v>
@@ -5393,28 +5393,28 @@
         <v>560.1</v>
       </c>
       <c r="M50">
-        <v>363.9542999898835</v>
+        <v>371.5366812396727</v>
       </c>
       <c r="N50">
-        <v>196.1457000101165</v>
+        <v>188.5633187603273</v>
       </c>
       <c r="O50">
-        <v>43.15205400222563</v>
+        <v>41.48393012727201</v>
       </c>
       <c r="P50">
-        <v>152.9936460078909</v>
+        <v>147.0793886330553</v>
       </c>
       <c r="Q50">
-        <v>854.8936460078909</v>
+        <v>848.9793886330554</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1161063855124954</v>
+        <v>0.1173086150869224</v>
       </c>
       <c r="T50">
-        <v>0.9163278914267554</v>
+        <v>0.9319969730175003</v>
       </c>
       <c r="U50">
         <v>0.1005941048847012</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.538929475529122</v>
+        <v>1.507522751538731</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09827446058126325</v>
+        <v>0.1040491678271968</v>
       </c>
       <c r="C51">
-        <v>2888.100476673092</v>
+        <v>2377.069422753841</v>
       </c>
       <c r="D51">
-        <v>6066.124476673092</v>
+        <v>5630.469422753841</v>
       </c>
       <c r="E51">
-        <v>2424.624</v>
+        <v>2500</v>
       </c>
       <c r="F51">
-        <v>3693.424</v>
+        <v>3768.8</v>
       </c>
       <c r="G51">
         <v>515.4</v>
@@ -5475,45 +5475,45 @@
         <v>560.1</v>
       </c>
       <c r="M51">
-        <v>371.5366812396727</v>
+        <v>432.6360224894621</v>
       </c>
       <c r="N51">
-        <v>188.5633187603273</v>
+        <v>127.463977510538</v>
       </c>
       <c r="O51">
-        <v>41.48393012727201</v>
+        <v>28.04207505231835</v>
       </c>
       <c r="P51">
-        <v>147.0793886330553</v>
+        <v>99.42190245821962</v>
       </c>
       <c r="Q51">
-        <v>848.9793886330554</v>
+        <v>801.3219024582196</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1173086150869224</v>
+        <v>0.1185589338443266</v>
       </c>
       <c r="T51">
-        <v>0.9319969730175003</v>
+        <v>0.9482928178718749</v>
       </c>
       <c r="U51">
-        <v>0.1005941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V51">
         <v>0.22</v>
       </c>
       <c r="W51">
-        <v>0.07846340181006696</v>
+        <v>0.08953940181006696</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.507522751538731</v>
+        <v>1.294621739486898</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1040491678271968</v>
+        <v>0.1043966350731303</v>
       </c>
       <c r="C52">
-        <v>2377.069422753841</v>
+        <v>2277.467113014833</v>
       </c>
       <c r="D52">
-        <v>5630.469422753841</v>
+        <v>5606.243113014833</v>
       </c>
       <c r="E52">
-        <v>2500</v>
+        <v>2575.376</v>
       </c>
       <c r="F52">
-        <v>3768.8</v>
+        <v>3844.176</v>
       </c>
       <c r="G52">
         <v>515.4</v>
@@ -5557,28 +5557,28 @@
         <v>560.1</v>
       </c>
       <c r="M52">
-        <v>432.6360224894621</v>
+        <v>441.2887429392513</v>
       </c>
       <c r="N52">
-        <v>127.463977510538</v>
+        <v>118.8112570607487</v>
       </c>
       <c r="O52">
-        <v>28.04207505231835</v>
+        <v>26.13847655336473</v>
       </c>
       <c r="P52">
-        <v>99.42190245821962</v>
+        <v>92.67278050738402</v>
       </c>
       <c r="Q52">
-        <v>801.3219024582196</v>
+        <v>794.572780507384</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1185589338443266</v>
+        <v>0.1198602860204003</v>
       </c>
       <c r="T52">
-        <v>0.9482928178718749</v>
+        <v>0.9652537992509179</v>
       </c>
       <c r="U52">
         <v>0.1147941048847012</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.294621739486898</v>
+        <v>1.269236999496959</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1043966350731303</v>
+        <v>0.1164170503665526</v>
       </c>
       <c r="C53">
-        <v>2277.467113014833</v>
+        <v>1475.722725858248</v>
       </c>
       <c r="D53">
-        <v>5606.243113014833</v>
+        <v>4879.874725858249</v>
       </c>
       <c r="E53">
-        <v>2575.376</v>
+        <v>2650.752</v>
       </c>
       <c r="F53">
-        <v>3844.176</v>
+        <v>3919.552</v>
       </c>
       <c r="G53">
         <v>515.4</v>
@@ -5639,45 +5639,45 @@
         <v>560.1</v>
       </c>
       <c r="M53">
-        <v>441.2887429392513</v>
+        <v>562.0406505890405</v>
       </c>
       <c r="N53">
-        <v>118.8112570607487</v>
+        <v>-1.940650589040501</v>
       </c>
       <c r="O53">
-        <v>26.13847655336473</v>
+        <v>-0.4269431295889103</v>
       </c>
       <c r="P53">
-        <v>92.67278050738402</v>
+        <v>-1.513707459451591</v>
       </c>
       <c r="Q53">
-        <v>794.572780507384</v>
+        <v>700.3862925405484</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1198602860204003</v>
+        <v>0.1212494992476293</v>
       </c>
       <c r="T53">
-        <v>0.9652537992509179</v>
+        <v>0.9833599046632436</v>
       </c>
       <c r="U53">
-        <v>0.1147941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V53">
-        <v>0.22</v>
+        <v>0.2192403696616224</v>
       </c>
       <c r="W53">
-        <v>0.08953940181006696</v>
+        <v>0.1119563283224819</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.269236999496959</v>
+        <v>0.9965471348255565</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1164170503665526</v>
+        <v>0.1173929914153996</v>
       </c>
       <c r="C54">
-        <v>1475.722725858248</v>
+        <v>1349.547960463706</v>
       </c>
       <c r="D54">
-        <v>4879.874725858249</v>
+        <v>4829.075960463707</v>
       </c>
       <c r="E54">
-        <v>2650.752</v>
+        <v>2726.128000000001</v>
       </c>
       <c r="F54">
-        <v>3919.552</v>
+        <v>3994.928</v>
       </c>
       <c r="G54">
         <v>515.4</v>
@@ -5721,37 +5721,37 @@
         <v>560.1</v>
       </c>
       <c r="M54">
-        <v>562.0406505890405</v>
+        <v>572.8491246388297</v>
       </c>
       <c r="N54">
-        <v>-1.940650589040501</v>
+        <v>-12.7491246388297</v>
       </c>
       <c r="O54">
-        <v>-0.4269431295889103</v>
+        <v>-2.804807420542534</v>
       </c>
       <c r="P54">
-        <v>-1.513707459451591</v>
+        <v>-9.944317218287164</v>
       </c>
       <c r="Q54">
-        <v>700.3862925405484</v>
+        <v>691.9556827817128</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1212494992476293</v>
+        <v>0.1228548077422597</v>
       </c>
       <c r="T54">
-        <v>0.9833599046632436</v>
+        <v>1.004282455826291</v>
       </c>
       <c r="U54">
         <v>0.1433941048847012</v>
       </c>
       <c r="V54">
-        <v>0.2192403696616224</v>
+        <v>0.2151037589132899</v>
       </c>
       <c r="W54">
-        <v>0.1119563283224819</v>
+        <v>0.1125494939179954</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9965471348255565</v>
+        <v>0.9777443586967725</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1173929914153996</v>
+        <v>0.1183689324642467</v>
       </c>
       <c r="C55">
-        <v>1349.547960463706</v>
+        <v>1224.419913968799</v>
       </c>
       <c r="D55">
-        <v>4829.075960463707</v>
+        <v>4779.3239139688</v>
       </c>
       <c r="E55">
-        <v>2726.128000000001</v>
+        <v>2801.504000000001</v>
       </c>
       <c r="F55">
-        <v>3994.928</v>
+        <v>4070.304000000001</v>
       </c>
       <c r="G55">
         <v>515.4</v>
@@ -5803,37 +5803,37 @@
         <v>560.1</v>
       </c>
       <c r="M55">
-        <v>572.8491246388297</v>
+        <v>583.657598688619</v>
       </c>
       <c r="N55">
-        <v>-12.7491246388297</v>
+        <v>-23.55759868861901</v>
       </c>
       <c r="O55">
-        <v>-2.804807420542534</v>
+        <v>-5.182671711496182</v>
       </c>
       <c r="P55">
-        <v>-9.944317218287164</v>
+        <v>-18.37492697712283</v>
       </c>
       <c r="Q55">
-        <v>691.9556827817128</v>
+        <v>683.5250730228771</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1228548077422597</v>
+        <v>0.1245299122583958</v>
       </c>
       <c r="T55">
-        <v>1.004282455826291</v>
+        <v>1.026114683126863</v>
       </c>
       <c r="U55">
         <v>0.1433941048847012</v>
       </c>
       <c r="V55">
-        <v>0.2151037589132899</v>
+        <v>0.2111203559704512</v>
       </c>
       <c r="W55">
-        <v>0.1125494939179954</v>
+        <v>0.1131206904173789</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.9777443586967725</v>
+        <v>0.9596379816838692</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1183689324642467</v>
+        <v>0.1193448735130937</v>
       </c>
       <c r="C56">
-        <v>1224.419913968799</v>
+        <v>1100.306564498219</v>
       </c>
       <c r="D56">
-        <v>4779.3239139688</v>
+        <v>4730.58656449822</v>
       </c>
       <c r="E56">
-        <v>2801.504000000001</v>
+        <v>2876.88</v>
       </c>
       <c r="F56">
-        <v>4070.304000000001</v>
+        <v>4145.68</v>
       </c>
       <c r="G56">
         <v>515.4</v>
@@ -5885,37 +5885,37 @@
         <v>560.1</v>
       </c>
       <c r="M56">
-        <v>583.657598688619</v>
+        <v>594.4660727384082</v>
       </c>
       <c r="N56">
-        <v>-23.55759868861901</v>
+        <v>-34.36607273840821</v>
       </c>
       <c r="O56">
-        <v>-5.182671711496182</v>
+        <v>-7.560536002449806</v>
       </c>
       <c r="P56">
-        <v>-18.37492697712283</v>
+        <v>-26.8055367359584</v>
       </c>
       <c r="Q56">
-        <v>683.5250730228771</v>
+        <v>675.0944632640416</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1245299122583958</v>
+        <v>0.1262794658641379</v>
       </c>
       <c r="T56">
-        <v>1.026114683126863</v>
+        <v>1.048917231640793</v>
       </c>
       <c r="U56">
         <v>0.1433941048847012</v>
       </c>
       <c r="V56">
-        <v>0.2111203559704512</v>
+        <v>0.2072818040437157</v>
       </c>
       <c r="W56">
-        <v>0.1131206904173789</v>
+        <v>0.1136711161349666</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9596379816838692</v>
+        <v>0.9421900183805261</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1193448735130937</v>
+        <v>0.1203208145619407</v>
       </c>
       <c r="C57">
-        <v>1100.306564498219</v>
+        <v>977.1771831688056</v>
       </c>
       <c r="D57">
-        <v>4730.58656449822</v>
+        <v>4682.833183168806</v>
       </c>
       <c r="E57">
-        <v>2876.88</v>
+        <v>2952.256</v>
       </c>
       <c r="F57">
-        <v>4145.68</v>
+        <v>4221.056</v>
       </c>
       <c r="G57">
         <v>515.4</v>
@@ -5967,37 +5967,37 @@
         <v>560.1</v>
       </c>
       <c r="M57">
-        <v>594.4660727384082</v>
+        <v>605.2745467881974</v>
       </c>
       <c r="N57">
-        <v>-34.36607273840821</v>
+        <v>-45.1745467881974</v>
       </c>
       <c r="O57">
-        <v>-7.560536002449806</v>
+        <v>-9.938400293403429</v>
       </c>
       <c r="P57">
-        <v>-26.8055367359584</v>
+        <v>-35.23614649479397</v>
       </c>
       <c r="Q57">
-        <v>675.0944632640416</v>
+        <v>666.663853505206</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1262794658641379</v>
+        <v>0.1281085446337774</v>
       </c>
       <c r="T57">
-        <v>1.048917231640793</v>
+        <v>1.072756259632629</v>
       </c>
       <c r="U57">
         <v>0.1433941048847012</v>
       </c>
       <c r="V57">
-        <v>0.2072818040437157</v>
+        <v>0.2035803432572208</v>
       </c>
       <c r="W57">
-        <v>0.1136711161349666</v>
+        <v>0.1142018837912118</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9421900183805261</v>
+        <v>0.9253651966237311</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1203208145619407</v>
+        <v>0.1212967556107877</v>
       </c>
       <c r="C58">
-        <v>977.1771831688056</v>
+        <v>855.0022694805593</v>
       </c>
       <c r="D58">
-        <v>4682.833183168806</v>
+        <v>4636.03426948056</v>
       </c>
       <c r="E58">
-        <v>2952.256</v>
+        <v>3027.632000000001</v>
       </c>
       <c r="F58">
-        <v>4221.056</v>
+        <v>4296.432000000001</v>
       </c>
       <c r="G58">
         <v>515.4</v>
@@ -6049,37 +6049,37 @@
         <v>560.1</v>
       </c>
       <c r="M58">
-        <v>605.2745467881974</v>
+        <v>616.0830208379867</v>
       </c>
       <c r="N58">
-        <v>-45.1745467881974</v>
+        <v>-55.98302083798671</v>
       </c>
       <c r="O58">
-        <v>-9.938400293403429</v>
+        <v>-12.31626458435708</v>
       </c>
       <c r="P58">
-        <v>-35.23614649479397</v>
+        <v>-43.66675625362964</v>
       </c>
       <c r="Q58">
-        <v>666.663853505206</v>
+        <v>658.2332437463704</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1281085446337774</v>
+        <v>0.1300226968345629</v>
       </c>
       <c r="T58">
-        <v>1.072756259632629</v>
+        <v>1.097704079624086</v>
       </c>
       <c r="U58">
         <v>0.1433941048847012</v>
       </c>
       <c r="V58">
-        <v>0.2035803432572208</v>
+        <v>0.2000087582877959</v>
       </c>
       <c r="W58">
-        <v>0.1142018837912118</v>
+        <v>0.1147140280209222</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9253651966237311</v>
+        <v>0.9091307194899813</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1212967556107877</v>
+        <v>0.1222726966596347</v>
       </c>
       <c r="C59">
-        <v>855.0022694805593</v>
+        <v>733.7534905434095</v>
       </c>
       <c r="D59">
-        <v>4636.03426948056</v>
+        <v>4590.161490543411</v>
       </c>
       <c r="E59">
-        <v>3027.632000000001</v>
+        <v>3103.008000000001</v>
       </c>
       <c r="F59">
-        <v>4296.432000000001</v>
+        <v>4371.808000000001</v>
       </c>
       <c r="G59">
         <v>515.4</v>
@@ -6131,37 +6131,37 @@
         <v>560.1</v>
       </c>
       <c r="M59">
-        <v>616.0830208379867</v>
+        <v>626.891494887776</v>
       </c>
       <c r="N59">
-        <v>-55.98302083798671</v>
+        <v>-66.79149488777603</v>
       </c>
       <c r="O59">
-        <v>-12.31626458435708</v>
+        <v>-14.69412887531073</v>
       </c>
       <c r="P59">
-        <v>-43.66675625362964</v>
+        <v>-52.0973660124653</v>
       </c>
       <c r="Q59">
-        <v>658.2332437463704</v>
+        <v>649.8026339875347</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1300226968345629</v>
+        <v>0.1320279991401478</v>
       </c>
       <c r="T59">
-        <v>1.097704079624086</v>
+        <v>1.123839891043707</v>
       </c>
       <c r="U59">
         <v>0.1433941048847012</v>
       </c>
       <c r="V59">
-        <v>0.2000087582877959</v>
+        <v>0.1965603314207649</v>
       </c>
       <c r="W59">
-        <v>0.1147140280209222</v>
+        <v>0.1152085121047804</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9091307194899813</v>
+        <v>0.8934560519125677</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1222726966596347</v>
+        <v>0.1232486377084817</v>
       </c>
       <c r="C60">
-        <v>733.7534905434104</v>
+        <v>613.4036238766903</v>
       </c>
       <c r="D60">
-        <v>4590.161490543411</v>
+        <v>4545.187623876691</v>
       </c>
       <c r="E60">
-        <v>3103.008</v>
+        <v>3178.384</v>
       </c>
       <c r="F60">
-        <v>4371.808</v>
+        <v>4447.184</v>
       </c>
       <c r="G60">
         <v>515.4</v>
@@ -6213,37 +6213,37 @@
         <v>560.1</v>
       </c>
       <c r="M60">
-        <v>626.8914948877759</v>
+        <v>637.6999689375651</v>
       </c>
       <c r="N60">
-        <v>-66.79149488777591</v>
+        <v>-77.59996893756511</v>
       </c>
       <c r="O60">
-        <v>-14.6941288753107</v>
+        <v>-17.07199316626432</v>
       </c>
       <c r="P60">
-        <v>-52.09736601246521</v>
+        <v>-60.52797577130079</v>
       </c>
       <c r="Q60">
-        <v>649.8026339875348</v>
+        <v>641.3720242286992</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1320279991401477</v>
+        <v>0.1341311210703952</v>
       </c>
       <c r="T60">
-        <v>1.123839891043707</v>
+        <v>1.151250620093553</v>
       </c>
       <c r="U60">
         <v>0.1433941048847012</v>
       </c>
       <c r="V60">
-        <v>0.196560331420765</v>
+        <v>0.1932288003797351</v>
       </c>
       <c r="W60">
-        <v>0.1152085121047804</v>
+        <v>0.1156862340163045</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8934560519125678</v>
+        <v>0.8783127289987956</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1232486377084817</v>
+        <v>0.1242245787573287</v>
       </c>
       <c r="C61">
-        <v>613.4036238766903</v>
+        <v>493.9265035386443</v>
       </c>
       <c r="D61">
-        <v>4545.187623876691</v>
+        <v>4501.086503538645</v>
       </c>
       <c r="E61">
-        <v>3178.384</v>
+        <v>3253.76</v>
       </c>
       <c r="F61">
-        <v>4447.184</v>
+        <v>4522.56</v>
       </c>
       <c r="G61">
         <v>515.4</v>
@@ -6295,37 +6295,37 @@
         <v>560.1</v>
       </c>
       <c r="M61">
-        <v>637.6999689375651</v>
+        <v>648.5084429873544</v>
       </c>
       <c r="N61">
-        <v>-77.59996893756511</v>
+        <v>-88.40844298735442</v>
       </c>
       <c r="O61">
-        <v>-17.07199316626432</v>
+        <v>-19.44985745721797</v>
       </c>
       <c r="P61">
-        <v>-60.52797577130079</v>
+        <v>-68.95858553013645</v>
       </c>
       <c r="Q61">
-        <v>641.3720242286992</v>
+        <v>632.9414144698635</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1341311210703952</v>
+        <v>0.1363393990971551</v>
       </c>
       <c r="T61">
-        <v>1.151250620093553</v>
+        <v>1.180031885595892</v>
       </c>
       <c r="U61">
         <v>0.1433941048847012</v>
       </c>
       <c r="V61">
-        <v>0.1932288003797351</v>
+        <v>0.1900083203734061</v>
       </c>
       <c r="W61">
-        <v>0.1156862340163045</v>
+        <v>0.1161480318641111</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8783127289987956</v>
+        <v>0.8636741835154822</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1242245787573287</v>
+        <v>0.1252005198061757</v>
       </c>
       <c r="C62">
-        <v>493.9265035386443</v>
+        <v>375.2969693619716</v>
       </c>
       <c r="D62">
-        <v>4501.086503538645</v>
+        <v>4457.832969361972</v>
       </c>
       <c r="E62">
-        <v>3253.76</v>
+        <v>3329.136</v>
       </c>
       <c r="F62">
-        <v>4522.56</v>
+        <v>4597.936</v>
       </c>
       <c r="G62">
         <v>515.4</v>
@@ -6377,37 +6377,37 @@
         <v>560.1</v>
       </c>
       <c r="M62">
-        <v>648.5084429873544</v>
+        <v>659.3169170371435</v>
       </c>
       <c r="N62">
-        <v>-88.40844298735442</v>
+        <v>-99.2169170371435</v>
       </c>
       <c r="O62">
-        <v>-19.44985745721797</v>
+        <v>-21.82772174817157</v>
       </c>
       <c r="P62">
-        <v>-68.95858553013645</v>
+        <v>-77.38919528897193</v>
       </c>
       <c r="Q62">
-        <v>632.9414144698635</v>
+        <v>624.5108047110281</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1363393990971551</v>
+        <v>0.1386609221509283</v>
       </c>
       <c r="T62">
-        <v>1.180031885595892</v>
+        <v>1.210289113431684</v>
       </c>
       <c r="U62">
         <v>0.1433941048847012</v>
       </c>
       <c r="V62">
-        <v>0.1900083203734061</v>
+        <v>0.1868934298754815</v>
       </c>
       <c r="W62">
-        <v>0.1161480318641111</v>
+        <v>0.1165946887988749</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8636741835154822</v>
+        <v>0.8495155903430975</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1252005198061757</v>
+        <v>0.1261764608550227</v>
       </c>
       <c r="C63">
-        <v>375.2969693619716</v>
+        <v>257.4908190884598</v>
       </c>
       <c r="D63">
-        <v>4457.832969361972</v>
+        <v>4415.40281908846</v>
       </c>
       <c r="E63">
-        <v>3329.136</v>
+        <v>3404.512</v>
       </c>
       <c r="F63">
-        <v>4597.936</v>
+        <v>4673.312</v>
       </c>
       <c r="G63">
         <v>515.4</v>
@@ -6459,37 +6459,37 @@
         <v>560.1</v>
       </c>
       <c r="M63">
-        <v>659.3169170371435</v>
+        <v>670.1253910869328</v>
       </c>
       <c r="N63">
-        <v>-99.2169170371435</v>
+        <v>-110.0253910869328</v>
       </c>
       <c r="O63">
-        <v>-21.82772174817157</v>
+        <v>-24.20558603912522</v>
       </c>
       <c r="P63">
-        <v>-77.38919528897193</v>
+        <v>-85.81980504780759</v>
       </c>
       <c r="Q63">
-        <v>624.5108047110281</v>
+        <v>616.0801949521924</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1386609221509283</v>
+        <v>0.1411046306285843</v>
       </c>
       <c r="T63">
-        <v>1.210289113431684</v>
+        <v>1.242138826943044</v>
       </c>
       <c r="U63">
         <v>0.1433941048847012</v>
       </c>
       <c r="V63">
-        <v>0.1868934298754815</v>
+        <v>0.1838790197161995</v>
       </c>
       <c r="W63">
-        <v>0.1165946887988749</v>
+        <v>0.1170269374454205</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8495155903430975</v>
+        <v>0.8358137259827249</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1261764608550227</v>
+        <v>0.1271524019038698</v>
       </c>
       <c r="C64">
-        <v>257.4908190884598</v>
+        <v>140.4847632113733</v>
       </c>
       <c r="D64">
-        <v>4415.40281908846</v>
+        <v>4373.772763211374</v>
       </c>
       <c r="E64">
-        <v>3404.512</v>
+        <v>3479.888</v>
       </c>
       <c r="F64">
-        <v>4673.312</v>
+        <v>4748.688</v>
       </c>
       <c r="G64">
         <v>515.4</v>
@@ -6541,37 +6541,37 @@
         <v>560.1</v>
       </c>
       <c r="M64">
-        <v>670.1253910869328</v>
+        <v>680.9338651367221</v>
       </c>
       <c r="N64">
-        <v>-110.0253910869328</v>
+        <v>-120.8338651367221</v>
       </c>
       <c r="O64">
-        <v>-24.20558603912522</v>
+        <v>-26.58345033007887</v>
       </c>
       <c r="P64">
-        <v>-85.81980504780759</v>
+        <v>-94.25041480664325</v>
       </c>
       <c r="Q64">
-        <v>616.0801949521924</v>
+        <v>607.6495851933568</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1411046306285843</v>
+        <v>0.1436804314563839</v>
       </c>
       <c r="T64">
-        <v>1.242138826943044</v>
+        <v>1.275710146590154</v>
       </c>
       <c r="U64">
         <v>0.1433941048847012</v>
       </c>
       <c r="V64">
-        <v>0.1838790197161995</v>
+        <v>0.1809603051175296</v>
       </c>
       <c r="W64">
-        <v>0.1170269374454205</v>
+        <v>0.1174454639127107</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8358137259827249</v>
+        <v>0.8225468414433165</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1271524019038698</v>
+        <v>0.1281283429527168</v>
       </c>
       <c r="C65">
-        <v>140.4847632113733</v>
+        <v>24.2563823485616</v>
       </c>
       <c r="D65">
-        <v>4373.772763211374</v>
+        <v>4332.920382348562</v>
       </c>
       <c r="E65">
-        <v>3479.888</v>
+        <v>3555.264</v>
       </c>
       <c r="F65">
-        <v>4748.688</v>
+        <v>4824.064</v>
       </c>
       <c r="G65">
         <v>515.4</v>
@@ -6623,37 +6623,37 @@
         <v>560.1</v>
       </c>
       <c r="M65">
-        <v>680.9338651367221</v>
+        <v>691.7423391865113</v>
       </c>
       <c r="N65">
-        <v>-120.8338651367221</v>
+        <v>-131.6423391865113</v>
       </c>
       <c r="O65">
-        <v>-26.58345033007887</v>
+        <v>-28.96131462103249</v>
       </c>
       <c r="P65">
-        <v>-94.25041480664325</v>
+        <v>-102.6810245654788</v>
       </c>
       <c r="Q65">
-        <v>607.6495851933568</v>
+        <v>599.2189754345211</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1436804314563839</v>
+        <v>0.1463993323301724</v>
       </c>
       <c r="T65">
-        <v>1.275710146590154</v>
+        <v>1.311146539550991</v>
       </c>
       <c r="U65">
         <v>0.1433941048847012</v>
       </c>
       <c r="V65">
-        <v>0.1809603051175296</v>
+        <v>0.1781328003500682</v>
       </c>
       <c r="W65">
-        <v>0.1174454639127107</v>
+        <v>0.117850911427898</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8225468414433165</v>
+        <v>0.8096945470457647</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1281283429527168</v>
+        <v>0.1482001220484656</v>
       </c>
       <c r="C66">
-        <v>24.2563823485616</v>
+        <v>-749.3393098757106</v>
       </c>
       <c r="D66">
-        <v>4332.920382348562</v>
+        <v>3634.70069012429</v>
       </c>
       <c r="E66">
-        <v>3555.264</v>
+        <v>3630.64</v>
       </c>
       <c r="F66">
-        <v>4824.064</v>
+        <v>4899.440000000001</v>
       </c>
       <c r="G66">
         <v>515.4</v>
@@ -6705,45 +6705,45 @@
         <v>560.1</v>
       </c>
       <c r="M66">
-        <v>691.7423391865113</v>
+        <v>840.7150212363007</v>
       </c>
       <c r="N66">
-        <v>-131.6423391865113</v>
+        <v>-280.6150212363007</v>
       </c>
       <c r="O66">
-        <v>-28.96131462103249</v>
+        <v>-61.73530467198615</v>
       </c>
       <c r="P66">
-        <v>-102.6810245654788</v>
+        <v>-218.8797165643145</v>
       </c>
       <c r="Q66">
-        <v>599.2189754345211</v>
+        <v>483.0202834356854</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1463993323301724</v>
+        <v>0.1514617076736111</v>
       </c>
       <c r="T66">
-        <v>1.311146539550991</v>
+        <v>1.377126260884264</v>
       </c>
       <c r="U66">
-        <v>0.1433941048847012</v>
+        <v>0.1715941048847012</v>
       </c>
       <c r="V66">
-        <v>0.1781328003500682</v>
+        <v>0.1465680960699355</v>
       </c>
       <c r="W66">
-        <v>0.117850911427898</v>
+        <v>0.1464438836349257</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8096945470457647</v>
+        <v>0.666218618499707</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1482001220484656</v>
+        <v>0.1494580630973126</v>
       </c>
       <c r="C67">
-        <v>-749.3393098757106</v>
+        <v>-861.0557717601796</v>
       </c>
       <c r="D67">
-        <v>3634.70069012429</v>
+        <v>3598.360228239821</v>
       </c>
       <c r="E67">
-        <v>3630.64</v>
+        <v>3706.016000000001</v>
       </c>
       <c r="F67">
-        <v>4899.440000000001</v>
+        <v>4974.816000000001</v>
       </c>
       <c r="G67">
         <v>515.4</v>
@@ -6787,37 +6787,37 @@
         <v>560.1</v>
       </c>
       <c r="M67">
-        <v>840.7150212363007</v>
+        <v>853.6490984860899</v>
       </c>
       <c r="N67">
-        <v>-280.6150212363007</v>
+        <v>-293.5490984860899</v>
       </c>
       <c r="O67">
-        <v>-61.73530467198615</v>
+        <v>-64.58080166693976</v>
       </c>
       <c r="P67">
-        <v>-218.8797165643145</v>
+        <v>-228.9682968191501</v>
       </c>
       <c r="Q67">
-        <v>483.0202834356854</v>
+        <v>472.9317031808499</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1514617076736111</v>
+        <v>0.1545694049581291</v>
       </c>
       <c r="T67">
-        <v>1.377126260884264</v>
+        <v>1.417629974439683</v>
       </c>
       <c r="U67">
         <v>0.1715941048847012</v>
       </c>
       <c r="V67">
-        <v>0.1465680960699355</v>
+        <v>0.1443473673416032</v>
       </c>
       <c r="W67">
-        <v>0.1464438836349257</v>
+        <v>0.1468249475932557</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.666218618499707</v>
+        <v>0.6561243970072872</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1494580630973126</v>
+        <v>0.1878281527221357</v>
       </c>
       <c r="C68">
-        <v>-861.0557717601796</v>
+        <v>-1777.360287939618</v>
       </c>
       <c r="D68">
-        <v>3598.360228239821</v>
+        <v>2757.431712060383</v>
       </c>
       <c r="E68">
-        <v>3706.016000000001</v>
+        <v>3781.392000000001</v>
       </c>
       <c r="F68">
-        <v>4974.816000000001</v>
+        <v>5050.192000000001</v>
       </c>
       <c r="G68">
         <v>515.4</v>
@@ -6869,45 +6869,45 @@
         <v>560.1</v>
       </c>
       <c r="M68">
-        <v>853.6490984860899</v>
+        <v>1139.293543735879</v>
       </c>
       <c r="N68">
-        <v>-293.5490984860899</v>
+        <v>-579.1935437358792</v>
       </c>
       <c r="O68">
-        <v>-64.58080166693976</v>
+        <v>-127.4225796218934</v>
       </c>
       <c r="P68">
-        <v>-228.9682968191501</v>
+        <v>-451.7709641139858</v>
       </c>
       <c r="Q68">
-        <v>472.9317031808499</v>
+        <v>250.1290358860142</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1545694049581291</v>
+        <v>0.1606901401870907</v>
       </c>
       <c r="T68">
-        <v>1.417629974439683</v>
+        <v>1.497403673022709</v>
       </c>
       <c r="U68">
-        <v>0.1715941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V68">
-        <v>0.1443473673416032</v>
+        <v>0.108156498101394</v>
       </c>
       <c r="W68">
-        <v>0.1468249475932557</v>
+        <v>0.2011946365080534</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.6561243970072872</v>
+        <v>0.4916204459154271</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1878281527221357</v>
+        <v>0.1896260937709827</v>
       </c>
       <c r="C69">
-        <v>-1777.360287939618</v>
+        <v>-1882.604685050287</v>
       </c>
       <c r="D69">
-        <v>2757.431712060383</v>
+        <v>2727.563314949713</v>
       </c>
       <c r="E69">
-        <v>3781.392000000001</v>
+        <v>3856.768</v>
       </c>
       <c r="F69">
-        <v>5050.192000000001</v>
+        <v>5125.568</v>
       </c>
       <c r="G69">
         <v>515.4</v>
@@ -6951,37 +6951,37 @@
         <v>560.1</v>
       </c>
       <c r="M69">
-        <v>1139.293543735879</v>
+        <v>1156.297924985668</v>
       </c>
       <c r="N69">
-        <v>-579.1935437358792</v>
+        <v>-596.1979249856682</v>
       </c>
       <c r="O69">
-        <v>-127.4225796218934</v>
+        <v>-131.163543496847</v>
       </c>
       <c r="P69">
-        <v>-451.7709641139858</v>
+        <v>-465.0343814888212</v>
       </c>
       <c r="Q69">
-        <v>250.1290358860142</v>
+        <v>236.8656185111788</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1606901401870907</v>
+        <v>0.1642804570679373</v>
       </c>
       <c r="T69">
-        <v>1.497403673022709</v>
+        <v>1.544197537804669</v>
       </c>
       <c r="U69">
         <v>0.2255941048847012</v>
       </c>
       <c r="V69">
-        <v>0.108156498101394</v>
+        <v>0.1065659613646088</v>
       </c>
       <c r="W69">
-        <v>0.2011946365080534</v>
+        <v>0.2015534522194747</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4916204459154271</v>
+        <v>0.4843907334754943</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1896260937709827</v>
+        <v>0.1914240348198297</v>
       </c>
       <c r="C70">
-        <v>-1882.604685050287</v>
+        <v>-1987.208949336346</v>
       </c>
       <c r="D70">
-        <v>2727.563314949713</v>
+        <v>2698.335050663654</v>
       </c>
       <c r="E70">
-        <v>3856.768</v>
+        <v>3932.144</v>
       </c>
       <c r="F70">
-        <v>5125.568</v>
+        <v>5200.944</v>
       </c>
       <c r="G70">
         <v>515.4</v>
@@ -7033,37 +7033,37 @@
         <v>560.1</v>
       </c>
       <c r="M70">
-        <v>1156.297924985668</v>
+        <v>1173.302306235458</v>
       </c>
       <c r="N70">
-        <v>-596.1979249856682</v>
+        <v>-613.2023062354575</v>
       </c>
       <c r="O70">
-        <v>-131.163543496847</v>
+        <v>-134.9045073718007</v>
       </c>
       <c r="P70">
-        <v>-465.0343814888212</v>
+        <v>-478.2977988636569</v>
       </c>
       <c r="Q70">
-        <v>236.8656185111788</v>
+        <v>223.6022011363431</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1642804570679373</v>
+        <v>0.1681024072959353</v>
       </c>
       <c r="T70">
-        <v>1.544197537804669</v>
+        <v>1.594010361604819</v>
       </c>
       <c r="U70">
         <v>0.2255941048847012</v>
       </c>
       <c r="V70">
-        <v>0.1065659613646088</v>
+        <v>0.1050215271419333</v>
       </c>
       <c r="W70">
-        <v>0.2015534522194747</v>
+        <v>0.2019018674754924</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4843907334754943</v>
+        <v>0.4773705779178785</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1914240348198297</v>
+        <v>0.1932219758686767</v>
       </c>
       <c r="C71">
-        <v>-1987.208949336346</v>
+        <v>-2091.193441391809</v>
       </c>
       <c r="D71">
-        <v>2698.335050663654</v>
+        <v>2669.726558608191</v>
       </c>
       <c r="E71">
-        <v>3932.144</v>
+        <v>4007.52</v>
       </c>
       <c r="F71">
-        <v>5200.944</v>
+        <v>5276.320000000001</v>
       </c>
       <c r="G71">
         <v>515.4</v>
@@ -7115,37 +7115,37 @@
         <v>560.1</v>
       </c>
       <c r="M71">
-        <v>1173.302306235458</v>
+        <v>1190.306687485247</v>
       </c>
       <c r="N71">
-        <v>-613.2023062354575</v>
+        <v>-630.2066874852468</v>
       </c>
       <c r="O71">
-        <v>-134.9045073718007</v>
+        <v>-138.6454712467543</v>
       </c>
       <c r="P71">
-        <v>-478.2977988636569</v>
+        <v>-491.5612162384925</v>
       </c>
       <c r="Q71">
-        <v>223.6022011363431</v>
+        <v>210.3387837615074</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1681024072959353</v>
+        <v>0.1721791542057998</v>
       </c>
       <c r="T71">
-        <v>1.594010361604819</v>
+        <v>1.64714404032498</v>
       </c>
       <c r="U71">
         <v>0.2255941048847012</v>
       </c>
       <c r="V71">
-        <v>0.1050215271419333</v>
+        <v>0.1035212196113342</v>
       </c>
       <c r="W71">
-        <v>0.2019018674754924</v>
+        <v>0.2022403280099097</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4773705779178785</v>
+        <v>0.4705509982333373</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1932219758686767</v>
+        <v>0.1950199169175237</v>
       </c>
       <c r="C72">
-        <v>-2091.193441391809</v>
+        <v>-2194.577667394921</v>
       </c>
       <c r="D72">
-        <v>2669.726558608191</v>
+        <v>2641.71833260508</v>
       </c>
       <c r="E72">
-        <v>4007.52</v>
+        <v>4082.896000000001</v>
       </c>
       <c r="F72">
-        <v>5276.320000000001</v>
+        <v>5351.696000000001</v>
       </c>
       <c r="G72">
         <v>515.4</v>
@@ -7197,37 +7197,37 @@
         <v>560.1</v>
       </c>
       <c r="M72">
-        <v>1190.306687485247</v>
+        <v>1207.311068735036</v>
       </c>
       <c r="N72">
-        <v>-630.2066874852468</v>
+        <v>-647.2110687350361</v>
       </c>
       <c r="O72">
-        <v>-138.6454712467543</v>
+        <v>-142.3864351217079</v>
       </c>
       <c r="P72">
-        <v>-491.5612162384925</v>
+        <v>-504.8246336133282</v>
       </c>
       <c r="Q72">
-        <v>210.3387837615074</v>
+        <v>197.0753663866718</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1721791542057998</v>
+        <v>0.1765370560749653</v>
       </c>
       <c r="T72">
-        <v>1.64714404032498</v>
+        <v>1.703942110681014</v>
       </c>
       <c r="U72">
         <v>0.2255941048847012</v>
       </c>
       <c r="V72">
-        <v>0.1035212196113342</v>
+        <v>0.1020631742646957</v>
       </c>
       <c r="W72">
-        <v>0.2022403280099097</v>
+        <v>0.2025692544447659</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4705509982333373</v>
+        <v>0.4639235193849804</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1950199169175237</v>
+        <v>0.1968178579663707</v>
       </c>
       <c r="C73">
-        <v>-2194.577667394919</v>
+        <v>-2297.380323461418</v>
       </c>
       <c r="D73">
-        <v>2641.718332605081</v>
+        <v>2614.291676538582</v>
       </c>
       <c r="E73">
-        <v>4082.896</v>
+        <v>4158.272</v>
       </c>
       <c r="F73">
-        <v>5351.696</v>
+        <v>5427.072</v>
       </c>
       <c r="G73">
         <v>515.4</v>
@@ -7279,37 +7279,37 @@
         <v>560.1</v>
       </c>
       <c r="M73">
-        <v>1207.311068735036</v>
+        <v>1224.315449984825</v>
       </c>
       <c r="N73">
-        <v>-647.2110687350358</v>
+        <v>-664.2154499848251</v>
       </c>
       <c r="O73">
-        <v>-142.3864351217079</v>
+        <v>-146.1273989966615</v>
       </c>
       <c r="P73">
-        <v>-504.8246336133279</v>
+        <v>-518.0880509881636</v>
       </c>
       <c r="Q73">
-        <v>197.075366386672</v>
+        <v>183.8119490118364</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1765370560749653</v>
+        <v>0.1812062366490712</v>
       </c>
       <c r="T73">
-        <v>1.703942110681013</v>
+        <v>1.764797186062478</v>
       </c>
       <c r="U73">
         <v>0.2255941048847012</v>
       </c>
       <c r="V73">
-        <v>0.1020631742646957</v>
+        <v>0.1006456301776861</v>
       </c>
       <c r="W73">
-        <v>0.2025692544447659</v>
+        <v>0.2028890440342095</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4639235193849806</v>
+        <v>0.4574801371713003</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1968178579663707</v>
+        <v>0.1986157990152178</v>
       </c>
       <c r="C74">
-        <v>-2297.380323461418</v>
+        <v>-2399.61933726331</v>
       </c>
       <c r="D74">
-        <v>2614.291676538582</v>
+        <v>2587.42866273669</v>
       </c>
       <c r="E74">
-        <v>4158.272</v>
+        <v>4233.648</v>
       </c>
       <c r="F74">
-        <v>5427.072</v>
+        <v>5502.448</v>
       </c>
       <c r="G74">
         <v>515.4</v>
@@ -7361,37 +7361,37 @@
         <v>560.1</v>
       </c>
       <c r="M74">
-        <v>1224.315449984825</v>
+        <v>1241.319831234614</v>
       </c>
       <c r="N74">
-        <v>-664.2154499848251</v>
+        <v>-681.2198312346144</v>
       </c>
       <c r="O74">
-        <v>-146.1273989966615</v>
+        <v>-149.8683628716152</v>
       </c>
       <c r="P74">
-        <v>-518.0880509881636</v>
+        <v>-531.3514683629992</v>
       </c>
       <c r="Q74">
-        <v>183.8119490118364</v>
+        <v>170.5485316370008</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1812062366490712</v>
+        <v>0.1862212824508886</v>
       </c>
       <c r="T74">
-        <v>1.764797186062478</v>
+        <v>1.830160044805533</v>
       </c>
       <c r="U74">
         <v>0.2255941048847012</v>
       </c>
       <c r="V74">
-        <v>0.1006456301776861</v>
+        <v>0.09926692291497803</v>
       </c>
       <c r="W74">
-        <v>0.2028890440342095</v>
+        <v>0.2032000722650381</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4574801371713003</v>
+        <v>0.4512132859771728</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1986157990152178</v>
+        <v>0.2004137400640648</v>
       </c>
       <c r="C75">
-        <v>-2399.61933726331</v>
+        <v>-2501.311907107822</v>
       </c>
       <c r="D75">
-        <v>2587.42866273669</v>
+        <v>2561.112092892178</v>
       </c>
       <c r="E75">
-        <v>4233.648</v>
+        <v>4309.024</v>
       </c>
       <c r="F75">
-        <v>5502.448</v>
+        <v>5577.824000000001</v>
       </c>
       <c r="G75">
         <v>515.4</v>
@@ -7443,37 +7443,37 @@
         <v>560.1</v>
       </c>
       <c r="M75">
-        <v>1241.319831234614</v>
+        <v>1258.324212484404</v>
       </c>
       <c r="N75">
-        <v>-681.2198312346144</v>
+        <v>-698.2242124844039</v>
       </c>
       <c r="O75">
-        <v>-149.8683628716152</v>
+        <v>-153.6093267465689</v>
       </c>
       <c r="P75">
-        <v>-531.3514683629992</v>
+        <v>-544.614885737835</v>
       </c>
       <c r="Q75">
-        <v>170.5485316370008</v>
+        <v>157.2851142621649</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1862212824508886</v>
+        <v>0.191622101006692</v>
       </c>
       <c r="T75">
-        <v>1.830160044805533</v>
+        <v>1.900550815759592</v>
       </c>
       <c r="U75">
         <v>0.2255941048847012</v>
       </c>
       <c r="V75">
-        <v>0.09926692291497803</v>
+        <v>0.09792547801072155</v>
       </c>
       <c r="W75">
-        <v>0.2032000722650381</v>
+        <v>0.203502694327466</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4512132859771728</v>
+        <v>0.4451158091396434</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2004137400640648</v>
+        <v>0.2022116811129117</v>
       </c>
       <c r="C76">
-        <v>-2501.311907107822</v>
+        <v>-2602.474538655557</v>
       </c>
       <c r="D76">
-        <v>2561.112092892178</v>
+        <v>2535.325461344444</v>
       </c>
       <c r="E76">
-        <v>4309.024</v>
+        <v>4384.400000000001</v>
       </c>
       <c r="F76">
-        <v>5577.824000000001</v>
+        <v>5653.200000000001</v>
       </c>
       <c r="G76">
         <v>515.4</v>
@@ -7525,37 +7525,37 @@
         <v>560.1</v>
       </c>
       <c r="M76">
-        <v>1258.324212484404</v>
+        <v>1275.328593734193</v>
       </c>
       <c r="N76">
-        <v>-698.2242124844039</v>
+        <v>-715.2285937341932</v>
       </c>
       <c r="O76">
-        <v>-153.6093267465689</v>
+        <v>-157.3502906215225</v>
       </c>
       <c r="P76">
-        <v>-544.614885737835</v>
+        <v>-557.8783031126707</v>
       </c>
       <c r="Q76">
-        <v>157.2851142621649</v>
+        <v>144.0216968873293</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.191622101006692</v>
+        <v>0.1974549850469597</v>
       </c>
       <c r="T76">
-        <v>1.900550815759592</v>
+        <v>1.976572848389976</v>
       </c>
       <c r="U76">
         <v>0.2255941048847012</v>
       </c>
       <c r="V76">
-        <v>0.09792547801072155</v>
+        <v>0.09661980497057859</v>
       </c>
       <c r="W76">
-        <v>0.203502694327466</v>
+        <v>0.2037972464682291</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4451158091396434</v>
+        <v>0.4391809316844482</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2022116811129117</v>
+        <v>0.2040096221617588</v>
       </c>
       <c r="C77">
-        <v>-2602.474538655557</v>
+        <v>-2703.123079442571</v>
       </c>
       <c r="D77">
-        <v>2535.325461344444</v>
+        <v>2510.052920557429</v>
       </c>
       <c r="E77">
-        <v>4384.400000000001</v>
+        <v>4459.776</v>
       </c>
       <c r="F77">
-        <v>5653.200000000001</v>
+        <v>5728.576</v>
       </c>
       <c r="G77">
         <v>515.4</v>
@@ -7607,37 +7607,37 @@
         <v>560.1</v>
       </c>
       <c r="M77">
-        <v>1275.328593734193</v>
+        <v>1292.332974983982</v>
       </c>
       <c r="N77">
-        <v>-715.2285937341932</v>
+        <v>-732.2329749839822</v>
       </c>
       <c r="O77">
-        <v>-157.3502906215225</v>
+        <v>-161.0912544964761</v>
       </c>
       <c r="P77">
-        <v>-557.8783031126707</v>
+        <v>-571.1417204875061</v>
       </c>
       <c r="Q77">
-        <v>144.0216968873293</v>
+        <v>130.7582795124939</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1974549850469597</v>
+        <v>0.2037739427572497</v>
       </c>
       <c r="T77">
-        <v>1.976572848389976</v>
+        <v>2.058930050406225</v>
       </c>
       <c r="U77">
         <v>0.2255941048847012</v>
       </c>
       <c r="V77">
-        <v>0.09661980497057859</v>
+        <v>0.09534849174728152</v>
       </c>
       <c r="W77">
-        <v>0.2037972464682291</v>
+        <v>0.2040840472368669</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4391809316844482</v>
+        <v>0.4334022352149159</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2040096221617588</v>
+        <v>0.2058075632106058</v>
       </c>
       <c r="C78">
-        <v>-2703.123079442571</v>
+        <v>-2803.272751358094</v>
       </c>
       <c r="D78">
-        <v>2510.052920557429</v>
+        <v>2485.279248641906</v>
       </c>
       <c r="E78">
-        <v>4459.776</v>
+        <v>4535.152</v>
       </c>
       <c r="F78">
-        <v>5728.576</v>
+        <v>5803.952</v>
       </c>
       <c r="G78">
         <v>515.4</v>
@@ -7689,37 +7689,37 @@
         <v>560.1</v>
       </c>
       <c r="M78">
-        <v>1292.332974983982</v>
+        <v>1309.337356233772</v>
       </c>
       <c r="N78">
-        <v>-732.2329749839822</v>
+        <v>-749.2373562337715</v>
       </c>
       <c r="O78">
-        <v>-161.0912544964761</v>
+        <v>-164.8322183714297</v>
       </c>
       <c r="P78">
-        <v>-571.1417204875061</v>
+        <v>-584.4051378623418</v>
       </c>
       <c r="Q78">
-        <v>130.7582795124939</v>
+        <v>117.4948621376582</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2037739427572497</v>
+        <v>0.2106423750510432</v>
       </c>
       <c r="T78">
-        <v>2.058930050406225</v>
+        <v>2.148448748249974</v>
       </c>
       <c r="U78">
         <v>0.2255941048847012</v>
       </c>
       <c r="V78">
-        <v>0.09534849174728152</v>
+        <v>0.09411019964666748</v>
       </c>
       <c r="W78">
-        <v>0.2040840472368669</v>
+        <v>0.2043633986348908</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4334022352149159</v>
+        <v>0.4277736347575795</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2058075632106058</v>
+        <v>0.2076055042594528</v>
       </c>
       <c r="C79">
-        <v>-2803.272751358094</v>
+        <v>-2902.938181217771</v>
       </c>
       <c r="D79">
-        <v>2485.279248641906</v>
+        <v>2460.98981878223</v>
       </c>
       <c r="E79">
-        <v>4535.152</v>
+        <v>4610.528</v>
       </c>
       <c r="F79">
-        <v>5803.952</v>
+        <v>5879.328</v>
       </c>
       <c r="G79">
         <v>515.4</v>
@@ -7771,37 +7771,37 @@
         <v>560.1</v>
       </c>
       <c r="M79">
-        <v>1309.337356233772</v>
+        <v>1326.341737483561</v>
       </c>
       <c r="N79">
-        <v>-749.2373562337715</v>
+        <v>-766.2417374835608</v>
       </c>
       <c r="O79">
-        <v>-164.8322183714297</v>
+        <v>-168.5731822463834</v>
       </c>
       <c r="P79">
-        <v>-584.4051378623418</v>
+        <v>-597.6685552371774</v>
       </c>
       <c r="Q79">
-        <v>117.4948621376582</v>
+        <v>104.2314447628225</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2106423750510432</v>
+        <v>0.218135210280636</v>
       </c>
       <c r="T79">
-        <v>2.148448748249974</v>
+        <v>2.246105509534063</v>
       </c>
       <c r="U79">
         <v>0.2255941048847012</v>
       </c>
       <c r="V79">
-        <v>0.09411019964666748</v>
+        <v>0.09290365862555636</v>
       </c>
       <c r="W79">
-        <v>0.2043633986348908</v>
+        <v>0.204635587176555</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4277736347575795</v>
+        <v>0.4222893573888925</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2076055042594528</v>
+        <v>0.2094034453082998</v>
       </c>
       <c r="C80">
-        <v>-2902.938181217771</v>
+        <v>-3002.133429561427</v>
       </c>
       <c r="D80">
-        <v>2460.98981878223</v>
+        <v>2437.170570438574</v>
       </c>
       <c r="E80">
-        <v>4610.528</v>
+        <v>4685.904</v>
       </c>
       <c r="F80">
-        <v>5879.328</v>
+        <v>5954.704000000001</v>
       </c>
       <c r="G80">
         <v>515.4</v>
@@ -7853,37 +7853,37 @@
         <v>560.1</v>
       </c>
       <c r="M80">
-        <v>1326.341737483561</v>
+        <v>1343.34611873335</v>
       </c>
       <c r="N80">
-        <v>-766.2417374835608</v>
+        <v>-783.24611873335</v>
       </c>
       <c r="O80">
-        <v>-168.5731822463834</v>
+        <v>-172.314146121337</v>
       </c>
       <c r="P80">
-        <v>-597.6685552371774</v>
+        <v>-610.9319726120131</v>
       </c>
       <c r="Q80">
-        <v>104.2314447628225</v>
+        <v>90.96802738798692</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.218135210280636</v>
+        <v>0.2263416488654282</v>
       </c>
       <c r="T80">
-        <v>2.246105509534063</v>
+        <v>2.353062914749971</v>
       </c>
       <c r="U80">
         <v>0.2255941048847012</v>
       </c>
       <c r="V80">
-        <v>0.09290365862555636</v>
+        <v>0.09172766294675183</v>
       </c>
       <c r="W80">
-        <v>0.204635587176555</v>
+        <v>0.2049008848690632</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4222893573888925</v>
+        <v>0.4169439224852356</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2094034453082998</v>
+        <v>0.2112013863571469</v>
       </c>
       <c r="C81">
-        <v>-3002.133429561427</v>
+        <v>-3100.872017794523</v>
       </c>
       <c r="D81">
-        <v>2437.170570438574</v>
+        <v>2413.807982205478</v>
       </c>
       <c r="E81">
-        <v>4685.904</v>
+        <v>4761.280000000001</v>
       </c>
       <c r="F81">
-        <v>5954.704000000001</v>
+        <v>6030.080000000001</v>
       </c>
       <c r="G81">
         <v>515.4</v>
@@ -7935,37 +7935,37 @@
         <v>560.1</v>
       </c>
       <c r="M81">
-        <v>1343.34611873335</v>
+        <v>1360.350499983139</v>
       </c>
       <c r="N81">
-        <v>-783.24611873335</v>
+        <v>-800.2504999831393</v>
       </c>
       <c r="O81">
-        <v>-172.314146121337</v>
+        <v>-176.0551099962906</v>
       </c>
       <c r="P81">
-        <v>-610.9319726120131</v>
+        <v>-624.1953899868487</v>
       </c>
       <c r="Q81">
-        <v>90.96802738798692</v>
+        <v>77.7046100131513</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2263416488654282</v>
+        <v>0.2353687313086997</v>
       </c>
       <c r="T81">
-        <v>2.353062914749971</v>
+        <v>2.47071606048747</v>
       </c>
       <c r="U81">
         <v>0.2255941048847012</v>
       </c>
       <c r="V81">
-        <v>0.09172766294675183</v>
+        <v>0.09058106715991743</v>
       </c>
       <c r="W81">
-        <v>0.2049008848690632</v>
+        <v>0.2051595501192587</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4169439224852356</v>
+        <v>0.4117321234541702</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2112013863571469</v>
+        <v>0.2129993274059939</v>
       </c>
       <c r="C82">
-        <v>-3100.872017794523</v>
+        <v>-3199.166953783368</v>
       </c>
       <c r="D82">
-        <v>2413.807982205478</v>
+        <v>2390.889046216633</v>
       </c>
       <c r="E82">
-        <v>4761.280000000001</v>
+        <v>4836.656000000001</v>
       </c>
       <c r="F82">
-        <v>6030.080000000001</v>
+        <v>6105.456000000001</v>
       </c>
       <c r="G82">
         <v>515.4</v>
@@ -8017,37 +8017,37 @@
         <v>560.1</v>
       </c>
       <c r="M82">
-        <v>1360.350499983139</v>
+        <v>1377.354881232929</v>
       </c>
       <c r="N82">
-        <v>-800.2504999831393</v>
+        <v>-817.2548812329286</v>
       </c>
       <c r="O82">
-        <v>-176.0551099962906</v>
+        <v>-179.7960738712443</v>
       </c>
       <c r="P82">
-        <v>-624.1953899868487</v>
+        <v>-637.4588073616843</v>
       </c>
       <c r="Q82">
-        <v>77.7046100131513</v>
+        <v>64.44119263831567</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2353687313086997</v>
+        <v>0.245346032956526</v>
       </c>
       <c r="T82">
-        <v>2.47071606048747</v>
+        <v>2.600753747881547</v>
       </c>
       <c r="U82">
         <v>0.2255941048847012</v>
       </c>
       <c r="V82">
-        <v>0.09058106715991743</v>
+        <v>0.08946278238016536</v>
       </c>
       <c r="W82">
-        <v>0.2051595501192587</v>
+        <v>0.205411828573153</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4117321234541702</v>
+        <v>0.4066490108189335</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2129993274059939</v>
+        <v>0.2147972684548408</v>
       </c>
       <c r="C83">
-        <v>-3199.166953783368</v>
+        <v>-3297.030756005897</v>
       </c>
       <c r="D83">
-        <v>2390.889046216633</v>
+        <v>2368.401243994103</v>
       </c>
       <c r="E83">
-        <v>4836.656000000001</v>
+        <v>4912.032</v>
       </c>
       <c r="F83">
-        <v>6105.456000000001</v>
+        <v>6180.832</v>
       </c>
       <c r="G83">
         <v>515.4</v>
@@ -8099,37 +8099,37 @@
         <v>560.1</v>
       </c>
       <c r="M83">
-        <v>1377.354881232929</v>
+        <v>1394.359262482718</v>
       </c>
       <c r="N83">
-        <v>-817.2548812329286</v>
+        <v>-834.2592624827176</v>
       </c>
       <c r="O83">
-        <v>-179.7960738712443</v>
+        <v>-183.5370377461979</v>
       </c>
       <c r="P83">
-        <v>-637.4588073616843</v>
+        <v>-650.7222247365198</v>
       </c>
       <c r="Q83">
-        <v>64.44119263831567</v>
+        <v>51.17777526348016</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.245346032956526</v>
+        <v>0.2564319236763329</v>
       </c>
       <c r="T83">
-        <v>2.600753747881547</v>
+        <v>2.7452400672083</v>
       </c>
       <c r="U83">
         <v>0.2255941048847012</v>
       </c>
       <c r="V83">
-        <v>0.08946278238016536</v>
+        <v>0.08837177283894385</v>
       </c>
       <c r="W83">
-        <v>0.205411828573153</v>
+        <v>0.2056579538940255</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4066490108189335</v>
+        <v>0.4016898765406538</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2147972684548408</v>
+        <v>0.2165952095036879</v>
       </c>
       <c r="C84">
-        <v>-3297.030756005897</v>
+        <v>-3394.475476352237</v>
       </c>
       <c r="D84">
-        <v>2368.401243994103</v>
+        <v>2346.332523647764</v>
       </c>
       <c r="E84">
-        <v>4912.032</v>
+        <v>4987.408</v>
       </c>
       <c r="F84">
-        <v>6180.832</v>
+        <v>6256.208000000001</v>
       </c>
       <c r="G84">
         <v>515.4</v>
@@ -8181,37 +8181,37 @@
         <v>560.1</v>
       </c>
       <c r="M84">
-        <v>1394.359262482718</v>
+        <v>1411.363643732507</v>
       </c>
       <c r="N84">
-        <v>-834.2592624827176</v>
+        <v>-851.2636437325069</v>
       </c>
       <c r="O84">
-        <v>-183.5370377461979</v>
+        <v>-187.2780016211515</v>
       </c>
       <c r="P84">
-        <v>-650.7222247365198</v>
+        <v>-663.9856421113554</v>
       </c>
       <c r="Q84">
-        <v>51.17777526348016</v>
+        <v>37.91435788864453</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2564319236763329</v>
+        <v>0.2688220368337643</v>
       </c>
       <c r="T84">
-        <v>2.7452400672083</v>
+        <v>2.906724777044083</v>
       </c>
       <c r="U84">
         <v>0.2255941048847012</v>
       </c>
       <c r="V84">
-        <v>0.08837177283894385</v>
+        <v>0.08730705268425777</v>
       </c>
       <c r="W84">
-        <v>0.2056579538940255</v>
+        <v>0.2058981484842747</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4016898765406538</v>
+        <v>0.396850239473899</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2165952095036879</v>
+        <v>0.2183931505525349</v>
       </c>
       <c r="C85">
-        <v>-3394.475476352237</v>
+        <v>-3491.512721662295</v>
       </c>
       <c r="D85">
-        <v>2346.332523647764</v>
+        <v>2324.671278337706</v>
       </c>
       <c r="E85">
-        <v>4987.408</v>
+        <v>5062.784000000001</v>
       </c>
       <c r="F85">
-        <v>6256.208000000001</v>
+        <v>6331.584000000001</v>
       </c>
       <c r="G85">
         <v>515.4</v>
@@ -8263,37 +8263,37 @@
         <v>560.1</v>
       </c>
       <c r="M85">
-        <v>1411.363643732507</v>
+        <v>1428.368024982296</v>
       </c>
       <c r="N85">
-        <v>-851.2636437325069</v>
+        <v>-868.2680249822962</v>
       </c>
       <c r="O85">
-        <v>-187.2780016211515</v>
+        <v>-191.0189654961052</v>
       </c>
       <c r="P85">
-        <v>-663.9856421113554</v>
+        <v>-677.2490594861911</v>
       </c>
       <c r="Q85">
-        <v>37.91435788864453</v>
+        <v>24.65094051380891</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2688220368337643</v>
+        <v>0.2827609141358747</v>
       </c>
       <c r="T85">
-        <v>2.906724777044083</v>
+        <v>3.088395075609339</v>
       </c>
       <c r="U85">
         <v>0.2255941048847012</v>
       </c>
       <c r="V85">
-        <v>0.08730705268425777</v>
+        <v>0.08626768300944518</v>
       </c>
       <c r="W85">
-        <v>0.2058981484842747</v>
+        <v>0.2061326241557083</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.396850239473899</v>
+        <v>0.3921258318611145</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2183931505525348</v>
+        <v>0.2201910916013819</v>
       </c>
       <c r="C86">
-        <v>-3491.512721662293</v>
+        <v>-3588.153674081269</v>
       </c>
       <c r="D86">
-        <v>2324.671278337707</v>
+        <v>2303.406325918731</v>
       </c>
       <c r="E86">
-        <v>5062.784</v>
+        <v>5138.16</v>
       </c>
       <c r="F86">
-        <v>6331.584</v>
+        <v>6406.96</v>
       </c>
       <c r="G86">
         <v>515.4</v>
@@ -8345,37 +8345,37 @@
         <v>560.1</v>
       </c>
       <c r="M86">
-        <v>1428.368024982296</v>
+        <v>1445.372406232085</v>
       </c>
       <c r="N86">
-        <v>-868.268024982296</v>
+        <v>-885.2724062320852</v>
       </c>
       <c r="O86">
-        <v>-191.0189654961051</v>
+        <v>-194.7599293710587</v>
       </c>
       <c r="P86">
-        <v>-677.2490594861908</v>
+        <v>-690.5124768610265</v>
       </c>
       <c r="Q86">
-        <v>24.65094051380913</v>
+        <v>11.38752313897351</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2827609141358745</v>
+        <v>0.2985583084115995</v>
       </c>
       <c r="T86">
-        <v>3.088395075609336</v>
+        <v>3.294288080649959</v>
       </c>
       <c r="U86">
         <v>0.2255941048847012</v>
       </c>
       <c r="V86">
-        <v>0.08626768300944519</v>
+        <v>0.08525276909168701</v>
       </c>
       <c r="W86">
-        <v>0.2061326241557083</v>
+        <v>0.20636158275252</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3921258318611145</v>
+        <v>0.3875125867803955</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2201910916013819</v>
+        <v>0.2219890326502289</v>
       </c>
       <c r="C87">
-        <v>-3588.153674081269</v>
+        <v>-3684.409110308072</v>
       </c>
       <c r="D87">
-        <v>2303.406325918731</v>
+        <v>2282.526889691928</v>
       </c>
       <c r="E87">
-        <v>5138.16</v>
+        <v>5213.536</v>
       </c>
       <c r="F87">
-        <v>6406.96</v>
+        <v>6482.336</v>
       </c>
       <c r="G87">
         <v>515.4</v>
@@ -8427,37 +8427,37 @@
         <v>560.1</v>
       </c>
       <c r="M87">
-        <v>1445.372406232085</v>
+        <v>1462.376787481875</v>
       </c>
       <c r="N87">
-        <v>-885.2724062320852</v>
+        <v>-902.2767874818745</v>
       </c>
       <c r="O87">
-        <v>-194.7599293710587</v>
+        <v>-198.5008932460124</v>
       </c>
       <c r="P87">
-        <v>-690.5124768610265</v>
+        <v>-703.7758942358621</v>
       </c>
       <c r="Q87">
-        <v>11.38752313897351</v>
+        <v>-1.87589423586212</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2985583084115995</v>
+        <v>0.3166124732981423</v>
       </c>
       <c r="T87">
-        <v>3.294288080649959</v>
+        <v>3.529594372124956</v>
       </c>
       <c r="U87">
         <v>0.2255941048847012</v>
       </c>
       <c r="V87">
-        <v>0.08525276909168701</v>
+        <v>0.08426145782317902</v>
       </c>
       <c r="W87">
-        <v>0.20636158275252</v>
+        <v>0.2065852167308011</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3875125867803955</v>
+        <v>0.3830066264689955</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2219890326502289</v>
+        <v>0.2237869736990759</v>
       </c>
       <c r="C88">
-        <v>-3684.409110308072</v>
+        <v>-3780.289419806268</v>
       </c>
       <c r="D88">
-        <v>2282.526889691928</v>
+        <v>2262.022580193732</v>
       </c>
       <c r="E88">
-        <v>5213.536</v>
+        <v>5288.912</v>
       </c>
       <c r="F88">
-        <v>6482.336</v>
+        <v>6557.712</v>
       </c>
       <c r="G88">
         <v>515.4</v>
@@ -8509,37 +8509,37 @@
         <v>560.1</v>
       </c>
       <c r="M88">
-        <v>1462.376787481875</v>
+        <v>1479.381168731664</v>
       </c>
       <c r="N88">
-        <v>-902.2767874818745</v>
+        <v>-919.2811687316638</v>
       </c>
       <c r="O88">
-        <v>-198.5008932460124</v>
+        <v>-202.241857120966</v>
       </c>
       <c r="P88">
-        <v>-703.7758942358621</v>
+        <v>-717.0393116106977</v>
       </c>
       <c r="Q88">
-        <v>-1.87589423586212</v>
+        <v>-15.13931161069775</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3166124732981423</v>
+        <v>0.337444202013384</v>
       </c>
       <c r="T88">
-        <v>3.529594372124956</v>
+        <v>3.801101631519183</v>
       </c>
       <c r="U88">
         <v>0.2255941048847012</v>
       </c>
       <c r="V88">
-        <v>0.08426145782317902</v>
+        <v>0.08329293531946431</v>
       </c>
       <c r="W88">
-        <v>0.2065852167308011</v>
+        <v>0.2068037096980873</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3830066264689955</v>
+        <v>0.3786042514521105</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2237869736990759</v>
+        <v>0.2255849147479229</v>
       </c>
       <c r="C89">
-        <v>-3780.289419806268</v>
+        <v>-3875.804622042222</v>
       </c>
       <c r="D89">
-        <v>2262.022580193732</v>
+        <v>2241.883377957778</v>
       </c>
       <c r="E89">
-        <v>5288.912</v>
+        <v>5364.288</v>
       </c>
       <c r="F89">
-        <v>6557.712</v>
+        <v>6633.088000000001</v>
       </c>
       <c r="G89">
         <v>515.4</v>
@@ -8591,37 +8591,37 @@
         <v>560.1</v>
       </c>
       <c r="M89">
-        <v>1479.381168731664</v>
+        <v>1496.385549981453</v>
       </c>
       <c r="N89">
-        <v>-919.2811687316638</v>
+        <v>-936.2855499814531</v>
       </c>
       <c r="O89">
-        <v>-202.241857120966</v>
+        <v>-205.9828209959197</v>
       </c>
       <c r="P89">
-        <v>-717.0393116106977</v>
+        <v>-730.3027289855333</v>
       </c>
       <c r="Q89">
-        <v>-15.13931161069775</v>
+        <v>-28.40272898553337</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.337444202013384</v>
+        <v>0.3617478855144994</v>
       </c>
       <c r="T89">
-        <v>3.801101631519183</v>
+        <v>4.117860100812449</v>
       </c>
       <c r="U89">
         <v>0.2255941048847012</v>
       </c>
       <c r="V89">
-        <v>0.08329293531946431</v>
+        <v>0.08234642469083404</v>
       </c>
       <c r="W89">
-        <v>0.2068037096980873</v>
+        <v>0.207017236916117</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3786042514521105</v>
+        <v>0.374301930412882</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2255849147479229</v>
+        <v>0.22738285579677</v>
       </c>
       <c r="C90">
-        <v>-3875.804622042222</v>
+        <v>-3970.96438281051</v>
       </c>
       <c r="D90">
-        <v>2241.883377957778</v>
+        <v>2222.099617189491</v>
       </c>
       <c r="E90">
-        <v>5364.288</v>
+        <v>5439.664000000001</v>
       </c>
       <c r="F90">
-        <v>6633.088000000001</v>
+        <v>6708.464000000001</v>
       </c>
       <c r="G90">
         <v>515.4</v>
@@ -8673,37 +8673,37 @@
         <v>560.1</v>
       </c>
       <c r="M90">
-        <v>1496.385549981453</v>
+        <v>1513.389931231242</v>
       </c>
       <c r="N90">
-        <v>-936.2855499814531</v>
+        <v>-953.2899312312423</v>
       </c>
       <c r="O90">
-        <v>-205.9828209959197</v>
+        <v>-209.7237848708733</v>
       </c>
       <c r="P90">
-        <v>-730.3027289855333</v>
+        <v>-743.566146360369</v>
       </c>
       <c r="Q90">
-        <v>-28.40272898553337</v>
+        <v>-41.666146360369</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3617478855144994</v>
+        <v>0.3904704205612721</v>
       </c>
       <c r="T90">
-        <v>4.117860100812449</v>
+        <v>4.492211019068127</v>
       </c>
       <c r="U90">
         <v>0.2255941048847012</v>
       </c>
       <c r="V90">
-        <v>0.08234642469083404</v>
+        <v>0.08142118396397073</v>
       </c>
       <c r="W90">
-        <v>0.207017236916117</v>
+        <v>0.2072259657696967</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.374301930412882</v>
+        <v>0.3700962907453216</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.22738285579677</v>
+        <v>0.229180796845617</v>
       </c>
       <c r="C91">
-        <v>-3970.96438281051</v>
+        <v>-4065.778029702501</v>
       </c>
       <c r="D91">
-        <v>2222.099617189491</v>
+        <v>2202.661970297499</v>
       </c>
       <c r="E91">
-        <v>5439.664000000001</v>
+        <v>5515.04</v>
       </c>
       <c r="F91">
-        <v>6708.464000000001</v>
+        <v>6783.84</v>
       </c>
       <c r="G91">
         <v>515.4</v>
@@ -8755,37 +8755,37 @@
         <v>560.1</v>
       </c>
       <c r="M91">
-        <v>1513.389931231242</v>
+        <v>1530.394312481032</v>
       </c>
       <c r="N91">
-        <v>-953.2899312312423</v>
+        <v>-970.2943124810316</v>
       </c>
       <c r="O91">
-        <v>-209.7237848708733</v>
+        <v>-213.464748745827</v>
       </c>
       <c r="P91">
-        <v>-743.566146360369</v>
+        <v>-756.8295637352046</v>
       </c>
       <c r="Q91">
-        <v>-41.666146360369</v>
+        <v>-54.92956373520462</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3904704205612721</v>
+        <v>0.4249374626173993</v>
       </c>
       <c r="T91">
-        <v>4.492211019068127</v>
+        <v>4.94143212097494</v>
       </c>
       <c r="U91">
         <v>0.2255941048847012</v>
       </c>
       <c r="V91">
-        <v>0.08142118396397073</v>
+        <v>0.08051650414214884</v>
       </c>
       <c r="W91">
-        <v>0.2072259657696967</v>
+        <v>0.2074300562043078</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3700962907453216</v>
+        <v>0.3659841097370402</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.229180796845617</v>
+        <v>0.230978737894464</v>
       </c>
       <c r="C92">
-        <v>-4065.778029702501</v>
+        <v>-4160.254566770131</v>
       </c>
       <c r="D92">
-        <v>2202.661970297499</v>
+        <v>2183.56143322987</v>
       </c>
       <c r="E92">
-        <v>5515.04</v>
+        <v>5590.416</v>
       </c>
       <c r="F92">
-        <v>6783.84</v>
+        <v>6859.216</v>
       </c>
       <c r="G92">
         <v>515.4</v>
@@ -8837,37 +8837,37 @@
         <v>560.1</v>
       </c>
       <c r="M92">
-        <v>1530.394312481032</v>
+        <v>1547.398693730821</v>
       </c>
       <c r="N92">
-        <v>-970.2943124810316</v>
+        <v>-987.2986937308209</v>
       </c>
       <c r="O92">
-        <v>-213.464748745827</v>
+        <v>-217.2057126207806</v>
       </c>
       <c r="P92">
-        <v>-756.8295637352046</v>
+        <v>-770.0929811100403</v>
       </c>
       <c r="Q92">
-        <v>-54.92956373520462</v>
+        <v>-68.19298111004036</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4249374626173993</v>
+        <v>0.4670638473526659</v>
       </c>
       <c r="T92">
-        <v>4.94143212097494</v>
+        <v>5.4904801344166</v>
       </c>
       <c r="U92">
         <v>0.2255941048847012</v>
       </c>
       <c r="V92">
-        <v>0.08051650414214884</v>
+        <v>0.07963170739333401</v>
       </c>
       <c r="W92">
-        <v>0.2074300562043078</v>
+        <v>0.2076296611348616</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3659841097370402</v>
+        <v>0.3619623063333364</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.230978737894464</v>
+        <v>0.232776678943311</v>
       </c>
       <c r="C93">
-        <v>-4160.254566770131</v>
+        <v>-4254.402688433267</v>
       </c>
       <c r="D93">
-        <v>2183.56143322987</v>
+        <v>2164.789311566733</v>
       </c>
       <c r="E93">
-        <v>5590.416</v>
+        <v>5665.792</v>
       </c>
       <c r="F93">
-        <v>6859.216</v>
+        <v>6934.592000000001</v>
       </c>
       <c r="G93">
         <v>515.4</v>
@@ -8919,37 +8919,37 @@
         <v>560.1</v>
       </c>
       <c r="M93">
-        <v>1547.398693730821</v>
+        <v>1564.40307498061</v>
       </c>
       <c r="N93">
-        <v>-987.2986937308209</v>
+        <v>-1004.30307498061</v>
       </c>
       <c r="O93">
-        <v>-217.2057126207806</v>
+        <v>-220.9466764957342</v>
       </c>
       <c r="P93">
-        <v>-770.0929811100403</v>
+        <v>-783.356398484876</v>
       </c>
       <c r="Q93">
-        <v>-68.19298111004036</v>
+        <v>-81.45639848487599</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4670638473526659</v>
+        <v>0.5197218282717493</v>
       </c>
       <c r="T93">
-        <v>5.4904801344166</v>
+        <v>6.176790151218677</v>
       </c>
       <c r="U93">
         <v>0.2255941048847012</v>
       </c>
       <c r="V93">
-        <v>0.07963170739333401</v>
+        <v>0.07876614535644995</v>
       </c>
       <c r="W93">
-        <v>0.2076296611348616</v>
+        <v>0.2078249268277946</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3619623063333364</v>
+        <v>0.3580279334384089</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.232776678943311</v>
+        <v>0.234574619992158</v>
       </c>
       <c r="C94">
-        <v>-4254.402688433267</v>
+        <v>-4348.230792675833</v>
       </c>
       <c r="D94">
-        <v>2164.789311566733</v>
+        <v>2146.337207324167</v>
       </c>
       <c r="E94">
-        <v>5665.792</v>
+        <v>5741.168000000001</v>
       </c>
       <c r="F94">
-        <v>6934.592000000001</v>
+        <v>7009.968000000001</v>
       </c>
       <c r="G94">
         <v>515.4</v>
@@ -9001,37 +9001,37 @@
         <v>560.1</v>
       </c>
       <c r="M94">
-        <v>1564.40307498061</v>
+        <v>1581.407456230399</v>
       </c>
       <c r="N94">
-        <v>-1004.30307498061</v>
+        <v>-1021.307456230399</v>
       </c>
       <c r="O94">
-        <v>-220.9466764957342</v>
+        <v>-224.6876403706879</v>
       </c>
       <c r="P94">
-        <v>-783.356398484876</v>
+        <v>-796.6198158597116</v>
       </c>
       <c r="Q94">
-        <v>-81.45639848487599</v>
+        <v>-94.71981585971162</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5197218282717493</v>
+        <v>0.5874249465962849</v>
       </c>
       <c r="T94">
-        <v>6.176790151218677</v>
+        <v>7.059188744249917</v>
       </c>
       <c r="U94">
         <v>0.2255941048847012</v>
       </c>
       <c r="V94">
-        <v>0.07876614535644995</v>
+        <v>0.07791919755691822</v>
       </c>
       <c r="W94">
-        <v>0.2078249268277946</v>
+        <v>0.2080159932585141</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3580279334384089</v>
+        <v>0.3541781707132646</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.234574619992158</v>
+        <v>0.236372561041005</v>
       </c>
       <c r="C95">
-        <v>-4348.230792675833</v>
+        <v>-4441.746993572749</v>
       </c>
       <c r="D95">
-        <v>2146.337207324167</v>
+        <v>2128.197006427252</v>
       </c>
       <c r="E95">
-        <v>5741.168000000001</v>
+        <v>5816.544000000001</v>
       </c>
       <c r="F95">
-        <v>7009.968000000001</v>
+        <v>7085.344000000001</v>
       </c>
       <c r="G95">
         <v>515.4</v>
@@ -9083,37 +9083,37 @@
         <v>560.1</v>
       </c>
       <c r="M95">
-        <v>1581.407456230399</v>
+        <v>1598.411837480189</v>
       </c>
       <c r="N95">
-        <v>-1021.307456230399</v>
+        <v>-1038.311837480189</v>
       </c>
       <c r="O95">
-        <v>-224.6876403706879</v>
+        <v>-228.4286042456415</v>
       </c>
       <c r="P95">
-        <v>-796.6198158597116</v>
+        <v>-809.8832332345473</v>
       </c>
       <c r="Q95">
-        <v>-94.71981585971162</v>
+        <v>-107.9832332345474</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5874249465962849</v>
+        <v>0.6776957710289992</v>
       </c>
       <c r="T95">
-        <v>7.059188744249917</v>
+        <v>8.235720201624906</v>
       </c>
       <c r="U95">
         <v>0.2255941048847012</v>
       </c>
       <c r="V95">
-        <v>0.07791919755691822</v>
+        <v>0.077090269923334</v>
       </c>
       <c r="W95">
-        <v>0.2080159932585141</v>
+        <v>0.2082029944460267</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3541781707132646</v>
+        <v>0.3504103178333362</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.236372561041005</v>
+        <v>0.238170502089852</v>
       </c>
       <c r="C96">
-        <v>-4441.746993572749</v>
+        <v>-4534.959133186943</v>
       </c>
       <c r="D96">
-        <v>2128.197006427252</v>
+        <v>2110.360866813057</v>
       </c>
       <c r="E96">
-        <v>5816.544000000001</v>
+        <v>5891.920000000001</v>
       </c>
       <c r="F96">
-        <v>7085.344000000001</v>
+        <v>7160.720000000001</v>
       </c>
       <c r="G96">
         <v>515.4</v>
@@ -9165,37 +9165,37 @@
         <v>560.1</v>
       </c>
       <c r="M96">
-        <v>1598.411837480189</v>
+        <v>1615.416218729978</v>
       </c>
       <c r="N96">
-        <v>-1038.311837480189</v>
+        <v>-1055.316218729978</v>
       </c>
       <c r="O96">
-        <v>-228.4286042456415</v>
+        <v>-232.1695681205952</v>
       </c>
       <c r="P96">
-        <v>-809.8832332345473</v>
+        <v>-823.146650609383</v>
       </c>
       <c r="Q96">
-        <v>-107.9832332345474</v>
+        <v>-121.246650609383</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6776957710289992</v>
+        <v>0.8040749252347995</v>
       </c>
       <c r="T96">
-        <v>8.235720201624906</v>
+        <v>9.882864241949893</v>
       </c>
       <c r="U96">
         <v>0.2255941048847012</v>
       </c>
       <c r="V96">
-        <v>0.077090269923334</v>
+        <v>0.07627879339782521</v>
       </c>
       <c r="W96">
-        <v>0.2082029944460267</v>
+        <v>0.2083860587664338</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3504103178333362</v>
+        <v>0.3467217881719327</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.238170502089852</v>
+        <v>0.2399684431386991</v>
       </c>
       <c r="C97">
-        <v>-4534.959133186943</v>
+        <v>-4627.874792873116</v>
       </c>
       <c r="D97">
-        <v>2110.360866813057</v>
+        <v>2092.821207126885</v>
       </c>
       <c r="E97">
-        <v>5891.920000000001</v>
+        <v>5967.296000000001</v>
       </c>
       <c r="F97">
-        <v>7160.720000000001</v>
+        <v>7236.096000000001</v>
       </c>
       <c r="G97">
         <v>515.4</v>
@@ -9247,37 +9247,37 @@
         <v>560.1</v>
       </c>
       <c r="M97">
-        <v>1615.416218729978</v>
+        <v>1632.420599979767</v>
       </c>
       <c r="N97">
-        <v>-1055.316218729978</v>
+        <v>-1072.320599979767</v>
       </c>
       <c r="O97">
-        <v>-232.1695681205952</v>
+        <v>-235.9105319955488</v>
       </c>
       <c r="P97">
-        <v>-823.146650609383</v>
+        <v>-836.4100679842186</v>
       </c>
       <c r="Q97">
-        <v>-121.246650609383</v>
+        <v>-134.5100679842186</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8040749252347995</v>
+        <v>0.9936436565434998</v>
       </c>
       <c r="T97">
-        <v>9.882864241949893</v>
+        <v>12.35358030243737</v>
       </c>
       <c r="U97">
         <v>0.2255941048847012</v>
       </c>
       <c r="V97">
-        <v>0.07627879339782521</v>
+        <v>0.07548422263326453</v>
       </c>
       <c r="W97">
-        <v>0.2083860587664338</v>
+        <v>0.2085653092468324</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3467217881719327</v>
+        <v>0.343110102878475</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.239968443138699</v>
+        <v>0.241766384187546</v>
       </c>
       <c r="C98">
-        <v>-4627.874792873115</v>
+        <v>-4720.501304022429</v>
       </c>
       <c r="D98">
-        <v>2092.821207126886</v>
+        <v>2075.57069597757</v>
       </c>
       <c r="E98">
-        <v>5967.296</v>
+        <v>6042.672</v>
       </c>
       <c r="F98">
-        <v>7236.096</v>
+        <v>7311.472</v>
       </c>
       <c r="G98">
         <v>515.4</v>
@@ -9329,37 +9329,37 @@
         <v>560.1</v>
       </c>
       <c r="M98">
-        <v>1632.420599979767</v>
+        <v>1649.424981229556</v>
       </c>
       <c r="N98">
-        <v>-1072.320599979767</v>
+        <v>-1089.324981229556</v>
       </c>
       <c r="O98">
-        <v>-235.9105319955487</v>
+        <v>-239.6514958705024</v>
       </c>
       <c r="P98">
-        <v>-836.4100679842182</v>
+        <v>-849.6734853590539</v>
       </c>
       <c r="Q98">
-        <v>-134.5100679842183</v>
+        <v>-147.7734853590539</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9936436565434972</v>
+        <v>1.309591542057996</v>
       </c>
       <c r="T98">
-        <v>12.35358030243734</v>
+        <v>16.47144040324978</v>
       </c>
       <c r="U98">
         <v>0.2255941048847012</v>
       </c>
       <c r="V98">
-        <v>0.07548422263326453</v>
+        <v>0.07470603477106594</v>
       </c>
       <c r="W98">
-        <v>0.2085653092468324</v>
+        <v>0.2087408638410372</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3431101028784752</v>
+        <v>0.339572885323027</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.241766384187546</v>
+        <v>0.2435643252363931</v>
       </c>
       <c r="C99">
-        <v>-4720.501304022429</v>
+        <v>-4812.845758280185</v>
       </c>
       <c r="D99">
-        <v>2075.57069597757</v>
+        <v>2058.602241719815</v>
       </c>
       <c r="E99">
-        <v>6042.672</v>
+        <v>6118.048</v>
       </c>
       <c r="F99">
-        <v>7311.472</v>
+        <v>7386.848</v>
       </c>
       <c r="G99">
         <v>515.4</v>
@@ -9411,37 +9411,37 @@
         <v>560.1</v>
       </c>
       <c r="M99">
-        <v>1649.424981229556</v>
+        <v>1666.429362479345</v>
       </c>
       <c r="N99">
-        <v>-1089.324981229556</v>
+        <v>-1106.329362479345</v>
       </c>
       <c r="O99">
-        <v>-239.6514958705024</v>
+        <v>-243.392459745456</v>
       </c>
       <c r="P99">
-        <v>-849.6734853590539</v>
+        <v>-862.9369027338895</v>
       </c>
       <c r="Q99">
-        <v>-147.7734853590539</v>
+        <v>-161.0369027338895</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.309591542057996</v>
+        <v>1.941487313086995</v>
       </c>
       <c r="T99">
-        <v>16.47144040324978</v>
+        <v>24.70716060487467</v>
       </c>
       <c r="U99">
         <v>0.2255941048847012</v>
       </c>
       <c r="V99">
-        <v>0.07470603477106594</v>
+        <v>0.07394372829381016</v>
       </c>
       <c r="W99">
-        <v>0.2087408638410372</v>
+        <v>0.2089128356884216</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.339572885323027</v>
+        <v>0.3361078558809553</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2435643252363931</v>
+        <v>0.24536226628524</v>
       </c>
       <c r="C100">
-        <v>-4812.845758280185</v>
+        <v>-4904.915017266335</v>
       </c>
       <c r="D100">
-        <v>2058.602241719815</v>
+        <v>2041.908982733665</v>
       </c>
       <c r="E100">
-        <v>6118.048</v>
+        <v>6193.424</v>
       </c>
       <c r="F100">
-        <v>7386.848</v>
+        <v>7462.224</v>
       </c>
       <c r="G100">
         <v>515.4</v>
@@ -9493,37 +9493,37 @@
         <v>560.1</v>
       </c>
       <c r="M100">
-        <v>1666.429362479345</v>
+        <v>1683.433743729135</v>
       </c>
       <c r="N100">
-        <v>-1106.329362479345</v>
+        <v>-1123.333743729135</v>
       </c>
       <c r="O100">
-        <v>-243.392459745456</v>
+        <v>-247.1334236204096</v>
       </c>
       <c r="P100">
-        <v>-862.9369027338895</v>
+        <v>-876.2003201087251</v>
       </c>
       <c r="Q100">
-        <v>-161.0369027338895</v>
+        <v>-174.3003201087251</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.941487313086995</v>
+        <v>3.837174626173989</v>
       </c>
       <c r="T100">
-        <v>24.70716060487467</v>
+        <v>49.41432120974935</v>
       </c>
       <c r="U100">
         <v>0.2255941048847012</v>
       </c>
       <c r="V100">
-        <v>0.07394372829381016</v>
+        <v>0.07319682194740804</v>
       </c>
       <c r="W100">
-        <v>0.2089128356884216</v>
+        <v>0.2090813333570709</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3361078558809553</v>
+        <v>0.3327128270336729</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.24536226628524</v>
-      </c>
-      <c r="C101">
-        <v>-4904.915017266335</v>
-      </c>
-      <c r="D101">
-        <v>2041.908982733665</v>
-      </c>
-      <c r="E101">
-        <v>6193.424</v>
-      </c>
-      <c r="F101">
-        <v>7462.224</v>
-      </c>
-      <c r="G101">
-        <v>515.4</v>
-      </c>
-      <c r="H101">
-        <v>6268.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1262</v>
-      </c>
-      <c r="K101">
-        <v>701.9</v>
-      </c>
-      <c r="L101">
-        <v>560.1</v>
-      </c>
-      <c r="M101">
-        <v>1683.433743729135</v>
-      </c>
-      <c r="N101">
-        <v>-1123.333743729135</v>
-      </c>
-      <c r="O101">
-        <v>-247.1334236204096</v>
-      </c>
-      <c r="P101">
-        <v>-876.2003201087251</v>
-      </c>
-      <c r="Q101">
-        <v>-174.3003201087251</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.837174626173989</v>
-      </c>
-      <c r="T101">
-        <v>49.41432120974935</v>
-      </c>
-      <c r="U101">
-        <v>0.2255941048847012</v>
-      </c>
-      <c r="V101">
-        <v>0.07319682194740804</v>
-      </c>
-      <c r="W101">
-        <v>0.2090813333570709</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3327128270336729</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
